--- a/artfynd/A 15853-2025 artfynd.xlsx
+++ b/artfynd/A 15853-2025 artfynd.xlsx
@@ -10440,10 +10440,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123913494</v>
+        <v>123913280</v>
       </c>
       <c r="B97" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10456,21 +10456,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10480,10 +10480,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>465741</v>
+        <v>465753</v>
       </c>
       <c r="R97" t="n">
-        <v>6798286</v>
+        <v>6798400</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10542,10 +10542,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123913280</v>
+        <v>123913446</v>
       </c>
       <c r="B98" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10558,21 +10558,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10582,10 +10582,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>465753</v>
+        <v>465875</v>
       </c>
       <c r="R98" t="n">
-        <v>6798400</v>
+        <v>6798559</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10644,10 +10644,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123913446</v>
+        <v>123913276</v>
       </c>
       <c r="B99" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10660,21 +10660,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10684,10 +10684,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>465875</v>
+        <v>465694</v>
       </c>
       <c r="R99" t="n">
-        <v>6798559</v>
+        <v>6798446</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10746,10 +10746,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123913276</v>
+        <v>123913494</v>
       </c>
       <c r="B100" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10762,21 +10762,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10786,10 +10786,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>465694</v>
+        <v>465741</v>
       </c>
       <c r="R100" t="n">
-        <v>6798446</v>
+        <v>6798286</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11562,10 +11562,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123913498</v>
+        <v>123913327</v>
       </c>
       <c r="B108" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11578,21 +11578,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11602,10 +11602,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>465746</v>
+        <v>465779</v>
       </c>
       <c r="R108" t="n">
-        <v>6798258</v>
+        <v>6798140</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11664,10 +11664,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123913323</v>
+        <v>123913498</v>
       </c>
       <c r="B109" t="n">
-        <v>90955</v>
+        <v>78788</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11676,25 +11676,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11704,10 +11704,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>465849</v>
+        <v>465746</v>
       </c>
       <c r="R109" t="n">
-        <v>6798130</v>
+        <v>6798258</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11766,10 +11766,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123913517</v>
+        <v>123913323</v>
       </c>
       <c r="B110" t="n">
-        <v>78788</v>
+        <v>90955</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11778,25 +11778,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11806,10 +11806,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>465837</v>
+        <v>465849</v>
       </c>
       <c r="R110" t="n">
-        <v>6798096</v>
+        <v>6798130</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11868,10 +11868,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123913311</v>
+        <v>123913517</v>
       </c>
       <c r="B111" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11884,21 +11884,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11908,10 +11908,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>465842</v>
+        <v>465837</v>
       </c>
       <c r="R111" t="n">
-        <v>6798116</v>
+        <v>6798096</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11970,10 +11970,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123913327</v>
+        <v>123913311</v>
       </c>
       <c r="B112" t="n">
-        <v>79377</v>
+        <v>78820</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11986,21 +11986,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12010,10 +12010,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>465779</v>
+        <v>465842</v>
       </c>
       <c r="R112" t="n">
-        <v>6798140</v>
+        <v>6798116</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12786,10 +12786,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>123913441</v>
+        <v>123913282</v>
       </c>
       <c r="B120" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12802,21 +12802,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>465893</v>
+        <v>465748</v>
       </c>
       <c r="R120" t="n">
-        <v>6798543</v>
+        <v>6798396</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12888,10 +12888,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123913282</v>
+        <v>123913441</v>
       </c>
       <c r="B121" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12904,21 +12904,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12928,10 +12928,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>465748</v>
+        <v>465893</v>
       </c>
       <c r="R121" t="n">
-        <v>6798396</v>
+        <v>6798543</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>

--- a/artfynd/A 15853-2025 artfynd.xlsx
+++ b/artfynd/A 15853-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123877304</v>
+        <v>123878436</v>
       </c>
       <c r="B2" t="n">
         <v>78788</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465832</v>
+        <v>465800</v>
       </c>
       <c r="R2" t="n">
-        <v>6798359</v>
+        <v>6798391</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +753,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Garnlav synligt ca 30 meters radie. Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -765,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123876786</v>
+        <v>123876143</v>
       </c>
       <c r="B3" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465862</v>
+        <v>465821</v>
       </c>
       <c r="R3" t="n">
-        <v>6798219</v>
+        <v>6798095</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -981,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123877884</v>
+        <v>123878923</v>
       </c>
       <c r="B5" t="n">
         <v>78788</v>
@@ -1017,17 +1022,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465816</v>
+        <v>465911</v>
       </c>
       <c r="R5" t="n">
-        <v>6798323</v>
+        <v>6798461</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1057,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,12 +1076,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123876339</v>
+        <v>123878630</v>
       </c>
       <c r="B7" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,37 +1206,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465823</v>
+        <v>465884</v>
       </c>
       <c r="R7" t="n">
-        <v>6798111</v>
+        <v>6798405</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1266,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,19 +1285,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123878365</v>
+        <v>123878210</v>
       </c>
       <c r="B8" t="n">
         <v>78788</v>
@@ -1332,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465783</v>
+        <v>465813</v>
       </c>
       <c r="R8" t="n">
-        <v>6798386</v>
+        <v>6798394</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1394,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123876291</v>
+        <v>123878365</v>
       </c>
       <c r="B9" t="n">
         <v>78788</v>
@@ -1434,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465806</v>
+        <v>465783</v>
       </c>
       <c r="R9" t="n">
-        <v>6798100</v>
+        <v>6798386</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1496,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123878923</v>
+        <v>123877017</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,37 +1517,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465911</v>
+        <v>465805</v>
       </c>
       <c r="R10" t="n">
-        <v>6798461</v>
+        <v>6798194</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1572,6 +1577,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1586,19 +1596,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123878436</v>
+        <v>123877248</v>
       </c>
       <c r="B11" t="n">
         <v>78788</v>
@@ -1638,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465800</v>
+        <v>465799</v>
       </c>
       <c r="R11" t="n">
-        <v>6798391</v>
+        <v>6798259</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,7 +1688,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Garnlav synligt ca 30 meters radie. Miljöbilder.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123877481</v>
+        <v>123877304</v>
       </c>
       <c r="B12" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,39 +1731,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465807</v>
+        <v>465832</v>
       </c>
       <c r="R12" t="n">
-        <v>6798288</v>
+        <v>6798359</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,22 +1805,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123876691</v>
+        <v>123877326</v>
       </c>
       <c r="B13" t="n">
-        <v>78820</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,37 +1833,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465832</v>
+        <v>465799</v>
       </c>
       <c r="R13" t="n">
-        <v>6798208</v>
+        <v>6798259</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1888,6 +1898,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,22 +1917,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123877326</v>
+        <v>123876691</v>
       </c>
       <c r="B14" t="n">
-        <v>57507</v>
+        <v>78820</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,42 +1945,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465799</v>
+        <v>465832</v>
       </c>
       <c r="R14" t="n">
-        <v>6798259</v>
+        <v>6798208</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1995,11 +2005,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2014,22 +2019,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123878210</v>
+        <v>123876339</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,21 +2047,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465813</v>
+        <v>465823</v>
       </c>
       <c r="R15" t="n">
-        <v>6798394</v>
+        <v>6798111</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2128,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123876866</v>
+        <v>123877884</v>
       </c>
       <c r="B16" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2140,41 +2145,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465848</v>
+        <v>465816</v>
       </c>
       <c r="R16" t="n">
-        <v>6798245</v>
+        <v>6798323</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2208,7 +2213,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Nyare spillning.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2223,22 +2228,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123877175</v>
+        <v>123877240</v>
       </c>
       <c r="B17" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2251,37 +2256,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465790</v>
+        <v>465859</v>
       </c>
       <c r="R17" t="n">
-        <v>6798239</v>
+        <v>6798332</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2311,11 +2316,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2330,22 +2330,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123877850</v>
+        <v>123876733</v>
       </c>
       <c r="B18" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2358,21 +2358,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2382,10 +2382,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465863</v>
+        <v>465844</v>
       </c>
       <c r="R18" t="n">
-        <v>6798375</v>
+        <v>6798212</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2444,7 +2444,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123876775</v>
+        <v>123876521</v>
       </c>
       <c r="B19" t="n">
         <v>78788</v>
@@ -2484,13 +2484,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465799</v>
+        <v>465877</v>
       </c>
       <c r="R19" t="n">
-        <v>6798205</v>
+        <v>6798138</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2546,10 +2546,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123876521</v>
+        <v>123877850</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2562,21 +2562,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2586,13 +2586,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465877</v>
+        <v>465863</v>
       </c>
       <c r="R20" t="n">
-        <v>6798138</v>
+        <v>6798375</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2636,22 +2636,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123876845</v>
+        <v>123878888</v>
       </c>
       <c r="B21" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2664,37 +2664,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465832</v>
+        <v>465907</v>
       </c>
       <c r="R21" t="n">
-        <v>6798231</v>
+        <v>6798419</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2724,6 +2724,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Garnlav i synfältet, 30 meter i radie. Miljöbilder</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2738,19 +2743,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123877433</v>
+        <v>123876157</v>
       </c>
       <c r="B22" t="n">
         <v>78788</v>
@@ -2790,10 +2795,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465854</v>
+        <v>465822</v>
       </c>
       <c r="R22" t="n">
-        <v>6798343</v>
+        <v>6798106</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2852,7 +2857,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123878561</v>
+        <v>123877433</v>
       </c>
       <c r="B23" t="n">
         <v>78788</v>
@@ -2892,10 +2897,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465804</v>
+        <v>465854</v>
       </c>
       <c r="R23" t="n">
-        <v>6798478</v>
+        <v>6798343</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2954,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123877138</v>
+        <v>123877481</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2970,37 +2975,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465846</v>
+        <v>465807</v>
       </c>
       <c r="R24" t="n">
-        <v>6798341</v>
+        <v>6798288</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3044,19 +3054,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123876586</v>
+        <v>123878104</v>
       </c>
       <c r="B25" t="n">
         <v>78788</v>
@@ -3096,13 +3106,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465848</v>
+        <v>465803</v>
       </c>
       <c r="R25" t="n">
-        <v>6798129</v>
+        <v>6798395</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3146,19 +3156,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123876656</v>
+        <v>123876775</v>
       </c>
       <c r="B26" t="n">
         <v>78788</v>
@@ -3198,13 +3208,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465833</v>
+        <v>465799</v>
       </c>
       <c r="R26" t="n">
-        <v>6798204</v>
+        <v>6798205</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3248,19 +3258,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123878888</v>
+        <v>123876291</v>
       </c>
       <c r="B27" t="n">
         <v>78788</v>
@@ -3296,17 +3306,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465907</v>
+        <v>465806</v>
       </c>
       <c r="R27" t="n">
-        <v>6798419</v>
+        <v>6798100</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3336,11 +3346,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Garnlav i synfältet, 30 meter i radie. Miljöbilder</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3355,19 +3360,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123877248</v>
+        <v>123876656</v>
       </c>
       <c r="B28" t="n">
         <v>78788</v>
@@ -3403,14 +3408,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465799</v>
+        <v>465833</v>
       </c>
       <c r="R28" t="n">
-        <v>6798259</v>
+        <v>6798204</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3445,11 +3450,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3462,19 +3462,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123877370</v>
+        <v>123877138</v>
       </c>
       <c r="B29" t="n">
         <v>78788</v>
@@ -3514,10 +3514,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465830</v>
+        <v>465846</v>
       </c>
       <c r="R29" t="n">
-        <v>6798388</v>
+        <v>6798341</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3576,7 +3576,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123876157</v>
+        <v>123877582</v>
       </c>
       <c r="B30" t="n">
         <v>78788</v>
@@ -3616,10 +3616,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465822</v>
+        <v>465745</v>
       </c>
       <c r="R30" t="n">
-        <v>6798106</v>
+        <v>6798476</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3780,7 +3780,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123878630</v>
+        <v>123877370</v>
       </c>
       <c r="B32" t="n">
         <v>78788</v>
@@ -3816,17 +3816,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>465884</v>
+        <v>465830</v>
       </c>
       <c r="R32" t="n">
-        <v>6798405</v>
+        <v>6798388</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3856,11 +3856,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3875,19 +3870,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123876733</v>
+        <v>123878561</v>
       </c>
       <c r="B33" t="n">
         <v>78788</v>
@@ -3927,10 +3922,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465844</v>
+        <v>465804</v>
       </c>
       <c r="R33" t="n">
-        <v>6798212</v>
+        <v>6798478</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3989,10 +3984,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123877017</v>
+        <v>123876845</v>
       </c>
       <c r="B34" t="n">
-        <v>79377</v>
+        <v>78820</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4005,37 +4000,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>465805</v>
+        <v>465832</v>
       </c>
       <c r="R34" t="n">
-        <v>6798194</v>
+        <v>6798231</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4065,11 +4060,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4084,22 +4074,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123876143</v>
+        <v>123876866</v>
       </c>
       <c r="B35" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4108,25 +4098,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4136,10 +4126,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465821</v>
+        <v>465848</v>
       </c>
       <c r="R35" t="n">
-        <v>6798095</v>
+        <v>6798245</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4172,6 +4162,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Nyare spillning.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4198,10 +4193,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123877582</v>
+        <v>123876786</v>
       </c>
       <c r="B36" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4214,21 +4209,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4238,10 +4233,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465745</v>
+        <v>465862</v>
       </c>
       <c r="R36" t="n">
-        <v>6798476</v>
+        <v>6798219</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4300,7 +4295,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123878104</v>
+        <v>123876586</v>
       </c>
       <c r="B37" t="n">
         <v>78788</v>
@@ -4340,13 +4335,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465803</v>
+        <v>465848</v>
       </c>
       <c r="R37" t="n">
-        <v>6798395</v>
+        <v>6798129</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4390,22 +4385,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123877240</v>
+        <v>123877175</v>
       </c>
       <c r="B38" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4418,37 +4413,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465859</v>
+        <v>465790</v>
       </c>
       <c r="R38" t="n">
-        <v>6798332</v>
+        <v>6798239</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4478,6 +4473,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4492,22 +4492,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123913251</v>
+        <v>123913432</v>
       </c>
       <c r="B39" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4520,21 +4520,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465775</v>
+        <v>465943</v>
       </c>
       <c r="R39" t="n">
-        <v>6798229</v>
+        <v>6798495</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4606,10 +4606,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123913258</v>
+        <v>123913280</v>
       </c>
       <c r="B40" t="n">
-        <v>74879</v>
+        <v>78820</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4622,21 +4622,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4646,10 +4646,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465915</v>
+        <v>465753</v>
       </c>
       <c r="R40" t="n">
-        <v>6798548</v>
+        <v>6798400</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4708,7 +4708,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123913482</v>
+        <v>123913480</v>
       </c>
       <c r="B41" t="n">
         <v>78788</v>
@@ -4748,10 +4748,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>465693</v>
+        <v>465696</v>
       </c>
       <c r="R41" t="n">
-        <v>6798461</v>
+        <v>6798479</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4810,10 +4810,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123913271</v>
+        <v>123913475</v>
       </c>
       <c r="B42" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4826,21 +4826,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>465720</v>
+        <v>465719</v>
       </c>
       <c r="R42" t="n">
-        <v>6798523</v>
+        <v>6798495</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4912,7 +4912,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123913423</v>
+        <v>123913458</v>
       </c>
       <c r="B43" t="n">
         <v>78788</v>
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465920</v>
+        <v>465826</v>
       </c>
       <c r="R43" t="n">
-        <v>6798445</v>
+        <v>6798611</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5014,10 +5014,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123913244</v>
+        <v>123913434</v>
       </c>
       <c r="B44" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465933</v>
+        <v>465938</v>
       </c>
       <c r="R44" t="n">
-        <v>6798458</v>
+        <v>6798529</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5116,7 +5116,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123913530</v>
+        <v>123913450</v>
       </c>
       <c r="B45" t="n">
         <v>78788</v>
@@ -5156,10 +5156,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465883</v>
+        <v>465835</v>
       </c>
       <c r="R45" t="n">
-        <v>6798119</v>
+        <v>6798579</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5218,10 +5218,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123913581</v>
+        <v>123913313</v>
       </c>
       <c r="B46" t="n">
-        <v>5176</v>
+        <v>78820</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5230,43 +5230,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465737</v>
+        <v>465883</v>
       </c>
       <c r="R46" t="n">
-        <v>6798286</v>
+        <v>6798119</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5318,17 +5313,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123913287</v>
+        <v>123913490</v>
       </c>
       <c r="B47" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5341,21 +5336,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5365,10 +5360,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465786</v>
+        <v>465741</v>
       </c>
       <c r="R47" t="n">
-        <v>6798207</v>
+        <v>6798376</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5427,10 +5422,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123913309</v>
+        <v>123913368</v>
       </c>
       <c r="B48" t="n">
-        <v>78820</v>
+        <v>78525</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5443,21 +5438,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5467,10 +5462,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>465845</v>
+        <v>465859</v>
       </c>
       <c r="R48" t="n">
-        <v>6798127</v>
+        <v>6798098</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5529,10 +5524,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123913285</v>
+        <v>123913522</v>
       </c>
       <c r="B49" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5545,21 +5540,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,10 +5564,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>465735</v>
+        <v>465842</v>
       </c>
       <c r="R49" t="n">
-        <v>6798291</v>
+        <v>6798113</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5631,7 +5626,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123913453</v>
+        <v>123913500</v>
       </c>
       <c r="B50" t="n">
         <v>78788</v>
@@ -5671,10 +5666,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>465833</v>
+        <v>465780</v>
       </c>
       <c r="R50" t="n">
-        <v>6798603</v>
+        <v>6798219</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5733,7 +5728,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123913522</v>
+        <v>123913430</v>
       </c>
       <c r="B51" t="n">
         <v>78788</v>
@@ -5773,10 +5768,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>465842</v>
+        <v>465947</v>
       </c>
       <c r="R51" t="n">
-        <v>6798113</v>
+        <v>6798479</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5947,7 +5942,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123913532</v>
+        <v>123913489</v>
       </c>
       <c r="B53" t="n">
         <v>78788</v>
@@ -5987,10 +5982,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>465912</v>
+        <v>465753</v>
       </c>
       <c r="R53" t="n">
-        <v>6798108</v>
+        <v>6798400</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6049,10 +6044,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123913330</v>
+        <v>123913439</v>
       </c>
       <c r="B54" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6065,21 +6060,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6089,10 +6084,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>465815</v>
+        <v>465919</v>
       </c>
       <c r="R54" t="n">
-        <v>6798097</v>
+        <v>6798535</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6151,10 +6146,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123913462</v>
+        <v>123913279</v>
       </c>
       <c r="B55" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6167,21 +6162,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6191,10 +6186,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>465782</v>
+        <v>465720</v>
       </c>
       <c r="R55" t="n">
-        <v>6798650</v>
+        <v>6798411</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6253,10 +6248,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123913307</v>
+        <v>123913260</v>
       </c>
       <c r="B56" t="n">
-        <v>78820</v>
+        <v>74879</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6269,21 +6264,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6293,10 +6288,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>465884</v>
+        <v>465830</v>
       </c>
       <c r="R56" t="n">
-        <v>6798130</v>
+        <v>6798623</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6355,10 +6350,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123913368</v>
+        <v>123913482</v>
       </c>
       <c r="B57" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6371,21 +6366,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6395,10 +6390,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>465859</v>
+        <v>465693</v>
       </c>
       <c r="R57" t="n">
-        <v>6798098</v>
+        <v>6798461</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6457,7 +6452,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123913515</v>
+        <v>123913451</v>
       </c>
       <c r="B58" t="n">
         <v>78788</v>
@@ -6497,10 +6492,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>465825</v>
+        <v>465838</v>
       </c>
       <c r="R58" t="n">
-        <v>6798086</v>
+        <v>6798591</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6559,10 +6554,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123913448</v>
+        <v>123913274</v>
       </c>
       <c r="B59" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6575,21 +6570,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6599,10 +6594,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>465839</v>
+        <v>465705</v>
       </c>
       <c r="R59" t="n">
-        <v>6798559</v>
+        <v>6798509</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6661,10 +6656,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123913475</v>
+        <v>123913306</v>
       </c>
       <c r="B60" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6677,21 +6672,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6701,10 +6696,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>465719</v>
+        <v>465841</v>
       </c>
       <c r="R60" t="n">
-        <v>6798495</v>
+        <v>6798109</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6763,7 +6758,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123913439</v>
+        <v>123913504</v>
       </c>
       <c r="B61" t="n">
         <v>78788</v>
@@ -6803,10 +6798,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>465919</v>
+        <v>465787</v>
       </c>
       <c r="R61" t="n">
-        <v>6798535</v>
+        <v>6798158</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6865,10 +6860,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123913262</v>
+        <v>123913532</v>
       </c>
       <c r="B62" t="n">
-        <v>74879</v>
+        <v>78788</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6881,21 +6876,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6905,10 +6900,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>465764</v>
+        <v>465912</v>
       </c>
       <c r="R62" t="n">
-        <v>6798656</v>
+        <v>6798108</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6967,10 +6962,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123913438</v>
+        <v>123913323</v>
       </c>
       <c r="B63" t="n">
-        <v>78788</v>
+        <v>90955</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6979,25 +6974,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7007,10 +7002,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465904</v>
+        <v>465849</v>
       </c>
       <c r="R63" t="n">
-        <v>6798521</v>
+        <v>6798130</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7069,7 +7064,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123913496</v>
+        <v>123913453</v>
       </c>
       <c r="B64" t="n">
         <v>78788</v>
@@ -7109,10 +7104,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>465749</v>
+        <v>465833</v>
       </c>
       <c r="R64" t="n">
-        <v>6798268</v>
+        <v>6798603</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7171,10 +7166,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123913500</v>
+        <v>123913249</v>
       </c>
       <c r="B65" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7187,21 +7182,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7211,10 +7206,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465780</v>
+        <v>465757</v>
       </c>
       <c r="R65" t="n">
-        <v>6798219</v>
+        <v>6798402</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7273,7 +7268,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123913477</v>
+        <v>123913436</v>
       </c>
       <c r="B66" t="n">
         <v>78788</v>
@@ -7313,10 +7308,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465708</v>
+        <v>465927</v>
       </c>
       <c r="R66" t="n">
-        <v>6798481</v>
+        <v>6798517</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7375,10 +7370,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123913502</v>
+        <v>123913330</v>
       </c>
       <c r="B67" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7391,21 +7386,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7415,10 +7410,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465783</v>
+        <v>465815</v>
       </c>
       <c r="R67" t="n">
-        <v>6798169</v>
+        <v>6798097</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7477,10 +7472,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123913289</v>
+        <v>123913496</v>
       </c>
       <c r="B68" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7493,21 +7488,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7517,10 +7512,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465786</v>
+        <v>465749</v>
       </c>
       <c r="R68" t="n">
-        <v>6798177</v>
+        <v>6798268</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7579,7 +7574,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123913525</v>
+        <v>123913443</v>
       </c>
       <c r="B69" t="n">
         <v>78788</v>
@@ -7619,10 +7614,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465837</v>
+        <v>465863</v>
       </c>
       <c r="R69" t="n">
-        <v>6798100</v>
+        <v>6798532</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7681,7 +7676,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123913492</v>
+        <v>123913448</v>
       </c>
       <c r="B70" t="n">
         <v>78788</v>
@@ -7721,10 +7716,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>465749</v>
+        <v>465839</v>
       </c>
       <c r="R70" t="n">
-        <v>6798363</v>
+        <v>6798559</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7783,7 +7778,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123913485</v>
+        <v>123913498</v>
       </c>
       <c r="B71" t="n">
         <v>78788</v>
@@ -7823,10 +7818,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465709</v>
+        <v>465746</v>
       </c>
       <c r="R71" t="n">
-        <v>6798426</v>
+        <v>6798258</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7885,10 +7880,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123913451</v>
+        <v>123913339</v>
       </c>
       <c r="B72" t="n">
-        <v>78788</v>
+        <v>57644</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7901,21 +7896,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7925,10 +7920,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>465838</v>
+        <v>465825</v>
       </c>
       <c r="R72" t="n">
-        <v>6798591</v>
+        <v>6798086</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7987,10 +7982,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123913443</v>
+        <v>123913327</v>
       </c>
       <c r="B73" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8003,21 +7998,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8027,10 +8022,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>465863</v>
+        <v>465779</v>
       </c>
       <c r="R73" t="n">
-        <v>6798532</v>
+        <v>6798140</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8089,10 +8084,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123913374</v>
+        <v>123913572</v>
       </c>
       <c r="B74" t="n">
-        <v>80741</v>
+        <v>78433</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8105,21 +8100,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8129,10 +8124,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>465857</v>
+        <v>465778</v>
       </c>
       <c r="R74" t="n">
-        <v>6798531</v>
+        <v>6798141</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8184,17 +8179,17 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123913458</v>
+        <v>123913309</v>
       </c>
       <c r="B75" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8207,21 +8202,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8231,10 +8226,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>465826</v>
+        <v>465845</v>
       </c>
       <c r="R75" t="n">
-        <v>6798611</v>
+        <v>6798127</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8293,10 +8288,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123913291</v>
+        <v>123913374</v>
       </c>
       <c r="B76" t="n">
-        <v>78820</v>
+        <v>80741</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8309,21 +8304,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8333,10 +8328,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>465775</v>
+        <v>465857</v>
       </c>
       <c r="R76" t="n">
-        <v>6798148</v>
+        <v>6798531</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8395,10 +8390,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123913249</v>
+        <v>123913307</v>
       </c>
       <c r="B77" t="n">
-        <v>79406</v>
+        <v>78820</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8411,21 +8406,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8435,10 +8430,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>465757</v>
+        <v>465884</v>
       </c>
       <c r="R77" t="n">
-        <v>6798402</v>
+        <v>6798130</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8497,10 +8492,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123913472</v>
+        <v>123913262</v>
       </c>
       <c r="B78" t="n">
-        <v>78788</v>
+        <v>74879</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8513,21 +8508,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8537,10 +8532,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>465710</v>
+        <v>465764</v>
       </c>
       <c r="R78" t="n">
-        <v>6798561</v>
+        <v>6798656</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8599,10 +8594,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123913317</v>
+        <v>123913462</v>
       </c>
       <c r="B79" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8615,21 +8610,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8639,10 +8634,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>465913</v>
+        <v>465782</v>
       </c>
       <c r="R79" t="n">
-        <v>6798106</v>
+        <v>6798650</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8701,10 +8696,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123913260</v>
+        <v>123913315</v>
       </c>
       <c r="B80" t="n">
-        <v>74879</v>
+        <v>78820</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8717,21 +8712,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8741,10 +8736,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>465830</v>
+        <v>465899</v>
       </c>
       <c r="R80" t="n">
-        <v>6798623</v>
+        <v>6798123</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8803,7 +8798,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123876771</v>
+        <v>123913517</v>
       </c>
       <c r="B81" t="n">
         <v>78788</v>
@@ -8843,10 +8838,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>465815</v>
+        <v>465837</v>
       </c>
       <c r="R81" t="n">
-        <v>6798172</v>
+        <v>6798096</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8881,11 +8876,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Garnlav bakom björnide, samt i en radie av ca 30 meter.  Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -8898,22 +8888,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123913269</v>
+        <v>123913446</v>
       </c>
       <c r="B82" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8926,21 +8916,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8950,10 +8940,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>465705</v>
+        <v>465875</v>
       </c>
       <c r="R82" t="n">
-        <v>6798564</v>
+        <v>6798559</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9012,10 +9002,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123913483</v>
+        <v>123913406</v>
       </c>
       <c r="B83" t="n">
-        <v>78788</v>
+        <v>91150</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9024,25 +9014,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9052,10 +9042,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>465694</v>
+        <v>465872</v>
       </c>
       <c r="R83" t="n">
-        <v>6798446</v>
+        <v>6798093</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9114,10 +9104,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123913247</v>
+        <v>123913277</v>
       </c>
       <c r="B84" t="n">
-        <v>79406</v>
+        <v>78820</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9130,21 +9120,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9154,10 +9144,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>465707</v>
+        <v>465709</v>
       </c>
       <c r="R84" t="n">
-        <v>6798475</v>
+        <v>6798426</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9216,10 +9206,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123913268</v>
+        <v>123913426</v>
       </c>
       <c r="B85" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9232,21 +9222,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9256,10 +9246,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>465767</v>
+        <v>465923</v>
       </c>
       <c r="R85" t="n">
-        <v>6798617</v>
+        <v>6798451</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9318,10 +9308,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123913339</v>
+        <v>123913423</v>
       </c>
       <c r="B86" t="n">
-        <v>57644</v>
+        <v>78788</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9334,21 +9324,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9358,10 +9348,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>465825</v>
+        <v>465920</v>
       </c>
       <c r="R86" t="n">
-        <v>6798086</v>
+        <v>6798445</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9420,10 +9410,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123913426</v>
+        <v>123913268</v>
       </c>
       <c r="B87" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9436,21 +9426,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9460,10 +9450,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>465923</v>
+        <v>465767</v>
       </c>
       <c r="R87" t="n">
-        <v>6798451</v>
+        <v>6798617</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9522,10 +9512,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123913313</v>
+        <v>123913470</v>
       </c>
       <c r="B88" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9538,21 +9528,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9562,10 +9552,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>465883</v>
+        <v>465726</v>
       </c>
       <c r="R88" t="n">
-        <v>6798119</v>
+        <v>6798570</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9624,10 +9614,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123913256</v>
+        <v>123913291</v>
       </c>
       <c r="B89" t="n">
-        <v>74879</v>
+        <v>78820</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9640,21 +9630,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9664,10 +9654,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>465939</v>
+        <v>465775</v>
       </c>
       <c r="R89" t="n">
-        <v>6798534</v>
+        <v>6798148</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9726,7 +9716,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123913277</v>
+        <v>123913266</v>
       </c>
       <c r="B90" t="n">
         <v>78820</v>
@@ -9766,10 +9756,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>465709</v>
+        <v>465839</v>
       </c>
       <c r="R90" t="n">
-        <v>6798426</v>
+        <v>6798559</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9828,7 +9818,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123913527</v>
+        <v>123913485</v>
       </c>
       <c r="B91" t="n">
         <v>78788</v>
@@ -9868,10 +9858,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>465878</v>
+        <v>465709</v>
       </c>
       <c r="R91" t="n">
-        <v>6798095</v>
+        <v>6798426</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9930,10 +9920,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123913406</v>
+        <v>123913311</v>
       </c>
       <c r="B92" t="n">
-        <v>91150</v>
+        <v>78820</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9942,25 +9932,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1503</v>
+        <v>185</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9970,10 +9960,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>465872</v>
+        <v>465842</v>
       </c>
       <c r="R92" t="n">
-        <v>6798093</v>
+        <v>6798116</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10032,10 +10022,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123913430</v>
+        <v>123913282</v>
       </c>
       <c r="B93" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10048,21 +10038,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10072,10 +10062,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>465947</v>
+        <v>465748</v>
       </c>
       <c r="R93" t="n">
-        <v>6798479</v>
+        <v>6798396</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10134,7 +10124,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123913504</v>
+        <v>123913519</v>
       </c>
       <c r="B94" t="n">
         <v>78788</v>
@@ -10174,10 +10164,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>465787</v>
+        <v>465865</v>
       </c>
       <c r="R94" t="n">
-        <v>6798158</v>
+        <v>6798133</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10236,10 +10226,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123913334</v>
+        <v>123913464</v>
       </c>
       <c r="B95" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10252,21 +10242,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10276,10 +10266,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>465933</v>
+        <v>465767</v>
       </c>
       <c r="R95" t="n">
-        <v>6798526</v>
+        <v>6798617</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10338,7 +10328,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123913266</v>
+        <v>123913276</v>
       </c>
       <c r="B96" t="n">
         <v>78820</v>
@@ -10378,10 +10368,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>465839</v>
+        <v>465694</v>
       </c>
       <c r="R96" t="n">
-        <v>6798559</v>
+        <v>6798446</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10440,10 +10430,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123913280</v>
+        <v>123913527</v>
       </c>
       <c r="B97" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10456,21 +10446,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10480,10 +10470,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>465753</v>
+        <v>465878</v>
       </c>
       <c r="R97" t="n">
-        <v>6798400</v>
+        <v>6798095</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10542,7 +10532,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123913446</v>
+        <v>123913502</v>
       </c>
       <c r="B98" t="n">
         <v>78788</v>
@@ -10582,10 +10572,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>465875</v>
+        <v>465783</v>
       </c>
       <c r="R98" t="n">
-        <v>6798559</v>
+        <v>6798169</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10644,10 +10634,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123913276</v>
+        <v>123913487</v>
       </c>
       <c r="B99" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10660,21 +10650,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10684,10 +10674,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>465694</v>
+        <v>465720</v>
       </c>
       <c r="R99" t="n">
-        <v>6798446</v>
+        <v>6798411</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10746,7 +10736,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123913494</v>
+        <v>123913492</v>
       </c>
       <c r="B100" t="n">
         <v>78788</v>
@@ -10786,10 +10776,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>465741</v>
+        <v>465749</v>
       </c>
       <c r="R100" t="n">
-        <v>6798286</v>
+        <v>6798363</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10848,7 +10838,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123913519</v>
+        <v>123913472</v>
       </c>
       <c r="B101" t="n">
         <v>78788</v>
@@ -10888,10 +10878,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>465865</v>
+        <v>465710</v>
       </c>
       <c r="R101" t="n">
-        <v>6798133</v>
+        <v>6798561</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10950,10 +10940,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123913464</v>
+        <v>123913247</v>
       </c>
       <c r="B102" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10966,21 +10956,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10990,10 +10980,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>465767</v>
+        <v>465707</v>
       </c>
       <c r="R102" t="n">
-        <v>6798617</v>
+        <v>6798475</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11052,10 +11042,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123913460</v>
+        <v>123913287</v>
       </c>
       <c r="B103" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11068,21 +11058,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11092,10 +11082,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>465809</v>
+        <v>465786</v>
       </c>
       <c r="R103" t="n">
-        <v>6798627</v>
+        <v>6798207</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11154,7 +11144,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>123913434</v>
+        <v>123913438</v>
       </c>
       <c r="B104" t="n">
         <v>78788</v>
@@ -11194,10 +11184,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>465938</v>
+        <v>465904</v>
       </c>
       <c r="R104" t="n">
-        <v>6798529</v>
+        <v>6798521</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11256,7 +11246,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123913487</v>
+        <v>123913525</v>
       </c>
       <c r="B105" t="n">
         <v>78788</v>
@@ -11296,10 +11286,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>465720</v>
+        <v>465837</v>
       </c>
       <c r="R105" t="n">
-        <v>6798411</v>
+        <v>6798100</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11358,7 +11348,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123913450</v>
+        <v>123913473</v>
       </c>
       <c r="B106" t="n">
         <v>78788</v>
@@ -11398,10 +11388,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>465835</v>
+        <v>465720</v>
       </c>
       <c r="R106" t="n">
-        <v>6798579</v>
+        <v>6798523</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11460,10 +11450,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123913315</v>
+        <v>123913256</v>
       </c>
       <c r="B107" t="n">
-        <v>78820</v>
+        <v>74879</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11476,21 +11466,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11500,10 +11490,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>465899</v>
+        <v>465939</v>
       </c>
       <c r="R107" t="n">
-        <v>6798123</v>
+        <v>6798534</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11562,10 +11552,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123913327</v>
+        <v>123913530</v>
       </c>
       <c r="B108" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11578,21 +11568,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11602,10 +11592,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>465779</v>
+        <v>465883</v>
       </c>
       <c r="R108" t="n">
-        <v>6798140</v>
+        <v>6798119</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11664,10 +11654,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123913498</v>
+        <v>123913269</v>
       </c>
       <c r="B109" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11680,21 +11670,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11704,10 +11694,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>465746</v>
+        <v>465705</v>
       </c>
       <c r="R109" t="n">
-        <v>6798258</v>
+        <v>6798564</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11766,10 +11756,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123913323</v>
+        <v>123913317</v>
       </c>
       <c r="B110" t="n">
-        <v>90955</v>
+        <v>78820</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11778,25 +11768,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11806,10 +11796,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>465849</v>
+        <v>465913</v>
       </c>
       <c r="R110" t="n">
-        <v>6798130</v>
+        <v>6798106</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11868,7 +11858,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123913517</v>
+        <v>123913477</v>
       </c>
       <c r="B111" t="n">
         <v>78788</v>
@@ -11908,10 +11898,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>465837</v>
+        <v>465708</v>
       </c>
       <c r="R111" t="n">
-        <v>6798096</v>
+        <v>6798481</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11970,7 +11960,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123913311</v>
+        <v>123913271</v>
       </c>
       <c r="B112" t="n">
         <v>78820</v>
@@ -12010,10 +12000,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>465842</v>
+        <v>465720</v>
       </c>
       <c r="R112" t="n">
-        <v>6798116</v>
+        <v>6798523</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12072,10 +12062,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>123913490</v>
+        <v>123913251</v>
       </c>
       <c r="B113" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12088,21 +12078,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12112,10 +12102,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>465741</v>
+        <v>465775</v>
       </c>
       <c r="R113" t="n">
-        <v>6798376</v>
+        <v>6798229</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12174,10 +12164,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123913279</v>
+        <v>123913460</v>
       </c>
       <c r="B114" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12190,21 +12180,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12214,10 +12204,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>465720</v>
+        <v>465809</v>
       </c>
       <c r="R114" t="n">
-        <v>6798411</v>
+        <v>6798627</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12276,10 +12266,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123913432</v>
+        <v>123913285</v>
       </c>
       <c r="B115" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12292,21 +12282,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12316,10 +12306,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>465943</v>
+        <v>465735</v>
       </c>
       <c r="R115" t="n">
-        <v>6798495</v>
+        <v>6798291</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12378,10 +12368,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123913489</v>
+        <v>123913258</v>
       </c>
       <c r="B116" t="n">
-        <v>78788</v>
+        <v>74879</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12394,21 +12384,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12418,10 +12408,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>465753</v>
+        <v>465915</v>
       </c>
       <c r="R116" t="n">
-        <v>6798400</v>
+        <v>6798548</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12480,7 +12470,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123913470</v>
+        <v>123876771</v>
       </c>
       <c r="B117" t="n">
         <v>78788</v>
@@ -12520,10 +12510,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>465726</v>
+        <v>465815</v>
       </c>
       <c r="R117" t="n">
-        <v>6798570</v>
+        <v>6798172</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12558,6 +12548,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Garnlav bakom björnide, samt i en radie av ca 30 meter.  Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -12570,19 +12565,19 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123913473</v>
+        <v>123913494</v>
       </c>
       <c r="B118" t="n">
         <v>78788</v>
@@ -12622,10 +12617,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>465720</v>
+        <v>465741</v>
       </c>
       <c r="R118" t="n">
-        <v>6798523</v>
+        <v>6798286</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12684,10 +12679,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123913436</v>
+        <v>123913289</v>
       </c>
       <c r="B119" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12700,21 +12695,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12724,10 +12719,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>465927</v>
+        <v>465786</v>
       </c>
       <c r="R119" t="n">
-        <v>6798517</v>
+        <v>6798177</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12786,10 +12781,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>123913282</v>
+        <v>123913441</v>
       </c>
       <c r="B120" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12802,21 +12797,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12826,10 +12821,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>465748</v>
+        <v>465893</v>
       </c>
       <c r="R120" t="n">
-        <v>6798396</v>
+        <v>6798543</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12888,10 +12883,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123913441</v>
+        <v>123913334</v>
       </c>
       <c r="B121" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12904,21 +12899,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12928,10 +12923,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>465893</v>
+        <v>465933</v>
       </c>
       <c r="R121" t="n">
-        <v>6798543</v>
+        <v>6798526</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12990,10 +12985,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123913274</v>
+        <v>123913483</v>
       </c>
       <c r="B122" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13006,21 +13001,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13030,10 +13025,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>465705</v>
+        <v>465694</v>
       </c>
       <c r="R122" t="n">
-        <v>6798509</v>
+        <v>6798446</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13092,10 +13087,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123913572</v>
+        <v>123913515</v>
       </c>
       <c r="B123" t="n">
-        <v>78433</v>
+        <v>78788</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13108,21 +13103,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13132,10 +13127,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>465778</v>
+        <v>465825</v>
       </c>
       <c r="R123" t="n">
-        <v>6798141</v>
+        <v>6798086</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13187,17 +13182,17 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123913480</v>
+        <v>123913244</v>
       </c>
       <c r="B124" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13210,21 +13205,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13234,10 +13229,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>465696</v>
+        <v>465933</v>
       </c>
       <c r="R124" t="n">
-        <v>6798479</v>
+        <v>6798458</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13296,10 +13291,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>123913306</v>
+        <v>123913581</v>
       </c>
       <c r="B125" t="n">
-        <v>78820</v>
+        <v>5176</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13308,38 +13303,43 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>465841</v>
+        <v>465737</v>
       </c>
       <c r="R125" t="n">
-        <v>6798109</v>
+        <v>6798286</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>

--- a/artfynd/A 15853-2025 artfynd.xlsx
+++ b/artfynd/A 15853-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123878436</v>
+        <v>123878365</v>
       </c>
       <c r="B2" t="n">
         <v>78788</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465800</v>
+        <v>465783</v>
       </c>
       <c r="R2" t="n">
-        <v>6798391</v>
+        <v>6798386</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Garnlav synligt ca 30 meters radie. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123876143</v>
+        <v>123876339</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465821</v>
+        <v>465823</v>
       </c>
       <c r="R3" t="n">
-        <v>6798095</v>
+        <v>6798111</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123876878</v>
+        <v>123877582</v>
       </c>
       <c r="B4" t="n">
         <v>78788</v>
@@ -924,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465833</v>
+        <v>465745</v>
       </c>
       <c r="R4" t="n">
-        <v>6798269</v>
+        <v>6798476</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123878923</v>
+        <v>123877175</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,37 +997,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465911</v>
+        <v>465790</v>
       </c>
       <c r="R5" t="n">
-        <v>6798461</v>
+        <v>6798239</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1062,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,19 +1076,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123876806</v>
+        <v>123877304</v>
       </c>
       <c r="B6" t="n">
         <v>78788</v>
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465847</v>
+        <v>465832</v>
       </c>
       <c r="R6" t="n">
-        <v>6798227</v>
+        <v>6798359</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123878630</v>
+        <v>123877138</v>
       </c>
       <c r="B7" t="n">
         <v>78788</v>
@@ -1226,17 +1226,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465884</v>
+        <v>465846</v>
       </c>
       <c r="R7" t="n">
-        <v>6798405</v>
+        <v>6798341</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1266,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,19 +1280,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123878210</v>
+        <v>123877240</v>
       </c>
       <c r="B8" t="n">
         <v>78788</v>
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465813</v>
+        <v>465859</v>
       </c>
       <c r="R8" t="n">
-        <v>6798394</v>
+        <v>6798332</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1399,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123878365</v>
+        <v>123876845</v>
       </c>
       <c r="B9" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465783</v>
+        <v>465832</v>
       </c>
       <c r="R9" t="n">
-        <v>6798386</v>
+        <v>6798231</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1501,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123877017</v>
+        <v>123876143</v>
       </c>
       <c r="B10" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,37 +1512,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465805</v>
+        <v>465821</v>
       </c>
       <c r="R10" t="n">
-        <v>6798194</v>
+        <v>6798095</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1577,11 +1572,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1596,19 +1586,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123877248</v>
+        <v>123877884</v>
       </c>
       <c r="B11" t="n">
         <v>78788</v>
@@ -1648,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465799</v>
+        <v>465816</v>
       </c>
       <c r="R11" t="n">
-        <v>6798259</v>
+        <v>6798323</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1705,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123877304</v>
+        <v>123878630</v>
       </c>
       <c r="B12" t="n">
         <v>78788</v>
@@ -1751,14 +1741,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465832</v>
+        <v>465884</v>
       </c>
       <c r="R12" t="n">
-        <v>6798359</v>
+        <v>6798405</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1793,6 +1783,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1805,22 +1800,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123877326</v>
+        <v>123876733</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,42 +1828,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465799</v>
+        <v>465844</v>
       </c>
       <c r="R13" t="n">
-        <v>6798259</v>
+        <v>6798212</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1898,11 +1888,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1917,22 +1902,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123876691</v>
+        <v>123878923</v>
       </c>
       <c r="B14" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1969,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465832</v>
+        <v>465911</v>
       </c>
       <c r="R14" t="n">
-        <v>6798208</v>
+        <v>6798461</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2031,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123876339</v>
+        <v>123878540</v>
       </c>
       <c r="B15" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2071,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465823</v>
+        <v>465797</v>
       </c>
       <c r="R15" t="n">
-        <v>6798111</v>
+        <v>6798473</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2133,7 +2118,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123877884</v>
+        <v>123878888</v>
       </c>
       <c r="B16" t="n">
         <v>78788</v>
@@ -2173,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465816</v>
+        <v>465907</v>
       </c>
       <c r="R16" t="n">
-        <v>6798323</v>
+        <v>6798419</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2213,7 +2198,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Garnlav i synfältet, 30 meter i radie. Miljöbilder</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2240,7 +2225,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123877240</v>
+        <v>123876806</v>
       </c>
       <c r="B17" t="n">
         <v>78788</v>
@@ -2280,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465859</v>
+        <v>465847</v>
       </c>
       <c r="R17" t="n">
-        <v>6798332</v>
+        <v>6798227</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2342,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123876733</v>
+        <v>123877481</v>
       </c>
       <c r="B18" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2358,37 +2343,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465844</v>
+        <v>465807</v>
       </c>
       <c r="R18" t="n">
-        <v>6798212</v>
+        <v>6798288</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2432,19 +2422,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123876521</v>
+        <v>123877370</v>
       </c>
       <c r="B19" t="n">
         <v>78788</v>
@@ -2484,13 +2474,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465877</v>
+        <v>465830</v>
       </c>
       <c r="R19" t="n">
-        <v>6798138</v>
+        <v>6798388</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2534,22 +2524,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123877850</v>
+        <v>123876586</v>
       </c>
       <c r="B20" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2562,37 +2552,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465863</v>
+        <v>465848</v>
       </c>
       <c r="R20" t="n">
-        <v>6798375</v>
+        <v>6798129</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2636,19 +2626,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123878888</v>
+        <v>123876656</v>
       </c>
       <c r="B21" t="n">
         <v>78788</v>
@@ -2684,14 +2674,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465907</v>
+        <v>465833</v>
       </c>
       <c r="R21" t="n">
-        <v>6798419</v>
+        <v>6798204</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2726,11 +2716,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Garnlav i synfältet, 30 meter i radie. Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2743,22 +2728,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123876157</v>
+        <v>123877850</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2771,21 +2756,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2795,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465822</v>
+        <v>465863</v>
       </c>
       <c r="R22" t="n">
-        <v>6798106</v>
+        <v>6798375</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2857,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123877433</v>
+        <v>123876786</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2873,21 +2858,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2897,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465854</v>
+        <v>465862</v>
       </c>
       <c r="R23" t="n">
-        <v>6798343</v>
+        <v>6798219</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2959,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123877481</v>
+        <v>123878561</v>
       </c>
       <c r="B24" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2975,42 +2960,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465807</v>
+        <v>465804</v>
       </c>
       <c r="R24" t="n">
-        <v>6798288</v>
+        <v>6798478</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3054,19 +3034,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123878104</v>
+        <v>123877248</v>
       </c>
       <c r="B25" t="n">
         <v>78788</v>
@@ -3106,13 +3086,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465803</v>
+        <v>465799</v>
       </c>
       <c r="R25" t="n">
-        <v>6798395</v>
+        <v>6798259</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3142,6 +3122,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3156,19 +3141,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123876775</v>
+        <v>123878436</v>
       </c>
       <c r="B26" t="n">
         <v>78788</v>
@@ -3204,17 +3189,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465799</v>
+        <v>465800</v>
       </c>
       <c r="R26" t="n">
-        <v>6798205</v>
+        <v>6798391</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3244,6 +3229,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Garnlav synligt ca 30 meters radie. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3258,22 +3248,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123876291</v>
+        <v>123876866</v>
       </c>
       <c r="B27" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3282,25 +3272,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3310,10 +3300,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465806</v>
+        <v>465848</v>
       </c>
       <c r="R27" t="n">
-        <v>6798100</v>
+        <v>6798245</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3346,6 +3336,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Nyare spillning.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3372,10 +3367,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123876656</v>
+        <v>123877017</v>
       </c>
       <c r="B28" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3388,34 +3383,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465833</v>
+        <v>465805</v>
       </c>
       <c r="R28" t="n">
-        <v>6798204</v>
+        <v>6798194</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3450,6 +3445,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3462,19 +3462,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123877138</v>
+        <v>123876878</v>
       </c>
       <c r="B29" t="n">
         <v>78788</v>
@@ -3514,13 +3514,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465846</v>
+        <v>465833</v>
       </c>
       <c r="R29" t="n">
-        <v>6798341</v>
+        <v>6798269</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3564,19 +3564,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123877582</v>
+        <v>123876291</v>
       </c>
       <c r="B30" t="n">
         <v>78788</v>
@@ -3616,10 +3616,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465745</v>
+        <v>465806</v>
       </c>
       <c r="R30" t="n">
-        <v>6798476</v>
+        <v>6798100</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123878540</v>
+        <v>123876521</v>
       </c>
       <c r="B31" t="n">
         <v>78788</v>
@@ -3718,13 +3718,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465797</v>
+        <v>465877</v>
       </c>
       <c r="R31" t="n">
-        <v>6798473</v>
+        <v>6798138</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3768,19 +3768,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123877370</v>
+        <v>123878210</v>
       </c>
       <c r="B32" t="n">
         <v>78788</v>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>465830</v>
+        <v>465813</v>
       </c>
       <c r="R32" t="n">
-        <v>6798388</v>
+        <v>6798394</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3882,7 +3882,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123878561</v>
+        <v>123876157</v>
       </c>
       <c r="B33" t="n">
         <v>78788</v>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465804</v>
+        <v>465822</v>
       </c>
       <c r="R33" t="n">
-        <v>6798478</v>
+        <v>6798106</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3984,7 +3984,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123876845</v>
+        <v>123876691</v>
       </c>
       <c r="B34" t="n">
         <v>78820</v>
@@ -4027,7 +4027,7 @@
         <v>465832</v>
       </c>
       <c r="R34" t="n">
-        <v>6798231</v>
+        <v>6798208</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4086,10 +4086,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123876866</v>
+        <v>123876775</v>
       </c>
       <c r="B35" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4098,25 +4098,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4126,13 +4126,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465848</v>
+        <v>465799</v>
       </c>
       <c r="R35" t="n">
-        <v>6798245</v>
+        <v>6798205</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4162,11 +4162,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Nyare spillning.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4181,22 +4176,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123876786</v>
+        <v>123878104</v>
       </c>
       <c r="B36" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4209,37 +4204,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465862</v>
+        <v>465803</v>
       </c>
       <c r="R36" t="n">
-        <v>6798219</v>
+        <v>6798395</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4283,19 +4278,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123876586</v>
+        <v>123877433</v>
       </c>
       <c r="B37" t="n">
         <v>78788</v>
@@ -4331,17 +4326,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465848</v>
+        <v>465854</v>
       </c>
       <c r="R37" t="n">
-        <v>6798129</v>
+        <v>6798343</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4385,22 +4380,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123877175</v>
+        <v>123877326</v>
       </c>
       <c r="B38" t="n">
-        <v>79377</v>
+        <v>57507</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4413,34 +4408,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465790</v>
+        <v>465799</v>
       </c>
       <c r="R38" t="n">
-        <v>6798239</v>
+        <v>6798259</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123913432</v>
+        <v>123913426</v>
       </c>
       <c r="B39" t="n">
         <v>78788</v>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465943</v>
+        <v>465923</v>
       </c>
       <c r="R39" t="n">
-        <v>6798495</v>
+        <v>6798451</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4606,10 +4606,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123913280</v>
+        <v>123913460</v>
       </c>
       <c r="B40" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4622,21 +4622,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4646,10 +4646,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465753</v>
+        <v>465809</v>
       </c>
       <c r="R40" t="n">
-        <v>6798400</v>
+        <v>6798627</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4708,10 +4708,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123913480</v>
+        <v>123913311</v>
       </c>
       <c r="B41" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4724,21 +4724,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4748,10 +4748,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>465696</v>
+        <v>465842</v>
       </c>
       <c r="R41" t="n">
-        <v>6798479</v>
+        <v>6798116</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4810,10 +4810,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123913475</v>
+        <v>123913406</v>
       </c>
       <c r="B42" t="n">
-        <v>78788</v>
+        <v>91150</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4822,25 +4822,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>465719</v>
+        <v>465872</v>
       </c>
       <c r="R42" t="n">
-        <v>6798495</v>
+        <v>6798093</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4912,7 +4912,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123913458</v>
+        <v>123876771</v>
       </c>
       <c r="B43" t="n">
         <v>78788</v>
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465826</v>
+        <v>465815</v>
       </c>
       <c r="R43" t="n">
-        <v>6798611</v>
+        <v>6798172</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4990,6 +4990,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Garnlav bakom björnide, samt i en radie av ca 30 meter.  Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5002,19 +5007,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123913434</v>
+        <v>123913451</v>
       </c>
       <c r="B44" t="n">
         <v>78788</v>
@@ -5054,10 +5059,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465938</v>
+        <v>465838</v>
       </c>
       <c r="R44" t="n">
-        <v>6798529</v>
+        <v>6798591</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5116,7 +5121,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123913450</v>
+        <v>123913434</v>
       </c>
       <c r="B45" t="n">
         <v>78788</v>
@@ -5156,10 +5161,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465835</v>
+        <v>465938</v>
       </c>
       <c r="R45" t="n">
-        <v>6798579</v>
+        <v>6798529</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5218,7 +5223,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123913313</v>
+        <v>123913269</v>
       </c>
       <c r="B46" t="n">
         <v>78820</v>
@@ -5258,10 +5263,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465883</v>
+        <v>465705</v>
       </c>
       <c r="R46" t="n">
-        <v>6798119</v>
+        <v>6798564</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5320,10 +5325,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123913490</v>
+        <v>123913315</v>
       </c>
       <c r="B47" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5336,21 +5341,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5360,10 +5365,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465741</v>
+        <v>465899</v>
       </c>
       <c r="R47" t="n">
-        <v>6798376</v>
+        <v>6798123</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5422,10 +5427,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123913368</v>
+        <v>123913443</v>
       </c>
       <c r="B48" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5438,21 +5443,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5462,10 +5467,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>465859</v>
+        <v>465863</v>
       </c>
       <c r="R48" t="n">
-        <v>6798098</v>
+        <v>6798532</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5524,7 +5529,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123913522</v>
+        <v>123913438</v>
       </c>
       <c r="B49" t="n">
         <v>78788</v>
@@ -5564,10 +5569,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>465842</v>
+        <v>465904</v>
       </c>
       <c r="R49" t="n">
-        <v>6798113</v>
+        <v>6798521</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5626,7 +5631,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123913500</v>
+        <v>123913448</v>
       </c>
       <c r="B50" t="n">
         <v>78788</v>
@@ -5666,10 +5671,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>465780</v>
+        <v>465839</v>
       </c>
       <c r="R50" t="n">
-        <v>6798219</v>
+        <v>6798559</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5728,7 +5733,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123913430</v>
+        <v>123913502</v>
       </c>
       <c r="B51" t="n">
         <v>78788</v>
@@ -5768,10 +5773,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>465947</v>
+        <v>465783</v>
       </c>
       <c r="R51" t="n">
-        <v>6798479</v>
+        <v>6798169</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5830,10 +5835,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123913564</v>
+        <v>123913519</v>
       </c>
       <c r="B52" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5846,39 +5851,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>465737</v>
+        <v>465865</v>
       </c>
       <c r="R52" t="n">
-        <v>6798286</v>
+        <v>6798133</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5913,11 +5913,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Spår efter födosök</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5935,14 +5930,14 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123913489</v>
+        <v>123913432</v>
       </c>
       <c r="B53" t="n">
         <v>78788</v>
@@ -5982,10 +5977,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>465753</v>
+        <v>465943</v>
       </c>
       <c r="R53" t="n">
-        <v>6798400</v>
+        <v>6798495</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6044,10 +6039,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123913439</v>
+        <v>123913249</v>
       </c>
       <c r="B54" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6060,21 +6055,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6084,10 +6079,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>465919</v>
+        <v>465757</v>
       </c>
       <c r="R54" t="n">
-        <v>6798535</v>
+        <v>6798402</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6146,10 +6141,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123913279</v>
+        <v>123913564</v>
       </c>
       <c r="B55" t="n">
-        <v>78820</v>
+        <v>57491</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6162,34 +6157,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>465720</v>
+        <v>465737</v>
       </c>
       <c r="R55" t="n">
-        <v>6798411</v>
+        <v>6798286</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6224,6 +6224,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Spår efter födosök</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6241,17 +6246,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123913260</v>
+        <v>123913307</v>
       </c>
       <c r="B56" t="n">
-        <v>74879</v>
+        <v>78820</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6264,21 +6269,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6288,10 +6293,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>465830</v>
+        <v>465884</v>
       </c>
       <c r="R56" t="n">
-        <v>6798623</v>
+        <v>6798130</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6350,7 +6355,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123913482</v>
+        <v>123913487</v>
       </c>
       <c r="B57" t="n">
         <v>78788</v>
@@ -6390,10 +6395,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>465693</v>
+        <v>465720</v>
       </c>
       <c r="R57" t="n">
-        <v>6798461</v>
+        <v>6798411</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6452,7 +6457,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123913451</v>
+        <v>123913450</v>
       </c>
       <c r="B58" t="n">
         <v>78788</v>
@@ -6492,10 +6497,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>465838</v>
+        <v>465835</v>
       </c>
       <c r="R58" t="n">
-        <v>6798591</v>
+        <v>6798579</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6554,10 +6559,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123913274</v>
+        <v>123913327</v>
       </c>
       <c r="B59" t="n">
-        <v>78820</v>
+        <v>79377</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6570,21 +6575,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6594,10 +6599,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>465705</v>
+        <v>465779</v>
       </c>
       <c r="R59" t="n">
-        <v>6798509</v>
+        <v>6798140</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6656,10 +6661,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123913306</v>
+        <v>123913472</v>
       </c>
       <c r="B60" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6672,21 +6677,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6696,10 +6701,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>465841</v>
+        <v>465710</v>
       </c>
       <c r="R60" t="n">
-        <v>6798109</v>
+        <v>6798561</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6758,7 +6763,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123913504</v>
+        <v>123913496</v>
       </c>
       <c r="B61" t="n">
         <v>78788</v>
@@ -6798,10 +6803,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>465787</v>
+        <v>465749</v>
       </c>
       <c r="R61" t="n">
-        <v>6798158</v>
+        <v>6798268</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6860,10 +6865,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123913532</v>
+        <v>123913276</v>
       </c>
       <c r="B62" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6876,21 +6881,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6900,10 +6905,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>465912</v>
+        <v>465694</v>
       </c>
       <c r="R62" t="n">
-        <v>6798108</v>
+        <v>6798446</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6962,10 +6967,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123913323</v>
+        <v>123913374</v>
       </c>
       <c r="B63" t="n">
-        <v>90955</v>
+        <v>80741</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6974,25 +6979,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>1049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7002,10 +7007,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465849</v>
+        <v>465857</v>
       </c>
       <c r="R63" t="n">
-        <v>6798130</v>
+        <v>6798531</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7064,7 +7069,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123913453</v>
+        <v>123913458</v>
       </c>
       <c r="B64" t="n">
         <v>78788</v>
@@ -7104,10 +7109,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>465833</v>
+        <v>465826</v>
       </c>
       <c r="R64" t="n">
-        <v>6798603</v>
+        <v>6798611</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7166,10 +7171,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123913249</v>
+        <v>123913470</v>
       </c>
       <c r="B65" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7182,21 +7187,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7206,10 +7211,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465757</v>
+        <v>465726</v>
       </c>
       <c r="R65" t="n">
-        <v>6798402</v>
+        <v>6798570</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7268,7 +7273,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123913436</v>
+        <v>123913532</v>
       </c>
       <c r="B66" t="n">
         <v>78788</v>
@@ -7308,10 +7313,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465927</v>
+        <v>465912</v>
       </c>
       <c r="R66" t="n">
-        <v>6798517</v>
+        <v>6798108</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7370,10 +7375,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123913330</v>
+        <v>123913309</v>
       </c>
       <c r="B67" t="n">
-        <v>79377</v>
+        <v>78820</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7386,21 +7391,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7410,10 +7415,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465815</v>
+        <v>465845</v>
       </c>
       <c r="R67" t="n">
-        <v>6798097</v>
+        <v>6798127</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7472,10 +7477,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123913496</v>
+        <v>123913277</v>
       </c>
       <c r="B68" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7488,21 +7493,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7512,10 +7517,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465749</v>
+        <v>465709</v>
       </c>
       <c r="R68" t="n">
-        <v>6798268</v>
+        <v>6798426</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7574,10 +7579,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123913443</v>
+        <v>123913271</v>
       </c>
       <c r="B69" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7590,21 +7595,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7614,10 +7619,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465863</v>
+        <v>465720</v>
       </c>
       <c r="R69" t="n">
-        <v>6798532</v>
+        <v>6798523</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7676,7 +7681,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123913448</v>
+        <v>123913453</v>
       </c>
       <c r="B70" t="n">
         <v>78788</v>
@@ -7716,10 +7721,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>465839</v>
+        <v>465833</v>
       </c>
       <c r="R70" t="n">
-        <v>6798559</v>
+        <v>6798603</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7778,7 +7783,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123913498</v>
+        <v>123913436</v>
       </c>
       <c r="B71" t="n">
         <v>78788</v>
@@ -7818,10 +7823,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465746</v>
+        <v>465927</v>
       </c>
       <c r="R71" t="n">
-        <v>6798258</v>
+        <v>6798517</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7880,10 +7885,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123913339</v>
+        <v>123913446</v>
       </c>
       <c r="B72" t="n">
-        <v>57644</v>
+        <v>78788</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7896,21 +7901,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7920,10 +7925,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>465825</v>
+        <v>465875</v>
       </c>
       <c r="R72" t="n">
-        <v>6798086</v>
+        <v>6798559</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7982,10 +7987,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123913327</v>
+        <v>123913266</v>
       </c>
       <c r="B73" t="n">
-        <v>79377</v>
+        <v>78820</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7998,21 +8003,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8022,10 +8027,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>465779</v>
+        <v>465839</v>
       </c>
       <c r="R73" t="n">
-        <v>6798140</v>
+        <v>6798559</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8084,10 +8089,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123913572</v>
+        <v>123913289</v>
       </c>
       <c r="B74" t="n">
-        <v>78433</v>
+        <v>78820</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8100,21 +8105,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8124,10 +8129,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>465778</v>
+        <v>465786</v>
       </c>
       <c r="R74" t="n">
-        <v>6798141</v>
+        <v>6798177</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8179,14 +8184,14 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123913309</v>
+        <v>123913285</v>
       </c>
       <c r="B75" t="n">
         <v>78820</v>
@@ -8226,10 +8231,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>465845</v>
+        <v>465735</v>
       </c>
       <c r="R75" t="n">
-        <v>6798127</v>
+        <v>6798291</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8288,10 +8293,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123913374</v>
+        <v>123913480</v>
       </c>
       <c r="B76" t="n">
-        <v>80741</v>
+        <v>78788</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8304,21 +8309,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8328,10 +8333,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>465857</v>
+        <v>465696</v>
       </c>
       <c r="R76" t="n">
-        <v>6798531</v>
+        <v>6798479</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8390,10 +8395,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123913307</v>
+        <v>123913500</v>
       </c>
       <c r="B77" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8406,21 +8411,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8430,10 +8435,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>465884</v>
+        <v>465780</v>
       </c>
       <c r="R77" t="n">
-        <v>6798130</v>
+        <v>6798219</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8492,10 +8497,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123913262</v>
+        <v>123913490</v>
       </c>
       <c r="B78" t="n">
-        <v>74879</v>
+        <v>78788</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8508,21 +8513,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8532,10 +8537,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>465764</v>
+        <v>465741</v>
       </c>
       <c r="R78" t="n">
-        <v>6798656</v>
+        <v>6798376</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8594,10 +8599,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123913462</v>
+        <v>123913244</v>
       </c>
       <c r="B79" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8610,21 +8615,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8634,10 +8639,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>465782</v>
+        <v>465933</v>
       </c>
       <c r="R79" t="n">
-        <v>6798650</v>
+        <v>6798458</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8696,10 +8701,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123913315</v>
+        <v>123913339</v>
       </c>
       <c r="B80" t="n">
-        <v>78820</v>
+        <v>57644</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8712,21 +8717,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8736,10 +8741,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>465899</v>
+        <v>465825</v>
       </c>
       <c r="R80" t="n">
-        <v>6798123</v>
+        <v>6798086</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8798,10 +8803,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123913517</v>
+        <v>123913334</v>
       </c>
       <c r="B81" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8814,21 +8819,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8838,10 +8843,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>465837</v>
+        <v>465933</v>
       </c>
       <c r="R81" t="n">
-        <v>6798096</v>
+        <v>6798526</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8900,7 +8905,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123913446</v>
+        <v>123913464</v>
       </c>
       <c r="B82" t="n">
         <v>78788</v>
@@ -8940,10 +8945,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>465875</v>
+        <v>465767</v>
       </c>
       <c r="R82" t="n">
-        <v>6798559</v>
+        <v>6798617</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9002,10 +9007,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123913406</v>
+        <v>123913498</v>
       </c>
       <c r="B83" t="n">
-        <v>91150</v>
+        <v>78788</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9014,25 +9019,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9042,10 +9047,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>465872</v>
+        <v>465746</v>
       </c>
       <c r="R83" t="n">
-        <v>6798093</v>
+        <v>6798258</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9104,10 +9109,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123913277</v>
+        <v>123913247</v>
       </c>
       <c r="B84" t="n">
-        <v>78820</v>
+        <v>79406</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9120,21 +9125,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9144,10 +9149,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>465709</v>
+        <v>465707</v>
       </c>
       <c r="R84" t="n">
-        <v>6798426</v>
+        <v>6798475</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9206,10 +9211,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123913426</v>
+        <v>123913581</v>
       </c>
       <c r="B85" t="n">
-        <v>78788</v>
+        <v>5176</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9218,38 +9223,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>465923</v>
+        <v>465737</v>
       </c>
       <c r="R85" t="n">
-        <v>6798451</v>
+        <v>6798286</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9301,17 +9311,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123913423</v>
+        <v>123913572</v>
       </c>
       <c r="B86" t="n">
-        <v>78788</v>
+        <v>78433</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9324,21 +9334,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9348,10 +9358,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>465920</v>
+        <v>465778</v>
       </c>
       <c r="R86" t="n">
-        <v>6798445</v>
+        <v>6798141</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9403,14 +9413,14 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123913268</v>
+        <v>123913280</v>
       </c>
       <c r="B87" t="n">
         <v>78820</v>
@@ -9450,10 +9460,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>465767</v>
+        <v>465753</v>
       </c>
       <c r="R87" t="n">
-        <v>6798617</v>
+        <v>6798400</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9512,10 +9522,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123913470</v>
+        <v>123913313</v>
       </c>
       <c r="B88" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9528,21 +9538,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9552,10 +9562,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>465726</v>
+        <v>465883</v>
       </c>
       <c r="R88" t="n">
-        <v>6798570</v>
+        <v>6798119</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9614,10 +9624,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123913291</v>
+        <v>123913258</v>
       </c>
       <c r="B89" t="n">
-        <v>78820</v>
+        <v>74879</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9630,21 +9640,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9654,10 +9664,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>465775</v>
+        <v>465915</v>
       </c>
       <c r="R89" t="n">
-        <v>6798148</v>
+        <v>6798548</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9716,10 +9726,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123913266</v>
+        <v>123913473</v>
       </c>
       <c r="B90" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9732,21 +9742,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9756,10 +9766,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>465839</v>
+        <v>465720</v>
       </c>
       <c r="R90" t="n">
-        <v>6798559</v>
+        <v>6798523</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9818,10 +9828,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123913485</v>
+        <v>123913287</v>
       </c>
       <c r="B91" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9834,21 +9844,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9858,10 +9868,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>465709</v>
+        <v>465786</v>
       </c>
       <c r="R91" t="n">
-        <v>6798426</v>
+        <v>6798207</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9920,10 +9930,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123913311</v>
+        <v>123913494</v>
       </c>
       <c r="B92" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9936,21 +9946,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9960,10 +9970,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>465842</v>
+        <v>465741</v>
       </c>
       <c r="R92" t="n">
-        <v>6798116</v>
+        <v>6798286</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10022,10 +10032,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123913282</v>
+        <v>123913477</v>
       </c>
       <c r="B93" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10038,21 +10048,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10062,10 +10072,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>465748</v>
+        <v>465708</v>
       </c>
       <c r="R93" t="n">
-        <v>6798396</v>
+        <v>6798481</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10124,10 +10134,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123913519</v>
+        <v>123913330</v>
       </c>
       <c r="B94" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10140,21 +10150,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10164,10 +10174,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>465865</v>
+        <v>465815</v>
       </c>
       <c r="R94" t="n">
-        <v>6798133</v>
+        <v>6798097</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10226,10 +10236,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123913464</v>
+        <v>123913282</v>
       </c>
       <c r="B95" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10242,21 +10252,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10266,10 +10276,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>465767</v>
+        <v>465748</v>
       </c>
       <c r="R95" t="n">
-        <v>6798617</v>
+        <v>6798396</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10328,7 +10338,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123913276</v>
+        <v>123913279</v>
       </c>
       <c r="B96" t="n">
         <v>78820</v>
@@ -10368,10 +10378,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>465694</v>
+        <v>465720</v>
       </c>
       <c r="R96" t="n">
-        <v>6798446</v>
+        <v>6798411</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10430,7 +10440,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123913527</v>
+        <v>123913423</v>
       </c>
       <c r="B97" t="n">
         <v>78788</v>
@@ -10470,10 +10480,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>465878</v>
+        <v>465920</v>
       </c>
       <c r="R97" t="n">
-        <v>6798095</v>
+        <v>6798445</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10532,7 +10542,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123913502</v>
+        <v>123913530</v>
       </c>
       <c r="B98" t="n">
         <v>78788</v>
@@ -10572,10 +10582,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>465783</v>
+        <v>465883</v>
       </c>
       <c r="R98" t="n">
-        <v>6798169</v>
+        <v>6798119</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10634,10 +10644,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123913487</v>
+        <v>123913260</v>
       </c>
       <c r="B99" t="n">
-        <v>78788</v>
+        <v>74879</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10650,21 +10660,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10674,10 +10684,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>465720</v>
+        <v>465830</v>
       </c>
       <c r="R99" t="n">
-        <v>6798411</v>
+        <v>6798623</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10736,7 +10746,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123913492</v>
+        <v>123913489</v>
       </c>
       <c r="B100" t="n">
         <v>78788</v>
@@ -10776,10 +10786,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>465749</v>
+        <v>465753</v>
       </c>
       <c r="R100" t="n">
-        <v>6798363</v>
+        <v>6798400</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10838,7 +10848,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123913472</v>
+        <v>123913439</v>
       </c>
       <c r="B101" t="n">
         <v>78788</v>
@@ -10878,10 +10888,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>465710</v>
+        <v>465919</v>
       </c>
       <c r="R101" t="n">
-        <v>6798561</v>
+        <v>6798535</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10940,10 +10950,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123913247</v>
+        <v>123913485</v>
       </c>
       <c r="B102" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10956,21 +10966,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10980,10 +10990,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>465707</v>
+        <v>465709</v>
       </c>
       <c r="R102" t="n">
-        <v>6798475</v>
+        <v>6798426</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11042,10 +11052,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123913287</v>
+        <v>123913517</v>
       </c>
       <c r="B103" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11058,21 +11068,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11082,10 +11092,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>465786</v>
+        <v>465837</v>
       </c>
       <c r="R103" t="n">
-        <v>6798207</v>
+        <v>6798096</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11144,7 +11154,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>123913438</v>
+        <v>123913527</v>
       </c>
       <c r="B104" t="n">
         <v>78788</v>
@@ -11184,10 +11194,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>465904</v>
+        <v>465878</v>
       </c>
       <c r="R104" t="n">
-        <v>6798521</v>
+        <v>6798095</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11246,7 +11256,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123913525</v>
+        <v>123913504</v>
       </c>
       <c r="B105" t="n">
         <v>78788</v>
@@ -11286,10 +11296,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>465837</v>
+        <v>465787</v>
       </c>
       <c r="R105" t="n">
-        <v>6798100</v>
+        <v>6798158</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11348,7 +11358,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123913473</v>
+        <v>123913430</v>
       </c>
       <c r="B106" t="n">
         <v>78788</v>
@@ -11388,10 +11398,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>465720</v>
+        <v>465947</v>
       </c>
       <c r="R106" t="n">
-        <v>6798523</v>
+        <v>6798479</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11450,10 +11460,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123913256</v>
+        <v>123913483</v>
       </c>
       <c r="B107" t="n">
-        <v>74879</v>
+        <v>78788</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11466,21 +11476,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11490,10 +11500,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>465939</v>
+        <v>465694</v>
       </c>
       <c r="R107" t="n">
-        <v>6798534</v>
+        <v>6798446</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11552,10 +11562,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123913530</v>
+        <v>123913317</v>
       </c>
       <c r="B108" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11568,21 +11578,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11592,10 +11602,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>465883</v>
+        <v>465913</v>
       </c>
       <c r="R108" t="n">
-        <v>6798119</v>
+        <v>6798106</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11654,10 +11664,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123913269</v>
+        <v>123913251</v>
       </c>
       <c r="B109" t="n">
-        <v>78820</v>
+        <v>79406</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11670,21 +11680,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11694,10 +11704,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>465705</v>
+        <v>465775</v>
       </c>
       <c r="R109" t="n">
-        <v>6798564</v>
+        <v>6798229</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11756,10 +11766,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123913317</v>
+        <v>123913492</v>
       </c>
       <c r="B110" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11772,21 +11782,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11796,10 +11806,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>465913</v>
+        <v>465749</v>
       </c>
       <c r="R110" t="n">
-        <v>6798106</v>
+        <v>6798363</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11858,7 +11868,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123913477</v>
+        <v>123913522</v>
       </c>
       <c r="B111" t="n">
         <v>78788</v>
@@ -11898,10 +11908,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>465708</v>
+        <v>465842</v>
       </c>
       <c r="R111" t="n">
-        <v>6798481</v>
+        <v>6798113</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11960,10 +11970,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123913271</v>
+        <v>123913441</v>
       </c>
       <c r="B112" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11976,21 +11986,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12000,10 +12010,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>465720</v>
+        <v>465893</v>
       </c>
       <c r="R112" t="n">
-        <v>6798523</v>
+        <v>6798543</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12062,10 +12072,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>123913251</v>
+        <v>123913291</v>
       </c>
       <c r="B113" t="n">
-        <v>79406</v>
+        <v>78820</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12078,21 +12088,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12105,7 +12115,7 @@
         <v>465775</v>
       </c>
       <c r="R113" t="n">
-        <v>6798229</v>
+        <v>6798148</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12164,10 +12174,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123913460</v>
+        <v>123913268</v>
       </c>
       <c r="B114" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12180,21 +12190,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12204,10 +12214,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>465809</v>
+        <v>465767</v>
       </c>
       <c r="R114" t="n">
-        <v>6798627</v>
+        <v>6798617</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12266,7 +12276,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123913285</v>
+        <v>123913306</v>
       </c>
       <c r="B115" t="n">
         <v>78820</v>
@@ -12306,10 +12316,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>465735</v>
+        <v>465841</v>
       </c>
       <c r="R115" t="n">
-        <v>6798291</v>
+        <v>6798109</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12368,10 +12378,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123913258</v>
+        <v>123913515</v>
       </c>
       <c r="B116" t="n">
-        <v>74879</v>
+        <v>78788</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12384,21 +12394,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12408,10 +12418,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>465915</v>
+        <v>465825</v>
       </c>
       <c r="R116" t="n">
-        <v>6798548</v>
+        <v>6798086</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12470,10 +12480,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123876771</v>
+        <v>123913256</v>
       </c>
       <c r="B117" t="n">
-        <v>78788</v>
+        <v>74879</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12486,21 +12496,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12510,10 +12520,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>465815</v>
+        <v>465939</v>
       </c>
       <c r="R117" t="n">
-        <v>6798172</v>
+        <v>6798534</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12548,11 +12558,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Garnlav bakom björnide, samt i en radie av ca 30 meter.  Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -12565,19 +12570,19 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123913494</v>
+        <v>123913475</v>
       </c>
       <c r="B118" t="n">
         <v>78788</v>
@@ -12617,10 +12622,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>465741</v>
+        <v>465719</v>
       </c>
       <c r="R118" t="n">
-        <v>6798286</v>
+        <v>6798495</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12679,10 +12684,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123913289</v>
+        <v>123913262</v>
       </c>
       <c r="B119" t="n">
-        <v>78820</v>
+        <v>74879</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12695,21 +12700,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12719,10 +12724,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>465786</v>
+        <v>465764</v>
       </c>
       <c r="R119" t="n">
-        <v>6798177</v>
+        <v>6798656</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12781,10 +12786,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>123913441</v>
+        <v>123913323</v>
       </c>
       <c r="B120" t="n">
-        <v>78788</v>
+        <v>90955</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12793,25 +12798,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12821,10 +12826,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>465893</v>
+        <v>465849</v>
       </c>
       <c r="R120" t="n">
-        <v>6798543</v>
+        <v>6798130</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12883,10 +12888,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123913334</v>
+        <v>123913462</v>
       </c>
       <c r="B121" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12899,21 +12904,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12923,10 +12928,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>465933</v>
+        <v>465782</v>
       </c>
       <c r="R121" t="n">
-        <v>6798526</v>
+        <v>6798650</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12985,7 +12990,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123913483</v>
+        <v>123913482</v>
       </c>
       <c r="B122" t="n">
         <v>78788</v>
@@ -13025,10 +13030,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>465694</v>
+        <v>465693</v>
       </c>
       <c r="R122" t="n">
-        <v>6798446</v>
+        <v>6798461</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13087,7 +13092,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123913515</v>
+        <v>123913525</v>
       </c>
       <c r="B123" t="n">
         <v>78788</v>
@@ -13127,10 +13132,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>465825</v>
+        <v>465837</v>
       </c>
       <c r="R123" t="n">
-        <v>6798086</v>
+        <v>6798100</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13189,10 +13194,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123913244</v>
+        <v>123913274</v>
       </c>
       <c r="B124" t="n">
-        <v>79406</v>
+        <v>78820</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13205,21 +13210,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13229,10 +13234,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>465933</v>
+        <v>465705</v>
       </c>
       <c r="R124" t="n">
-        <v>6798458</v>
+        <v>6798509</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13291,10 +13296,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>123913581</v>
+        <v>123913368</v>
       </c>
       <c r="B125" t="n">
-        <v>5176</v>
+        <v>78525</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13303,43 +13308,38 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100526</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>465737</v>
+        <v>465859</v>
       </c>
       <c r="R125" t="n">
-        <v>6798286</v>
+        <v>6798098</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>

--- a/artfynd/A 15853-2025 artfynd.xlsx
+++ b/artfynd/A 15853-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123878365</v>
+        <v>123877884</v>
       </c>
       <c r="B2" t="n">
         <v>78788</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465783</v>
+        <v>465816</v>
       </c>
       <c r="R2" t="n">
-        <v>6798386</v>
+        <v>6798323</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123876339</v>
+        <v>123878888</v>
       </c>
       <c r="B3" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465823</v>
+        <v>465907</v>
       </c>
       <c r="R3" t="n">
-        <v>6798111</v>
+        <v>6798419</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Garnlav i synfältet, 30 meter i radie. Miljöbilder</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123877582</v>
+        <v>123877326</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +905,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465745</v>
+        <v>465799</v>
       </c>
       <c r="R4" t="n">
-        <v>6798476</v>
+        <v>6798259</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -955,6 +970,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,22 +989,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123877175</v>
+        <v>123876878</v>
       </c>
       <c r="B5" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,37 +1017,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465790</v>
+        <v>465833</v>
       </c>
       <c r="R5" t="n">
-        <v>6798239</v>
+        <v>6798269</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1057,11 +1077,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,19 +1091,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123877304</v>
+        <v>123877433</v>
       </c>
       <c r="B6" t="n">
         <v>78788</v>
@@ -1128,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465832</v>
+        <v>465854</v>
       </c>
       <c r="R6" t="n">
-        <v>6798359</v>
+        <v>6798343</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123877138</v>
+        <v>123876586</v>
       </c>
       <c r="B7" t="n">
         <v>78788</v>
@@ -1226,17 +1241,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465846</v>
+        <v>465848</v>
       </c>
       <c r="R7" t="n">
-        <v>6798341</v>
+        <v>6798129</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,22 +1295,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123877240</v>
+        <v>123876786</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465859</v>
+        <v>465862</v>
       </c>
       <c r="R8" t="n">
-        <v>6798332</v>
+        <v>6798219</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1394,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123876845</v>
+        <v>123878104</v>
       </c>
       <c r="B9" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,37 +1425,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465832</v>
+        <v>465803</v>
       </c>
       <c r="R9" t="n">
-        <v>6798231</v>
+        <v>6798395</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1484,19 +1499,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123876143</v>
+        <v>123877138</v>
       </c>
       <c r="B10" t="n">
         <v>78788</v>
@@ -1536,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465821</v>
+        <v>465846</v>
       </c>
       <c r="R10" t="n">
-        <v>6798095</v>
+        <v>6798341</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1598,7 +1613,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123877884</v>
+        <v>123877582</v>
       </c>
       <c r="B11" t="n">
         <v>78788</v>
@@ -1634,17 +1649,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465816</v>
+        <v>465745</v>
       </c>
       <c r="R11" t="n">
-        <v>6798323</v>
+        <v>6798476</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1674,11 +1689,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,19 +1703,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123878630</v>
+        <v>123878923</v>
       </c>
       <c r="B12" t="n">
         <v>78788</v>
@@ -1741,17 +1751,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465884</v>
+        <v>465911</v>
       </c>
       <c r="R12" t="n">
-        <v>6798405</v>
+        <v>6798461</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1781,11 +1791,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1800,22 +1805,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123876733</v>
+        <v>123877850</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465844</v>
+        <v>465863</v>
       </c>
       <c r="R13" t="n">
-        <v>6798212</v>
+        <v>6798375</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1914,7 +1919,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123878923</v>
+        <v>123878561</v>
       </c>
       <c r="B14" t="n">
         <v>78788</v>
@@ -1954,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465911</v>
+        <v>465804</v>
       </c>
       <c r="R14" t="n">
-        <v>6798461</v>
+        <v>6798478</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2118,7 +2123,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123878888</v>
+        <v>123878630</v>
       </c>
       <c r="B16" t="n">
         <v>78788</v>
@@ -2158,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465907</v>
+        <v>465884</v>
       </c>
       <c r="R16" t="n">
-        <v>6798419</v>
+        <v>6798405</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,7 +2203,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Garnlav i synfältet, 30 meter i radie. Miljöbilder</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2225,7 +2230,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123876806</v>
+        <v>123876775</v>
       </c>
       <c r="B17" t="n">
         <v>78788</v>
@@ -2265,13 +2270,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465847</v>
+        <v>465799</v>
       </c>
       <c r="R17" t="n">
-        <v>6798227</v>
+        <v>6798205</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2315,22 +2320,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123877481</v>
+        <v>123876656</v>
       </c>
       <c r="B18" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,39 +2348,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465807</v>
+        <v>465833</v>
       </c>
       <c r="R18" t="n">
-        <v>6798288</v>
+        <v>6798204</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2422,22 +2422,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123877370</v>
+        <v>123876845</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,21 +2450,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465830</v>
+        <v>465832</v>
       </c>
       <c r="R19" t="n">
-        <v>6798388</v>
+        <v>6798231</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123876586</v>
+        <v>123877481</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,34 +2552,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465848</v>
+        <v>465807</v>
       </c>
       <c r="R20" t="n">
-        <v>6798129</v>
+        <v>6798288</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,7 +2643,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123876656</v>
+        <v>123876143</v>
       </c>
       <c r="B21" t="n">
         <v>78788</v>
@@ -2678,13 +2683,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465833</v>
+        <v>465821</v>
       </c>
       <c r="R21" t="n">
-        <v>6798204</v>
+        <v>6798095</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2740,10 +2745,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123877850</v>
+        <v>123877248</v>
       </c>
       <c r="B22" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2756,37 +2761,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465863</v>
+        <v>465799</v>
       </c>
       <c r="R22" t="n">
-        <v>6798375</v>
+        <v>6798259</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2816,6 +2821,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2830,22 +2840,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123876786</v>
+        <v>123877175</v>
       </c>
       <c r="B23" t="n">
-        <v>78525</v>
+        <v>79377</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2858,37 +2868,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465862</v>
+        <v>465790</v>
       </c>
       <c r="R23" t="n">
-        <v>6798219</v>
+        <v>6798239</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2918,6 +2928,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2932,19 +2947,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123878561</v>
+        <v>123876291</v>
       </c>
       <c r="B24" t="n">
         <v>78788</v>
@@ -2984,10 +2999,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465804</v>
+        <v>465806</v>
       </c>
       <c r="R24" t="n">
-        <v>6798478</v>
+        <v>6798100</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3046,7 +3061,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123877248</v>
+        <v>123878210</v>
       </c>
       <c r="B25" t="n">
         <v>78788</v>
@@ -3082,17 +3097,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465799</v>
+        <v>465813</v>
       </c>
       <c r="R25" t="n">
-        <v>6798259</v>
+        <v>6798394</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3122,11 +3137,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3141,19 +3151,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123878436</v>
+        <v>123877240</v>
       </c>
       <c r="B26" t="n">
         <v>78788</v>
@@ -3189,17 +3199,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465800</v>
+        <v>465859</v>
       </c>
       <c r="R26" t="n">
-        <v>6798391</v>
+        <v>6798332</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3229,11 +3239,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Garnlav synligt ca 30 meters radie. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3248,22 +3253,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123876866</v>
+        <v>123878436</v>
       </c>
       <c r="B27" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3272,41 +3277,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465848</v>
+        <v>465800</v>
       </c>
       <c r="R27" t="n">
-        <v>6798245</v>
+        <v>6798391</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3340,7 +3345,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Nyare spillning.</t>
+          <t>Garnlav synligt ca 30 meters radie. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3355,22 +3360,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123877017</v>
+        <v>123876521</v>
       </c>
       <c r="B28" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3383,34 +3388,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465805</v>
+        <v>465877</v>
       </c>
       <c r="R28" t="n">
-        <v>6798194</v>
+        <v>6798138</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3445,11 +3450,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3462,22 +3462,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123876878</v>
+        <v>123877017</v>
       </c>
       <c r="B29" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3490,37 +3490,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465833</v>
+        <v>465805</v>
       </c>
       <c r="R29" t="n">
-        <v>6798269</v>
+        <v>6798194</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3550,6 +3550,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3564,19 +3569,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123876291</v>
+        <v>123876806</v>
       </c>
       <c r="B30" t="n">
         <v>78788</v>
@@ -3616,10 +3621,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465806</v>
+        <v>465847</v>
       </c>
       <c r="R30" t="n">
-        <v>6798100</v>
+        <v>6798227</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3678,7 +3683,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123876521</v>
+        <v>123876733</v>
       </c>
       <c r="B31" t="n">
         <v>78788</v>
@@ -3718,13 +3723,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465877</v>
+        <v>465844</v>
       </c>
       <c r="R31" t="n">
-        <v>6798138</v>
+        <v>6798212</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3768,19 +3773,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123878210</v>
+        <v>123878365</v>
       </c>
       <c r="B32" t="n">
         <v>78788</v>
@@ -3820,10 +3825,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>465813</v>
+        <v>465783</v>
       </c>
       <c r="R32" t="n">
-        <v>6798394</v>
+        <v>6798386</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3882,7 +3887,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123876157</v>
+        <v>123877304</v>
       </c>
       <c r="B33" t="n">
         <v>78788</v>
@@ -3922,13 +3927,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465822</v>
+        <v>465832</v>
       </c>
       <c r="R33" t="n">
-        <v>6798106</v>
+        <v>6798359</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3984,10 +3989,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123876691</v>
+        <v>123876866</v>
       </c>
       <c r="B34" t="n">
-        <v>78820</v>
+        <v>56700</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3996,25 +4001,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4024,10 +4029,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>465832</v>
+        <v>465848</v>
       </c>
       <c r="R34" t="n">
-        <v>6798208</v>
+        <v>6798245</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4060,6 +4065,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Nyare spillning.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4086,7 +4096,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123876775</v>
+        <v>123877370</v>
       </c>
       <c r="B35" t="n">
         <v>78788</v>
@@ -4126,13 +4136,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465799</v>
+        <v>465830</v>
       </c>
       <c r="R35" t="n">
-        <v>6798205</v>
+        <v>6798388</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4176,22 +4186,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123878104</v>
+        <v>123876339</v>
       </c>
       <c r="B36" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4204,37 +4214,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465803</v>
+        <v>465823</v>
       </c>
       <c r="R36" t="n">
-        <v>6798395</v>
+        <v>6798111</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4278,22 +4288,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123877433</v>
+        <v>123876691</v>
       </c>
       <c r="B37" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4306,21 +4316,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4330,10 +4340,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465854</v>
+        <v>465832</v>
       </c>
       <c r="R37" t="n">
-        <v>6798343</v>
+        <v>6798208</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4392,10 +4402,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123877326</v>
+        <v>123876157</v>
       </c>
       <c r="B38" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4408,42 +4418,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465799</v>
+        <v>465822</v>
       </c>
       <c r="R38" t="n">
-        <v>6798259</v>
+        <v>6798106</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4473,11 +4478,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4492,12 +4492,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -7069,10 +7069,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123913458</v>
+        <v>123913309</v>
       </c>
       <c r="B64" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7085,21 +7085,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7109,10 +7109,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>465826</v>
+        <v>465845</v>
       </c>
       <c r="R64" t="n">
-        <v>6798611</v>
+        <v>6798127</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7171,10 +7171,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123913470</v>
+        <v>123913277</v>
       </c>
       <c r="B65" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7187,21 +7187,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7211,10 +7211,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465726</v>
+        <v>465709</v>
       </c>
       <c r="R65" t="n">
-        <v>6798570</v>
+        <v>6798426</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7273,10 +7273,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123913532</v>
+        <v>123913271</v>
       </c>
       <c r="B66" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7289,21 +7289,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7313,10 +7313,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465912</v>
+        <v>465720</v>
       </c>
       <c r="R66" t="n">
-        <v>6798108</v>
+        <v>6798523</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7375,10 +7375,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123913309</v>
+        <v>123913453</v>
       </c>
       <c r="B67" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7391,21 +7391,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7415,10 +7415,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465845</v>
+        <v>465833</v>
       </c>
       <c r="R67" t="n">
-        <v>6798127</v>
+        <v>6798603</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7477,10 +7477,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123913277</v>
+        <v>123913458</v>
       </c>
       <c r="B68" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7493,21 +7493,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7517,10 +7517,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465709</v>
+        <v>465826</v>
       </c>
       <c r="R68" t="n">
-        <v>6798426</v>
+        <v>6798611</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7579,10 +7579,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123913271</v>
+        <v>123913470</v>
       </c>
       <c r="B69" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7595,21 +7595,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7619,10 +7619,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465720</v>
+        <v>465726</v>
       </c>
       <c r="R69" t="n">
-        <v>6798523</v>
+        <v>6798570</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123913453</v>
+        <v>123913532</v>
       </c>
       <c r="B70" t="n">
         <v>78788</v>
@@ -7721,10 +7721,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>465833</v>
+        <v>465912</v>
       </c>
       <c r="R70" t="n">
-        <v>6798603</v>
+        <v>6798108</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7987,10 +7987,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123913266</v>
+        <v>123913480</v>
       </c>
       <c r="B73" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8003,21 +8003,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8027,10 +8027,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>465839</v>
+        <v>465696</v>
       </c>
       <c r="R73" t="n">
-        <v>6798559</v>
+        <v>6798479</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8089,7 +8089,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123913289</v>
+        <v>123913266</v>
       </c>
       <c r="B74" t="n">
         <v>78820</v>
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>465786</v>
+        <v>465839</v>
       </c>
       <c r="R74" t="n">
-        <v>6798177</v>
+        <v>6798559</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8191,7 +8191,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123913285</v>
+        <v>123913289</v>
       </c>
       <c r="B75" t="n">
         <v>78820</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>465735</v>
+        <v>465786</v>
       </c>
       <c r="R75" t="n">
-        <v>6798291</v>
+        <v>6798177</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8293,10 +8293,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123913480</v>
+        <v>123913285</v>
       </c>
       <c r="B76" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8309,21 +8309,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8333,10 +8333,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>465696</v>
+        <v>465735</v>
       </c>
       <c r="R76" t="n">
-        <v>6798479</v>
+        <v>6798291</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8599,10 +8599,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123913244</v>
+        <v>123913339</v>
       </c>
       <c r="B79" t="n">
-        <v>79406</v>
+        <v>57644</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8615,21 +8615,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>465933</v>
+        <v>465825</v>
       </c>
       <c r="R79" t="n">
-        <v>6798458</v>
+        <v>6798086</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8701,10 +8701,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123913339</v>
+        <v>123913244</v>
       </c>
       <c r="B80" t="n">
-        <v>57644</v>
+        <v>79406</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8717,21 +8717,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>465825</v>
+        <v>465933</v>
       </c>
       <c r="R80" t="n">
-        <v>6798086</v>
+        <v>6798458</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9624,10 +9624,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123913258</v>
+        <v>123913330</v>
       </c>
       <c r="B89" t="n">
-        <v>74879</v>
+        <v>79377</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9640,21 +9640,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9664,10 +9664,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>465915</v>
+        <v>465815</v>
       </c>
       <c r="R89" t="n">
-        <v>6798548</v>
+        <v>6798097</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9726,10 +9726,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123913473</v>
+        <v>123913258</v>
       </c>
       <c r="B90" t="n">
-        <v>78788</v>
+        <v>74879</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9742,21 +9742,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>465720</v>
+        <v>465915</v>
       </c>
       <c r="R90" t="n">
-        <v>6798523</v>
+        <v>6798548</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9828,10 +9828,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123913287</v>
+        <v>123913473</v>
       </c>
       <c r="B91" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9844,21 +9844,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9868,10 +9868,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>465786</v>
+        <v>465720</v>
       </c>
       <c r="R91" t="n">
-        <v>6798207</v>
+        <v>6798523</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10134,10 +10134,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123913330</v>
+        <v>123913287</v>
       </c>
       <c r="B94" t="n">
-        <v>79377</v>
+        <v>78820</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10150,21 +10150,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10174,10 +10174,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>465815</v>
+        <v>465786</v>
       </c>
       <c r="R94" t="n">
-        <v>6798097</v>
+        <v>6798207</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10236,10 +10236,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123913282</v>
+        <v>123913423</v>
       </c>
       <c r="B95" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10252,21 +10252,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10276,10 +10276,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>465748</v>
+        <v>465920</v>
       </c>
       <c r="R95" t="n">
-        <v>6798396</v>
+        <v>6798445</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10338,10 +10338,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123913279</v>
+        <v>123913530</v>
       </c>
       <c r="B96" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10354,21 +10354,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10378,10 +10378,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>465720</v>
+        <v>465883</v>
       </c>
       <c r="R96" t="n">
-        <v>6798411</v>
+        <v>6798119</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10440,10 +10440,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123913423</v>
+        <v>123913260</v>
       </c>
       <c r="B97" t="n">
-        <v>78788</v>
+        <v>74879</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10456,21 +10456,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10480,10 +10480,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>465920</v>
+        <v>465830</v>
       </c>
       <c r="R97" t="n">
-        <v>6798445</v>
+        <v>6798623</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10542,7 +10542,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123913530</v>
+        <v>123913489</v>
       </c>
       <c r="B98" t="n">
         <v>78788</v>
@@ -10582,10 +10582,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>465883</v>
+        <v>465753</v>
       </c>
       <c r="R98" t="n">
-        <v>6798119</v>
+        <v>6798400</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10644,10 +10644,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123913260</v>
+        <v>123913439</v>
       </c>
       <c r="B99" t="n">
-        <v>74879</v>
+        <v>78788</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10660,21 +10660,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10684,10 +10684,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>465830</v>
+        <v>465919</v>
       </c>
       <c r="R99" t="n">
-        <v>6798623</v>
+        <v>6798535</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10746,10 +10746,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123913489</v>
+        <v>123913282</v>
       </c>
       <c r="B100" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10762,21 +10762,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10786,10 +10786,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>465753</v>
+        <v>465748</v>
       </c>
       <c r="R100" t="n">
-        <v>6798400</v>
+        <v>6798396</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10848,10 +10848,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123913439</v>
+        <v>123913279</v>
       </c>
       <c r="B101" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10864,21 +10864,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10888,10 +10888,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>465919</v>
+        <v>465720</v>
       </c>
       <c r="R101" t="n">
-        <v>6798535</v>
+        <v>6798411</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>

--- a/artfynd/A 15853-2025 artfynd.xlsx
+++ b/artfynd/A 15853-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123877884</v>
+        <v>123877481</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465816</v>
+        <v>465807</v>
       </c>
       <c r="R2" t="n">
-        <v>6798323</v>
+        <v>6798288</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +756,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123878888</v>
+        <v>123876656</v>
       </c>
       <c r="B3" t="n">
         <v>78788</v>
@@ -818,14 +818,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465907</v>
+        <v>465833</v>
       </c>
       <c r="R3" t="n">
-        <v>6798419</v>
+        <v>6798204</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,11 +860,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Garnlav i synfältet, 30 meter i radie. Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -877,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123877326</v>
+        <v>123878888</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465799</v>
+        <v>465907</v>
       </c>
       <c r="R4" t="n">
-        <v>6798259</v>
+        <v>6798419</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Garnlav i synfältet, 30 meter i radie. Miljöbilder</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123876878</v>
+        <v>123877240</v>
       </c>
       <c r="B5" t="n">
         <v>78788</v>
@@ -1041,13 +1031,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465833</v>
+        <v>465859</v>
       </c>
       <c r="R5" t="n">
-        <v>6798269</v>
+        <v>6798332</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,19 +1081,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123877433</v>
+        <v>123876775</v>
       </c>
       <c r="B6" t="n">
         <v>78788</v>
@@ -1143,13 +1133,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465854</v>
+        <v>465799</v>
       </c>
       <c r="R6" t="n">
-        <v>6798343</v>
+        <v>6798205</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,19 +1183,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123876586</v>
+        <v>123876291</v>
       </c>
       <c r="B7" t="n">
         <v>78788</v>
@@ -1241,17 +1231,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465848</v>
+        <v>465806</v>
       </c>
       <c r="R7" t="n">
-        <v>6798129</v>
+        <v>6798100</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,22 +1285,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123876786</v>
+        <v>123878104</v>
       </c>
       <c r="B8" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,37 +1313,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465862</v>
+        <v>465803</v>
       </c>
       <c r="R8" t="n">
-        <v>6798219</v>
+        <v>6798395</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,19 +1387,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123878104</v>
+        <v>123878540</v>
       </c>
       <c r="B9" t="n">
         <v>78788</v>
@@ -1445,17 +1435,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465803</v>
+        <v>465797</v>
       </c>
       <c r="R9" t="n">
-        <v>6798395</v>
+        <v>6798473</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1499,22 +1489,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123877138</v>
+        <v>123876339</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465846</v>
+        <v>465823</v>
       </c>
       <c r="R10" t="n">
-        <v>6798341</v>
+        <v>6798111</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1613,7 +1603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123877582</v>
+        <v>123876806</v>
       </c>
       <c r="B11" t="n">
         <v>78788</v>
@@ -1653,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465745</v>
+        <v>465847</v>
       </c>
       <c r="R11" t="n">
-        <v>6798476</v>
+        <v>6798227</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1715,7 +1705,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123878923</v>
+        <v>123878630</v>
       </c>
       <c r="B12" t="n">
         <v>78788</v>
@@ -1751,17 +1741,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465911</v>
+        <v>465884</v>
       </c>
       <c r="R12" t="n">
-        <v>6798461</v>
+        <v>6798405</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1791,6 +1781,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1805,22 +1800,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123877850</v>
+        <v>123877433</v>
       </c>
       <c r="B13" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465863</v>
+        <v>465854</v>
       </c>
       <c r="R13" t="n">
-        <v>6798375</v>
+        <v>6798343</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1919,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123878561</v>
+        <v>123876143</v>
       </c>
       <c r="B14" t="n">
         <v>78788</v>
@@ -1959,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465804</v>
+        <v>465821</v>
       </c>
       <c r="R14" t="n">
-        <v>6798478</v>
+        <v>6798095</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2021,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123878540</v>
+        <v>123877850</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465797</v>
+        <v>465863</v>
       </c>
       <c r="R15" t="n">
-        <v>6798473</v>
+        <v>6798375</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2123,7 +2118,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123878630</v>
+        <v>123877884</v>
       </c>
       <c r="B16" t="n">
         <v>78788</v>
@@ -2163,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465884</v>
+        <v>465816</v>
       </c>
       <c r="R16" t="n">
-        <v>6798405</v>
+        <v>6798323</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,7 +2198,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2230,7 +2225,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123876775</v>
+        <v>123878210</v>
       </c>
       <c r="B17" t="n">
         <v>78788</v>
@@ -2270,13 +2265,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465799</v>
+        <v>465813</v>
       </c>
       <c r="R17" t="n">
-        <v>6798205</v>
+        <v>6798394</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2320,19 +2315,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123876656</v>
+        <v>123877582</v>
       </c>
       <c r="B18" t="n">
         <v>78788</v>
@@ -2372,13 +2367,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465833</v>
+        <v>465745</v>
       </c>
       <c r="R18" t="n">
-        <v>6798204</v>
+        <v>6798476</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2434,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123876845</v>
+        <v>123877304</v>
       </c>
       <c r="B19" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,21 +2445,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2477,10 +2472,10 @@
         <v>465832</v>
       </c>
       <c r="R19" t="n">
-        <v>6798231</v>
+        <v>6798359</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2536,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123877481</v>
+        <v>123876845</v>
       </c>
       <c r="B20" t="n">
-        <v>57491</v>
+        <v>78820</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,42 +2547,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465807</v>
+        <v>465832</v>
       </c>
       <c r="R20" t="n">
-        <v>6798288</v>
+        <v>6798231</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2631,19 +2621,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123876143</v>
+        <v>123878923</v>
       </c>
       <c r="B21" t="n">
         <v>78788</v>
@@ -2683,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465821</v>
+        <v>465911</v>
       </c>
       <c r="R21" t="n">
-        <v>6798095</v>
+        <v>6798461</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2745,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123877248</v>
+        <v>123876691</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2761,37 +2751,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465799</v>
+        <v>465832</v>
       </c>
       <c r="R22" t="n">
-        <v>6798259</v>
+        <v>6798208</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2821,11 +2811,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2840,22 +2825,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123877175</v>
+        <v>123876586</v>
       </c>
       <c r="B23" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2868,21 +2853,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2892,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465790</v>
+        <v>465848</v>
       </c>
       <c r="R23" t="n">
-        <v>6798239</v>
+        <v>6798129</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,11 +2913,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2959,7 +2939,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123876291</v>
+        <v>123878436</v>
       </c>
       <c r="B24" t="n">
         <v>78788</v>
@@ -2995,17 +2975,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465806</v>
+        <v>465800</v>
       </c>
       <c r="R24" t="n">
-        <v>6798100</v>
+        <v>6798391</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3035,6 +3015,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Garnlav synligt ca 30 meters radie. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3049,19 +3034,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123878210</v>
+        <v>123876157</v>
       </c>
       <c r="B25" t="n">
         <v>78788</v>
@@ -3101,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465813</v>
+        <v>465822</v>
       </c>
       <c r="R25" t="n">
-        <v>6798394</v>
+        <v>6798106</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3163,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123877240</v>
+        <v>123877175</v>
       </c>
       <c r="B26" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3179,37 +3164,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465859</v>
+        <v>465790</v>
       </c>
       <c r="R26" t="n">
-        <v>6798332</v>
+        <v>6798239</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3239,6 +3224,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3253,22 +3243,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123878436</v>
+        <v>123877017</v>
       </c>
       <c r="B27" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3281,21 +3271,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3305,10 +3295,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465800</v>
+        <v>465805</v>
       </c>
       <c r="R27" t="n">
-        <v>6798391</v>
+        <v>6798194</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3345,7 +3335,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Garnlav synligt ca 30 meters radie. Miljöbilder.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3372,7 +3362,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123876521</v>
+        <v>123876733</v>
       </c>
       <c r="B28" t="n">
         <v>78788</v>
@@ -3412,13 +3402,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465877</v>
+        <v>465844</v>
       </c>
       <c r="R28" t="n">
-        <v>6798138</v>
+        <v>6798212</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3462,22 +3452,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123877017</v>
+        <v>123876521</v>
       </c>
       <c r="B29" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3490,34 +3480,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465805</v>
+        <v>465877</v>
       </c>
       <c r="R29" t="n">
-        <v>6798194</v>
+        <v>6798138</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3552,11 +3542,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3569,19 +3554,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123876806</v>
+        <v>123878365</v>
       </c>
       <c r="B30" t="n">
         <v>78788</v>
@@ -3621,10 +3606,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465847</v>
+        <v>465783</v>
       </c>
       <c r="R30" t="n">
-        <v>6798227</v>
+        <v>6798386</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3683,10 +3668,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123876733</v>
+        <v>123877326</v>
       </c>
       <c r="B31" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3699,37 +3684,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465844</v>
+        <v>465799</v>
       </c>
       <c r="R31" t="n">
-        <v>6798212</v>
+        <v>6798259</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3759,6 +3749,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3773,19 +3768,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123878365</v>
+        <v>123877248</v>
       </c>
       <c r="B32" t="n">
         <v>78788</v>
@@ -3821,17 +3816,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>465783</v>
+        <v>465799</v>
       </c>
       <c r="R32" t="n">
-        <v>6798386</v>
+        <v>6798259</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3861,6 +3856,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3875,22 +3875,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123877304</v>
+        <v>123876786</v>
       </c>
       <c r="B33" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3903,21 +3903,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3927,13 +3927,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465832</v>
+        <v>465862</v>
       </c>
       <c r="R33" t="n">
-        <v>6798359</v>
+        <v>6798219</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123877370</v>
+        <v>123878561</v>
       </c>
       <c r="B35" t="n">
         <v>78788</v>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465830</v>
+        <v>465804</v>
       </c>
       <c r="R35" t="n">
-        <v>6798388</v>
+        <v>6798478</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4198,10 +4198,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123876339</v>
+        <v>123877138</v>
       </c>
       <c r="B36" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4214,21 +4214,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465823</v>
+        <v>465846</v>
       </c>
       <c r="R36" t="n">
-        <v>6798111</v>
+        <v>6798341</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4300,10 +4300,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123876691</v>
+        <v>123877370</v>
       </c>
       <c r="B37" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4316,21 +4316,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465832</v>
+        <v>465830</v>
       </c>
       <c r="R37" t="n">
-        <v>6798208</v>
+        <v>6798388</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4402,7 +4402,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123876157</v>
+        <v>123876878</v>
       </c>
       <c r="B38" t="n">
         <v>78788</v>
@@ -4442,13 +4442,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465822</v>
+        <v>465833</v>
       </c>
       <c r="R38" t="n">
-        <v>6798106</v>
+        <v>6798269</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4492,19 +4492,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123913426</v>
+        <v>123913502</v>
       </c>
       <c r="B39" t="n">
         <v>78788</v>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465923</v>
+        <v>465783</v>
       </c>
       <c r="R39" t="n">
-        <v>6798451</v>
+        <v>6798169</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4606,10 +4606,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123913460</v>
+        <v>123913323</v>
       </c>
       <c r="B40" t="n">
-        <v>78788</v>
+        <v>90955</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4618,25 +4618,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4646,10 +4646,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465809</v>
+        <v>465849</v>
       </c>
       <c r="R40" t="n">
-        <v>6798627</v>
+        <v>6798130</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4708,10 +4708,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123913311</v>
+        <v>123913517</v>
       </c>
       <c r="B41" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4724,21 +4724,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4748,10 +4748,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>465842</v>
+        <v>465837</v>
       </c>
       <c r="R41" t="n">
-        <v>6798116</v>
+        <v>6798096</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4810,10 +4810,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123913406</v>
+        <v>123913473</v>
       </c>
       <c r="B42" t="n">
-        <v>91150</v>
+        <v>78788</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4822,25 +4822,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>465872</v>
+        <v>465720</v>
       </c>
       <c r="R42" t="n">
-        <v>6798093</v>
+        <v>6798523</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4912,7 +4912,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123876771</v>
+        <v>123913430</v>
       </c>
       <c r="B43" t="n">
         <v>78788</v>
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465815</v>
+        <v>465947</v>
       </c>
       <c r="R43" t="n">
-        <v>6798172</v>
+        <v>6798479</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4990,11 +4990,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Garnlav bakom björnide, samt i en radie av ca 30 meter.  Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5007,22 +5002,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123913451</v>
+        <v>123913266</v>
       </c>
       <c r="B44" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5035,21 +5030,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5059,10 +5054,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465838</v>
+        <v>465839</v>
       </c>
       <c r="R44" t="n">
-        <v>6798591</v>
+        <v>6798559</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5121,10 +5116,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123913434</v>
+        <v>123913309</v>
       </c>
       <c r="B45" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5137,21 +5132,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5161,10 +5156,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465938</v>
+        <v>465845</v>
       </c>
       <c r="R45" t="n">
-        <v>6798529</v>
+        <v>6798127</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5223,10 +5218,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123913269</v>
+        <v>123913462</v>
       </c>
       <c r="B46" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5239,21 +5234,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5263,10 +5258,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465705</v>
+        <v>465782</v>
       </c>
       <c r="R46" t="n">
-        <v>6798564</v>
+        <v>6798650</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5325,10 +5320,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123913315</v>
+        <v>123913260</v>
       </c>
       <c r="B47" t="n">
-        <v>78820</v>
+        <v>74879</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5341,21 +5336,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5365,10 +5360,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465899</v>
+        <v>465830</v>
       </c>
       <c r="R47" t="n">
-        <v>6798123</v>
+        <v>6798623</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5427,10 +5422,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123913443</v>
+        <v>123913258</v>
       </c>
       <c r="B48" t="n">
-        <v>78788</v>
+        <v>74879</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5443,21 +5438,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5467,10 +5462,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>465863</v>
+        <v>465915</v>
       </c>
       <c r="R48" t="n">
-        <v>6798532</v>
+        <v>6798548</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5529,7 +5524,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123913438</v>
+        <v>123913434</v>
       </c>
       <c r="B49" t="n">
         <v>78788</v>
@@ -5569,10 +5564,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>465904</v>
+        <v>465938</v>
       </c>
       <c r="R49" t="n">
-        <v>6798521</v>
+        <v>6798529</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5631,7 +5626,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123913448</v>
+        <v>123913475</v>
       </c>
       <c r="B50" t="n">
         <v>78788</v>
@@ -5671,10 +5666,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>465839</v>
+        <v>465719</v>
       </c>
       <c r="R50" t="n">
-        <v>6798559</v>
+        <v>6798495</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5733,7 +5728,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123913502</v>
+        <v>123913532</v>
       </c>
       <c r="B51" t="n">
         <v>78788</v>
@@ -5773,10 +5768,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>465783</v>
+        <v>465912</v>
       </c>
       <c r="R51" t="n">
-        <v>6798169</v>
+        <v>6798108</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5835,7 +5830,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123913519</v>
+        <v>123913498</v>
       </c>
       <c r="B52" t="n">
         <v>78788</v>
@@ -5875,10 +5870,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>465865</v>
+        <v>465746</v>
       </c>
       <c r="R52" t="n">
-        <v>6798133</v>
+        <v>6798258</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5937,10 +5932,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123913432</v>
+        <v>123913277</v>
       </c>
       <c r="B53" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5953,21 +5948,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5977,10 +5972,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>465943</v>
+        <v>465709</v>
       </c>
       <c r="R53" t="n">
-        <v>6798495</v>
+        <v>6798426</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6039,10 +6034,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123913249</v>
+        <v>123913453</v>
       </c>
       <c r="B54" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6055,21 +6050,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6079,10 +6074,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>465757</v>
+        <v>465833</v>
       </c>
       <c r="R54" t="n">
-        <v>6798402</v>
+        <v>6798603</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6141,10 +6136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123913564</v>
+        <v>123913317</v>
       </c>
       <c r="B55" t="n">
-        <v>57491</v>
+        <v>78820</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6157,39 +6152,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>465737</v>
+        <v>465913</v>
       </c>
       <c r="R55" t="n">
-        <v>6798286</v>
+        <v>6798106</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6224,11 +6214,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Spår efter födosök</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6246,17 +6231,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123913307</v>
+        <v>123913500</v>
       </c>
       <c r="B56" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6269,21 +6254,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6293,10 +6278,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>465884</v>
+        <v>465780</v>
       </c>
       <c r="R56" t="n">
-        <v>6798130</v>
+        <v>6798219</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6355,7 +6340,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123913487</v>
+        <v>123913443</v>
       </c>
       <c r="B57" t="n">
         <v>78788</v>
@@ -6395,10 +6380,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>465720</v>
+        <v>465863</v>
       </c>
       <c r="R57" t="n">
-        <v>6798411</v>
+        <v>6798532</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6457,7 +6442,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123913450</v>
+        <v>123913480</v>
       </c>
       <c r="B58" t="n">
         <v>78788</v>
@@ -6497,10 +6482,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>465835</v>
+        <v>465696</v>
       </c>
       <c r="R58" t="n">
-        <v>6798579</v>
+        <v>6798479</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6559,10 +6544,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123913327</v>
+        <v>123913438</v>
       </c>
       <c r="B59" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6575,21 +6560,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6599,10 +6584,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>465779</v>
+        <v>465904</v>
       </c>
       <c r="R59" t="n">
-        <v>6798140</v>
+        <v>6798521</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6661,7 +6646,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123913472</v>
+        <v>123913464</v>
       </c>
       <c r="B60" t="n">
         <v>78788</v>
@@ -6701,10 +6686,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>465710</v>
+        <v>465767</v>
       </c>
       <c r="R60" t="n">
-        <v>6798561</v>
+        <v>6798617</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6763,7 +6748,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123913496</v>
+        <v>123913522</v>
       </c>
       <c r="B61" t="n">
         <v>78788</v>
@@ -6803,10 +6788,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>465749</v>
+        <v>465842</v>
       </c>
       <c r="R61" t="n">
-        <v>6798268</v>
+        <v>6798113</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6865,7 +6850,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123913276</v>
+        <v>123913287</v>
       </c>
       <c r="B62" t="n">
         <v>78820</v>
@@ -6905,10 +6890,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>465694</v>
+        <v>465786</v>
       </c>
       <c r="R62" t="n">
-        <v>6798446</v>
+        <v>6798207</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6967,10 +6952,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123913374</v>
+        <v>123913483</v>
       </c>
       <c r="B63" t="n">
-        <v>80741</v>
+        <v>78788</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6983,21 +6968,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7007,10 +6992,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465857</v>
+        <v>465694</v>
       </c>
       <c r="R63" t="n">
-        <v>6798531</v>
+        <v>6798446</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7069,7 +7054,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123913309</v>
+        <v>123913280</v>
       </c>
       <c r="B64" t="n">
         <v>78820</v>
@@ -7109,10 +7094,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>465845</v>
+        <v>465753</v>
       </c>
       <c r="R64" t="n">
-        <v>6798127</v>
+        <v>6798400</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7171,7 +7156,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123913277</v>
+        <v>123913282</v>
       </c>
       <c r="B65" t="n">
         <v>78820</v>
@@ -7211,10 +7196,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465709</v>
+        <v>465748</v>
       </c>
       <c r="R65" t="n">
-        <v>6798426</v>
+        <v>6798396</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7273,10 +7258,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123913271</v>
+        <v>123913519</v>
       </c>
       <c r="B66" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7289,21 +7274,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7313,10 +7298,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465720</v>
+        <v>465865</v>
       </c>
       <c r="R66" t="n">
-        <v>6798523</v>
+        <v>6798133</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7375,10 +7360,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123913453</v>
+        <v>123913406</v>
       </c>
       <c r="B67" t="n">
-        <v>78788</v>
+        <v>91150</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7387,25 +7372,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7415,10 +7400,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465833</v>
+        <v>465872</v>
       </c>
       <c r="R67" t="n">
-        <v>6798603</v>
+        <v>6798093</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7477,10 +7462,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123913458</v>
+        <v>123913274</v>
       </c>
       <c r="B68" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7493,21 +7478,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7517,10 +7502,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465826</v>
+        <v>465705</v>
       </c>
       <c r="R68" t="n">
-        <v>6798611</v>
+        <v>6798509</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7579,7 +7564,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123913470</v>
+        <v>123913525</v>
       </c>
       <c r="B69" t="n">
         <v>78788</v>
@@ -7619,10 +7604,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465726</v>
+        <v>465837</v>
       </c>
       <c r="R69" t="n">
-        <v>6798570</v>
+        <v>6798100</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7681,10 +7666,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123913532</v>
+        <v>123913291</v>
       </c>
       <c r="B70" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7697,21 +7682,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7721,10 +7706,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>465912</v>
+        <v>465775</v>
       </c>
       <c r="R70" t="n">
-        <v>6798108</v>
+        <v>6798148</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7783,7 +7768,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123913436</v>
+        <v>123913489</v>
       </c>
       <c r="B71" t="n">
         <v>78788</v>
@@ -7823,10 +7808,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465927</v>
+        <v>465753</v>
       </c>
       <c r="R71" t="n">
-        <v>6798517</v>
+        <v>6798400</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7885,10 +7870,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123913446</v>
+        <v>123913271</v>
       </c>
       <c r="B72" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7901,21 +7886,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7925,10 +7910,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>465875</v>
+        <v>465720</v>
       </c>
       <c r="R72" t="n">
-        <v>6798559</v>
+        <v>6798523</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7987,10 +7972,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123913480</v>
+        <v>123913339</v>
       </c>
       <c r="B73" t="n">
-        <v>78788</v>
+        <v>57644</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8003,21 +7988,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8027,10 +8012,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>465696</v>
+        <v>465825</v>
       </c>
       <c r="R73" t="n">
-        <v>6798479</v>
+        <v>6798086</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8089,10 +8074,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123913266</v>
+        <v>123913504</v>
       </c>
       <c r="B74" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8105,21 +8090,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8129,10 +8114,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>465839</v>
+        <v>465787</v>
       </c>
       <c r="R74" t="n">
-        <v>6798559</v>
+        <v>6798158</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8191,10 +8176,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123913289</v>
+        <v>123913451</v>
       </c>
       <c r="B75" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8207,21 +8192,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8231,10 +8216,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>465786</v>
+        <v>465838</v>
       </c>
       <c r="R75" t="n">
-        <v>6798177</v>
+        <v>6798591</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8293,10 +8278,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123913285</v>
+        <v>123913441</v>
       </c>
       <c r="B76" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8309,21 +8294,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8333,10 +8318,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>465735</v>
+        <v>465893</v>
       </c>
       <c r="R76" t="n">
-        <v>6798291</v>
+        <v>6798543</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8395,10 +8380,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123913500</v>
+        <v>123913268</v>
       </c>
       <c r="B77" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8411,21 +8396,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8435,10 +8420,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>465780</v>
+        <v>465767</v>
       </c>
       <c r="R77" t="n">
-        <v>6798219</v>
+        <v>6798617</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8497,10 +8482,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123913490</v>
+        <v>123913564</v>
       </c>
       <c r="B78" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8513,34 +8498,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>465741</v>
+        <v>465737</v>
       </c>
       <c r="R78" t="n">
-        <v>6798376</v>
+        <v>6798286</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8575,6 +8565,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Spår efter födosök</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -8592,17 +8587,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123913339</v>
+        <v>123913330</v>
       </c>
       <c r="B79" t="n">
-        <v>57644</v>
+        <v>79377</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8615,21 +8610,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8639,10 +8634,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>465825</v>
+        <v>465815</v>
       </c>
       <c r="R79" t="n">
-        <v>6798086</v>
+        <v>6798097</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8701,10 +8696,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123913244</v>
+        <v>123913327</v>
       </c>
       <c r="B80" t="n">
-        <v>79406</v>
+        <v>79377</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8717,21 +8712,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8741,10 +8736,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>465933</v>
+        <v>465779</v>
       </c>
       <c r="R80" t="n">
-        <v>6798458</v>
+        <v>6798140</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8803,10 +8798,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123913334</v>
+        <v>123876771</v>
       </c>
       <c r="B81" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8819,21 +8814,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8843,10 +8838,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>465933</v>
+        <v>465815</v>
       </c>
       <c r="R81" t="n">
-        <v>6798526</v>
+        <v>6798172</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8881,6 +8876,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Garnlav bakom björnide, samt i en radie av ca 30 meter.  Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -8893,22 +8893,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123913464</v>
+        <v>123913311</v>
       </c>
       <c r="B82" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8921,21 +8921,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8945,10 +8945,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>465767</v>
+        <v>465842</v>
       </c>
       <c r="R82" t="n">
-        <v>6798617</v>
+        <v>6798116</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9007,7 +9007,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123913498</v>
+        <v>123913432</v>
       </c>
       <c r="B83" t="n">
         <v>78788</v>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>465746</v>
+        <v>465943</v>
       </c>
       <c r="R83" t="n">
-        <v>6798258</v>
+        <v>6798495</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9109,10 +9109,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123913247</v>
+        <v>123913436</v>
       </c>
       <c r="B84" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9125,21 +9125,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9149,10 +9149,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>465707</v>
+        <v>465927</v>
       </c>
       <c r="R84" t="n">
-        <v>6798475</v>
+        <v>6798517</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9211,10 +9211,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123913581</v>
+        <v>123913313</v>
       </c>
       <c r="B85" t="n">
-        <v>5176</v>
+        <v>78820</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9223,43 +9223,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>465737</v>
+        <v>465883</v>
       </c>
       <c r="R85" t="n">
-        <v>6798286</v>
+        <v>6798119</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9311,17 +9306,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123913572</v>
+        <v>123913285</v>
       </c>
       <c r="B86" t="n">
-        <v>78433</v>
+        <v>78820</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9334,21 +9329,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9358,10 +9353,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>465778</v>
+        <v>465735</v>
       </c>
       <c r="R86" t="n">
-        <v>6798141</v>
+        <v>6798291</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9413,17 +9408,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123913280</v>
+        <v>123913247</v>
       </c>
       <c r="B87" t="n">
-        <v>78820</v>
+        <v>79406</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9436,21 +9431,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9460,10 +9455,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>465753</v>
+        <v>465707</v>
       </c>
       <c r="R87" t="n">
-        <v>6798400</v>
+        <v>6798475</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9522,10 +9517,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123913313</v>
+        <v>123913496</v>
       </c>
       <c r="B88" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9538,21 +9533,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9562,10 +9557,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>465883</v>
+        <v>465749</v>
       </c>
       <c r="R88" t="n">
-        <v>6798119</v>
+        <v>6798268</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9624,10 +9619,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123913330</v>
+        <v>123913249</v>
       </c>
       <c r="B89" t="n">
-        <v>79377</v>
+        <v>79406</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9640,21 +9635,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9664,10 +9659,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>465815</v>
+        <v>465757</v>
       </c>
       <c r="R89" t="n">
-        <v>6798097</v>
+        <v>6798402</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9726,10 +9721,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123913258</v>
+        <v>123913276</v>
       </c>
       <c r="B90" t="n">
-        <v>74879</v>
+        <v>78820</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9742,21 +9737,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9766,10 +9761,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>465915</v>
+        <v>465694</v>
       </c>
       <c r="R90" t="n">
-        <v>6798548</v>
+        <v>6798446</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9828,10 +9823,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123913473</v>
+        <v>123913307</v>
       </c>
       <c r="B91" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9844,21 +9839,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9868,10 +9863,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>465720</v>
+        <v>465884</v>
       </c>
       <c r="R91" t="n">
-        <v>6798523</v>
+        <v>6798130</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9930,7 +9925,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123913494</v>
+        <v>123913450</v>
       </c>
       <c r="B92" t="n">
         <v>78788</v>
@@ -9970,10 +9965,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>465741</v>
+        <v>465835</v>
       </c>
       <c r="R92" t="n">
-        <v>6798286</v>
+        <v>6798579</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10032,7 +10027,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123913477</v>
+        <v>123913527</v>
       </c>
       <c r="B93" t="n">
         <v>78788</v>
@@ -10072,10 +10067,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>465708</v>
+        <v>465878</v>
       </c>
       <c r="R93" t="n">
-        <v>6798481</v>
+        <v>6798095</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10134,10 +10129,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123913287</v>
+        <v>123913244</v>
       </c>
       <c r="B94" t="n">
-        <v>78820</v>
+        <v>79406</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10150,21 +10145,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10174,10 +10169,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>465786</v>
+        <v>465933</v>
       </c>
       <c r="R94" t="n">
-        <v>6798207</v>
+        <v>6798458</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10236,10 +10231,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123913423</v>
+        <v>123913368</v>
       </c>
       <c r="B95" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10252,21 +10247,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10276,10 +10271,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>465920</v>
+        <v>465859</v>
       </c>
       <c r="R95" t="n">
-        <v>6798445</v>
+        <v>6798098</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10440,10 +10435,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123913260</v>
+        <v>123913581</v>
       </c>
       <c r="B97" t="n">
-        <v>74879</v>
+        <v>5176</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10452,38 +10447,43 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6440</v>
+        <v>100526</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>465830</v>
+        <v>465737</v>
       </c>
       <c r="R97" t="n">
-        <v>6798623</v>
+        <v>6798286</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10535,14 +10535,14 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123913489</v>
+        <v>123913472</v>
       </c>
       <c r="B98" t="n">
         <v>78788</v>
@@ -10582,10 +10582,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>465753</v>
+        <v>465710</v>
       </c>
       <c r="R98" t="n">
-        <v>6798400</v>
+        <v>6798561</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10644,7 +10644,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123913439</v>
+        <v>123913470</v>
       </c>
       <c r="B99" t="n">
         <v>78788</v>
@@ -10684,10 +10684,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>465919</v>
+        <v>465726</v>
       </c>
       <c r="R99" t="n">
-        <v>6798535</v>
+        <v>6798570</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10746,10 +10746,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123913282</v>
+        <v>123913572</v>
       </c>
       <c r="B100" t="n">
-        <v>78820</v>
+        <v>78433</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10762,21 +10762,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10786,10 +10786,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>465748</v>
+        <v>465778</v>
       </c>
       <c r="R100" t="n">
-        <v>6798396</v>
+        <v>6798141</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10841,17 +10841,17 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123913279</v>
+        <v>123913492</v>
       </c>
       <c r="B101" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10864,21 +10864,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10888,10 +10888,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>465720</v>
+        <v>465749</v>
       </c>
       <c r="R101" t="n">
-        <v>6798411</v>
+        <v>6798363</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10950,10 +10950,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123913485</v>
+        <v>123913306</v>
       </c>
       <c r="B102" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10966,21 +10966,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10990,10 +10990,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>465709</v>
+        <v>465841</v>
       </c>
       <c r="R102" t="n">
-        <v>6798426</v>
+        <v>6798109</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11052,7 +11052,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123913517</v>
+        <v>123913460</v>
       </c>
       <c r="B103" t="n">
         <v>78788</v>
@@ -11092,10 +11092,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>465837</v>
+        <v>465809</v>
       </c>
       <c r="R103" t="n">
-        <v>6798096</v>
+        <v>6798627</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11154,7 +11154,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>123913527</v>
+        <v>123913494</v>
       </c>
       <c r="B104" t="n">
         <v>78788</v>
@@ -11194,10 +11194,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>465878</v>
+        <v>465741</v>
       </c>
       <c r="R104" t="n">
-        <v>6798095</v>
+        <v>6798286</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11256,10 +11256,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123913504</v>
+        <v>123913256</v>
       </c>
       <c r="B105" t="n">
-        <v>78788</v>
+        <v>74879</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11272,21 +11272,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11296,10 +11296,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>465787</v>
+        <v>465939</v>
       </c>
       <c r="R105" t="n">
-        <v>6798158</v>
+        <v>6798534</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11358,7 +11358,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123913430</v>
+        <v>123913487</v>
       </c>
       <c r="B106" t="n">
         <v>78788</v>
@@ -11398,10 +11398,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>465947</v>
+        <v>465720</v>
       </c>
       <c r="R106" t="n">
-        <v>6798479</v>
+        <v>6798411</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11460,7 +11460,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123913483</v>
+        <v>123913446</v>
       </c>
       <c r="B107" t="n">
         <v>78788</v>
@@ -11500,10 +11500,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>465694</v>
+        <v>465875</v>
       </c>
       <c r="R107" t="n">
-        <v>6798446</v>
+        <v>6798559</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11562,10 +11562,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123913317</v>
+        <v>123913482</v>
       </c>
       <c r="B108" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11578,21 +11578,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11602,10 +11602,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>465913</v>
+        <v>465693</v>
       </c>
       <c r="R108" t="n">
-        <v>6798106</v>
+        <v>6798461</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11664,10 +11664,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123913251</v>
+        <v>123913515</v>
       </c>
       <c r="B109" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11680,21 +11680,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11704,10 +11704,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>465775</v>
+        <v>465825</v>
       </c>
       <c r="R109" t="n">
-        <v>6798229</v>
+        <v>6798086</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11766,7 +11766,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123913492</v>
+        <v>123913423</v>
       </c>
       <c r="B110" t="n">
         <v>78788</v>
@@ -11806,10 +11806,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>465749</v>
+        <v>465920</v>
       </c>
       <c r="R110" t="n">
-        <v>6798363</v>
+        <v>6798445</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11868,7 +11868,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123913522</v>
+        <v>123913439</v>
       </c>
       <c r="B111" t="n">
         <v>78788</v>
@@ -11908,10 +11908,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>465842</v>
+        <v>465919</v>
       </c>
       <c r="R111" t="n">
-        <v>6798113</v>
+        <v>6798535</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11970,10 +11970,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123913441</v>
+        <v>123913289</v>
       </c>
       <c r="B112" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11986,21 +11986,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12010,10 +12010,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>465893</v>
+        <v>465786</v>
       </c>
       <c r="R112" t="n">
-        <v>6798543</v>
+        <v>6798177</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12072,10 +12072,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>123913291</v>
+        <v>123913251</v>
       </c>
       <c r="B113" t="n">
-        <v>78820</v>
+        <v>79406</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12088,21 +12088,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12115,7 +12115,7 @@
         <v>465775</v>
       </c>
       <c r="R113" t="n">
-        <v>6798148</v>
+        <v>6798229</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12174,10 +12174,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123913268</v>
+        <v>123913262</v>
       </c>
       <c r="B114" t="n">
-        <v>78820</v>
+        <v>74879</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12190,21 +12190,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12214,10 +12214,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>465767</v>
+        <v>465764</v>
       </c>
       <c r="R114" t="n">
-        <v>6798617</v>
+        <v>6798656</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12276,10 +12276,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123913306</v>
+        <v>123913485</v>
       </c>
       <c r="B115" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12292,21 +12292,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12316,10 +12316,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>465841</v>
+        <v>465709</v>
       </c>
       <c r="R115" t="n">
-        <v>6798109</v>
+        <v>6798426</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12378,10 +12378,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123913515</v>
+        <v>123913269</v>
       </c>
       <c r="B116" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12394,21 +12394,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12418,10 +12418,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>465825</v>
+        <v>465705</v>
       </c>
       <c r="R116" t="n">
-        <v>6798086</v>
+        <v>6798564</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12480,10 +12480,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123913256</v>
+        <v>123913315</v>
       </c>
       <c r="B117" t="n">
-        <v>74879</v>
+        <v>78820</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12496,21 +12496,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12520,10 +12520,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>465939</v>
+        <v>465899</v>
       </c>
       <c r="R117" t="n">
-        <v>6798534</v>
+        <v>6798123</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12582,10 +12582,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123913475</v>
+        <v>123913279</v>
       </c>
       <c r="B118" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12598,21 +12598,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12622,10 +12622,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>465719</v>
+        <v>465720</v>
       </c>
       <c r="R118" t="n">
-        <v>6798495</v>
+        <v>6798411</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12684,10 +12684,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123913262</v>
+        <v>123913490</v>
       </c>
       <c r="B119" t="n">
-        <v>74879</v>
+        <v>78788</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12700,21 +12700,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12724,10 +12724,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>465764</v>
+        <v>465741</v>
       </c>
       <c r="R119" t="n">
-        <v>6798656</v>
+        <v>6798376</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12786,10 +12786,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>123913323</v>
+        <v>123913334</v>
       </c>
       <c r="B120" t="n">
-        <v>90955</v>
+        <v>90990</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12798,25 +12798,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>465849</v>
+        <v>465933</v>
       </c>
       <c r="R120" t="n">
-        <v>6798130</v>
+        <v>6798526</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12888,7 +12888,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123913462</v>
+        <v>123913458</v>
       </c>
       <c r="B121" t="n">
         <v>78788</v>
@@ -12928,10 +12928,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>465782</v>
+        <v>465826</v>
       </c>
       <c r="R121" t="n">
-        <v>6798650</v>
+        <v>6798611</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12990,10 +12990,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123913482</v>
+        <v>123913374</v>
       </c>
       <c r="B122" t="n">
-        <v>78788</v>
+        <v>80741</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13006,21 +13006,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13030,10 +13030,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>465693</v>
+        <v>465857</v>
       </c>
       <c r="R122" t="n">
-        <v>6798461</v>
+        <v>6798531</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13092,7 +13092,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123913525</v>
+        <v>123913477</v>
       </c>
       <c r="B123" t="n">
         <v>78788</v>
@@ -13132,10 +13132,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>465837</v>
+        <v>465708</v>
       </c>
       <c r="R123" t="n">
-        <v>6798100</v>
+        <v>6798481</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13194,10 +13194,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123913274</v>
+        <v>123913426</v>
       </c>
       <c r="B124" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13210,21 +13210,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13234,10 +13234,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>465705</v>
+        <v>465923</v>
       </c>
       <c r="R124" t="n">
-        <v>6798509</v>
+        <v>6798451</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13296,10 +13296,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>123913368</v>
+        <v>123913448</v>
       </c>
       <c r="B125" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13312,21 +13312,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13336,10 +13336,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>465859</v>
+        <v>465839</v>
       </c>
       <c r="R125" t="n">
-        <v>6798098</v>
+        <v>6798559</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>

--- a/artfynd/A 15853-2025 artfynd.xlsx
+++ b/artfynd/A 15853-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123877481</v>
+        <v>123876656</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465807</v>
+        <v>465833</v>
       </c>
       <c r="R2" t="n">
-        <v>6798288</v>
+        <v>6798204</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123876656</v>
+        <v>123878888</v>
       </c>
       <c r="B3" t="n">
         <v>78788</v>
@@ -818,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465833</v>
+        <v>465907</v>
       </c>
       <c r="R3" t="n">
-        <v>6798204</v>
+        <v>6798419</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,6 +855,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Garnlav i synfältet, 30 meter i radie. Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -872,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123878888</v>
+        <v>123877481</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465907</v>
+        <v>465807</v>
       </c>
       <c r="R4" t="n">
-        <v>6798419</v>
+        <v>6798288</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Garnlav i synfältet, 30 meter i radie. Miljöbilder</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -3046,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123876157</v>
+        <v>123877175</v>
       </c>
       <c r="B25" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3062,37 +3062,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465822</v>
+        <v>465790</v>
       </c>
       <c r="R25" t="n">
-        <v>6798106</v>
+        <v>6798239</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3122,6 +3122,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3136,19 +3141,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123877175</v>
+        <v>123877017</v>
       </c>
       <c r="B26" t="n">
         <v>79377</v>
@@ -3188,10 +3193,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465790</v>
+        <v>465805</v>
       </c>
       <c r="R26" t="n">
-        <v>6798239</v>
+        <v>6798194</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3228,7 +3233,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3255,10 +3260,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123877017</v>
+        <v>123876157</v>
       </c>
       <c r="B27" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3271,37 +3276,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465805</v>
+        <v>465822</v>
       </c>
       <c r="R27" t="n">
-        <v>6798194</v>
+        <v>6798106</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3331,11 +3336,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3350,12 +3350,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3464,7 +3464,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123876521</v>
+        <v>123878365</v>
       </c>
       <c r="B29" t="n">
         <v>78788</v>
@@ -3504,13 +3504,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465877</v>
+        <v>465783</v>
       </c>
       <c r="R29" t="n">
-        <v>6798138</v>
+        <v>6798386</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3554,19 +3554,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123878365</v>
+        <v>123876521</v>
       </c>
       <c r="B30" t="n">
         <v>78788</v>
@@ -3606,13 +3606,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465783</v>
+        <v>465877</v>
       </c>
       <c r="R30" t="n">
-        <v>6798386</v>
+        <v>6798138</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3656,12 +3656,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123876786</v>
+        <v>123876866</v>
       </c>
       <c r="B33" t="n">
-        <v>78525</v>
+        <v>56700</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3899,25 +3899,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3927,10 +3927,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465862</v>
+        <v>465848</v>
       </c>
       <c r="R33" t="n">
-        <v>6798219</v>
+        <v>6798245</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3963,6 +3963,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Nyare spillning.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3989,10 +3994,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123876866</v>
+        <v>123876786</v>
       </c>
       <c r="B34" t="n">
-        <v>56700</v>
+        <v>78525</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4001,25 +4006,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4029,10 +4034,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>465848</v>
+        <v>465862</v>
       </c>
       <c r="R34" t="n">
-        <v>6798245</v>
+        <v>6798219</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4065,11 +4070,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Nyare spillning.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4096,7 +4096,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123878561</v>
+        <v>123877370</v>
       </c>
       <c r="B35" t="n">
         <v>78788</v>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465804</v>
+        <v>465830</v>
       </c>
       <c r="R35" t="n">
-        <v>6798478</v>
+        <v>6798388</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4198,7 +4198,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123877138</v>
+        <v>123878561</v>
       </c>
       <c r="B36" t="n">
         <v>78788</v>
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465846</v>
+        <v>465804</v>
       </c>
       <c r="R36" t="n">
-        <v>6798341</v>
+        <v>6798478</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4300,7 +4300,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123877370</v>
+        <v>123877138</v>
       </c>
       <c r="B37" t="n">
         <v>78788</v>
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465830</v>
+        <v>465846</v>
       </c>
       <c r="R37" t="n">
-        <v>6798388</v>
+        <v>6798341</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -7564,10 +7564,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123913525</v>
+        <v>123913291</v>
       </c>
       <c r="B69" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7580,21 +7580,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7604,10 +7604,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465837</v>
+        <v>465775</v>
       </c>
       <c r="R69" t="n">
-        <v>6798100</v>
+        <v>6798148</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7666,10 +7666,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123913291</v>
+        <v>123913489</v>
       </c>
       <c r="B70" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7682,21 +7682,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7706,10 +7706,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>465775</v>
+        <v>465753</v>
       </c>
       <c r="R70" t="n">
-        <v>6798148</v>
+        <v>6798400</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7768,10 +7768,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123913489</v>
+        <v>123913271</v>
       </c>
       <c r="B71" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7784,21 +7784,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465753</v>
+        <v>465720</v>
       </c>
       <c r="R71" t="n">
-        <v>6798400</v>
+        <v>6798523</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7870,10 +7870,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123913271</v>
+        <v>123913525</v>
       </c>
       <c r="B72" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7886,21 +7886,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7910,10 +7910,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>465720</v>
+        <v>465837</v>
       </c>
       <c r="R72" t="n">
-        <v>6798523</v>
+        <v>6798100</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -12786,10 +12786,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>123913334</v>
+        <v>123913426</v>
       </c>
       <c r="B120" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12802,21 +12802,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>465933</v>
+        <v>465923</v>
       </c>
       <c r="R120" t="n">
-        <v>6798526</v>
+        <v>6798451</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12888,7 +12888,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123913458</v>
+        <v>123913448</v>
       </c>
       <c r="B121" t="n">
         <v>78788</v>
@@ -12928,10 +12928,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>465826</v>
+        <v>465839</v>
       </c>
       <c r="R121" t="n">
-        <v>6798611</v>
+        <v>6798559</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12990,10 +12990,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123913374</v>
+        <v>123913334</v>
       </c>
       <c r="B122" t="n">
-        <v>80741</v>
+        <v>90990</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13006,21 +13006,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13030,10 +13030,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>465857</v>
+        <v>465933</v>
       </c>
       <c r="R122" t="n">
-        <v>6798531</v>
+        <v>6798526</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13092,7 +13092,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123913477</v>
+        <v>123913458</v>
       </c>
       <c r="B123" t="n">
         <v>78788</v>
@@ -13132,10 +13132,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>465708</v>
+        <v>465826</v>
       </c>
       <c r="R123" t="n">
-        <v>6798481</v>
+        <v>6798611</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13194,10 +13194,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123913426</v>
+        <v>123913374</v>
       </c>
       <c r="B124" t="n">
-        <v>78788</v>
+        <v>80741</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13210,21 +13210,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13234,10 +13234,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>465923</v>
+        <v>465857</v>
       </c>
       <c r="R124" t="n">
-        <v>6798451</v>
+        <v>6798531</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13296,7 +13296,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>123913448</v>
+        <v>123913477</v>
       </c>
       <c r="B125" t="n">
         <v>78788</v>
@@ -13336,10 +13336,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>465839</v>
+        <v>465708</v>
       </c>
       <c r="R125" t="n">
-        <v>6798559</v>
+        <v>6798481</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>

--- a/artfynd/A 15853-2025 artfynd.xlsx
+++ b/artfynd/A 15853-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123876656</v>
+        <v>123876339</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465833</v>
+        <v>465823</v>
       </c>
       <c r="R2" t="n">
-        <v>6798204</v>
+        <v>6798111</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123878888</v>
+        <v>123876845</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465907</v>
+        <v>465832</v>
       </c>
       <c r="R3" t="n">
-        <v>6798419</v>
+        <v>6798231</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Garnlav i synfältet, 30 meter i radie. Miljöbilder</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123877481</v>
+        <v>123876691</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
+        <v>78820</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,42 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465807</v>
+        <v>465832</v>
       </c>
       <c r="R4" t="n">
-        <v>6798288</v>
+        <v>6798208</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,19 +969,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123877240</v>
+        <v>123876291</v>
       </c>
       <c r="B5" t="n">
         <v>78788</v>
@@ -1031,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465859</v>
+        <v>465806</v>
       </c>
       <c r="R5" t="n">
-        <v>6798332</v>
+        <v>6798100</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1093,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123876775</v>
+        <v>123877326</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,37 +1099,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>465799</v>
       </c>
       <c r="R6" t="n">
-        <v>6798205</v>
+        <v>6798259</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,19 +1183,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123876291</v>
+        <v>123876775</v>
       </c>
       <c r="B7" t="n">
         <v>78788</v>
@@ -1235,13 +1235,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465806</v>
+        <v>465799</v>
       </c>
       <c r="R7" t="n">
-        <v>6798100</v>
+        <v>6798205</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,19 +1285,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123878104</v>
+        <v>123878365</v>
       </c>
       <c r="B8" t="n">
         <v>78788</v>
@@ -1333,17 +1333,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465803</v>
+        <v>465783</v>
       </c>
       <c r="R8" t="n">
-        <v>6798395</v>
+        <v>6798386</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,19 +1387,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123878540</v>
+        <v>123878888</v>
       </c>
       <c r="B9" t="n">
         <v>78788</v>
@@ -1435,17 +1435,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465797</v>
+        <v>465907</v>
       </c>
       <c r="R9" t="n">
-        <v>6798473</v>
+        <v>6798419</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1475,6 +1475,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Garnlav i synfältet, 30 meter i radie. Miljöbilder</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1489,22 +1494,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123876339</v>
+        <v>123877304</v>
       </c>
       <c r="B10" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,13 +1546,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465823</v>
+        <v>465832</v>
       </c>
       <c r="R10" t="n">
-        <v>6798111</v>
+        <v>6798359</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1603,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123876806</v>
+        <v>123876586</v>
       </c>
       <c r="B11" t="n">
         <v>78788</v>
@@ -1639,17 +1644,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465847</v>
+        <v>465848</v>
       </c>
       <c r="R11" t="n">
-        <v>6798227</v>
+        <v>6798129</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1693,19 +1698,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123878630</v>
+        <v>123876878</v>
       </c>
       <c r="B12" t="n">
         <v>78788</v>
@@ -1741,17 +1746,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465884</v>
+        <v>465833</v>
       </c>
       <c r="R12" t="n">
-        <v>6798405</v>
+        <v>6798269</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1781,11 +1786,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1800,19 +1800,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123877433</v>
+        <v>123878561</v>
       </c>
       <c r="B13" t="n">
         <v>78788</v>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465854</v>
+        <v>465804</v>
       </c>
       <c r="R13" t="n">
-        <v>6798343</v>
+        <v>6798478</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123876143</v>
+        <v>123877433</v>
       </c>
       <c r="B14" t="n">
         <v>78788</v>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465821</v>
+        <v>465854</v>
       </c>
       <c r="R14" t="n">
-        <v>6798095</v>
+        <v>6798343</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123877850</v>
+        <v>123876656</v>
       </c>
       <c r="B15" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,13 +2056,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465863</v>
+        <v>465833</v>
       </c>
       <c r="R15" t="n">
-        <v>6798375</v>
+        <v>6798204</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123877884</v>
+        <v>123877481</v>
       </c>
       <c r="B16" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,34 +2134,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465816</v>
+        <v>465807</v>
       </c>
       <c r="R16" t="n">
-        <v>6798323</v>
+        <v>6798288</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,11 +2199,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2225,7 +2225,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123878210</v>
+        <v>123877138</v>
       </c>
       <c r="B17" t="n">
         <v>78788</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465813</v>
+        <v>465846</v>
       </c>
       <c r="R17" t="n">
-        <v>6798394</v>
+        <v>6798341</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2327,7 +2327,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123877582</v>
+        <v>123878540</v>
       </c>
       <c r="B18" t="n">
         <v>78788</v>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465745</v>
+        <v>465797</v>
       </c>
       <c r="R18" t="n">
-        <v>6798476</v>
+        <v>6798473</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2429,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123877304</v>
+        <v>123876786</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2445,21 +2445,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,13 +2469,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465832</v>
+        <v>465862</v>
       </c>
       <c r="R19" t="n">
-        <v>6798359</v>
+        <v>6798219</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123876845</v>
+        <v>123877884</v>
       </c>
       <c r="B20" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,37 +2547,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465832</v>
+        <v>465816</v>
       </c>
       <c r="R20" t="n">
-        <v>6798231</v>
+        <v>6798323</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2607,6 +2607,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2621,19 +2626,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123878923</v>
+        <v>123877582</v>
       </c>
       <c r="B21" t="n">
         <v>78788</v>
@@ -2673,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465911</v>
+        <v>465745</v>
       </c>
       <c r="R21" t="n">
-        <v>6798461</v>
+        <v>6798476</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2735,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123876691</v>
+        <v>123877240</v>
       </c>
       <c r="B22" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,21 +2756,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465832</v>
+        <v>465859</v>
       </c>
       <c r="R22" t="n">
-        <v>6798208</v>
+        <v>6798332</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2837,7 +2842,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123876586</v>
+        <v>123876157</v>
       </c>
       <c r="B23" t="n">
         <v>78788</v>
@@ -2873,17 +2878,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465848</v>
+        <v>465822</v>
       </c>
       <c r="R23" t="n">
-        <v>6798129</v>
+        <v>6798106</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2927,19 +2932,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123878436</v>
+        <v>123876806</v>
       </c>
       <c r="B24" t="n">
         <v>78788</v>
@@ -2975,17 +2980,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465800</v>
+        <v>465847</v>
       </c>
       <c r="R24" t="n">
-        <v>6798391</v>
+        <v>6798227</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3015,11 +3020,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Garnlav synligt ca 30 meters radie. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3034,22 +3034,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123877175</v>
+        <v>123876866</v>
       </c>
       <c r="B25" t="n">
-        <v>79377</v>
+        <v>56700</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3058,41 +3058,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465790</v>
+        <v>465848</v>
       </c>
       <c r="R25" t="n">
-        <v>6798239</v>
+        <v>6798245</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Nyare spillning.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3141,22 +3141,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123877017</v>
+        <v>123878104</v>
       </c>
       <c r="B26" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3169,21 +3169,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3193,13 +3193,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465805</v>
+        <v>465803</v>
       </c>
       <c r="R26" t="n">
-        <v>6798194</v>
+        <v>6798395</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3229,11 +3229,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3248,19 +3243,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123876157</v>
+        <v>123876521</v>
       </c>
       <c r="B27" t="n">
         <v>78788</v>
@@ -3300,13 +3295,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465822</v>
+        <v>465877</v>
       </c>
       <c r="R27" t="n">
-        <v>6798106</v>
+        <v>6798138</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3350,19 +3345,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123876733</v>
+        <v>123877248</v>
       </c>
       <c r="B28" t="n">
         <v>78788</v>
@@ -3398,17 +3393,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465844</v>
+        <v>465799</v>
       </c>
       <c r="R28" t="n">
-        <v>6798212</v>
+        <v>6798259</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3438,6 +3433,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3452,19 +3452,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123878365</v>
+        <v>123878923</v>
       </c>
       <c r="B29" t="n">
         <v>78788</v>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465783</v>
+        <v>465911</v>
       </c>
       <c r="R29" t="n">
-        <v>6798386</v>
+        <v>6798461</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123876521</v>
+        <v>123878630</v>
       </c>
       <c r="B30" t="n">
         <v>78788</v>
@@ -3602,14 +3602,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465877</v>
+        <v>465884</v>
       </c>
       <c r="R30" t="n">
-        <v>6798138</v>
+        <v>6798405</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3644,6 +3644,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3656,22 +3661,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123877326</v>
+        <v>123878210</v>
       </c>
       <c r="B31" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3684,42 +3689,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465799</v>
+        <v>465813</v>
       </c>
       <c r="R31" t="n">
-        <v>6798259</v>
+        <v>6798394</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3749,11 +3749,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3768,19 +3763,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123877248</v>
+        <v>123876143</v>
       </c>
       <c r="B32" t="n">
         <v>78788</v>
@@ -3816,17 +3811,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>465799</v>
+        <v>465821</v>
       </c>
       <c r="R32" t="n">
-        <v>6798259</v>
+        <v>6798095</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3856,11 +3851,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3875,22 +3865,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123876866</v>
+        <v>123877370</v>
       </c>
       <c r="B33" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3899,25 +3889,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3927,10 +3917,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465848</v>
+        <v>465830</v>
       </c>
       <c r="R33" t="n">
-        <v>6798245</v>
+        <v>6798388</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3963,11 +3953,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Nyare spillning.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3994,10 +3979,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123876786</v>
+        <v>123876733</v>
       </c>
       <c r="B34" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4010,21 +3995,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4034,10 +4019,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>465862</v>
+        <v>465844</v>
       </c>
       <c r="R34" t="n">
-        <v>6798219</v>
+        <v>6798212</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4096,7 +4081,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123877370</v>
+        <v>123878436</v>
       </c>
       <c r="B35" t="n">
         <v>78788</v>
@@ -4132,17 +4117,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465830</v>
+        <v>465800</v>
       </c>
       <c r="R35" t="n">
-        <v>6798388</v>
+        <v>6798391</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4172,6 +4157,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Garnlav synligt ca 30 meters radie. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4186,22 +4176,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123878561</v>
+        <v>123877175</v>
       </c>
       <c r="B36" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4214,37 +4204,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465804</v>
+        <v>465790</v>
       </c>
       <c r="R36" t="n">
-        <v>6798478</v>
+        <v>6798239</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4274,6 +4264,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4288,22 +4283,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123877138</v>
+        <v>123877850</v>
       </c>
       <c r="B37" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4316,21 +4311,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4340,10 +4335,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465846</v>
+        <v>465863</v>
       </c>
       <c r="R37" t="n">
-        <v>6798341</v>
+        <v>6798375</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4402,10 +4397,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123876878</v>
+        <v>123877017</v>
       </c>
       <c r="B38" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4418,37 +4413,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465833</v>
+        <v>465805</v>
       </c>
       <c r="R38" t="n">
-        <v>6798269</v>
+        <v>6798194</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4478,6 +4473,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4492,19 +4492,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123913502</v>
+        <v>123913432</v>
       </c>
       <c r="B39" t="n">
         <v>78788</v>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465783</v>
+        <v>465943</v>
       </c>
       <c r="R39" t="n">
-        <v>6798169</v>
+        <v>6798495</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4606,10 +4606,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123913323</v>
+        <v>123913262</v>
       </c>
       <c r="B40" t="n">
-        <v>90955</v>
+        <v>74879</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4618,25 +4618,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4646,10 +4646,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465849</v>
+        <v>465764</v>
       </c>
       <c r="R40" t="n">
-        <v>6798130</v>
+        <v>6798656</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4708,10 +4708,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123913517</v>
+        <v>123913282</v>
       </c>
       <c r="B41" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4724,21 +4724,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4748,10 +4748,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>465837</v>
+        <v>465748</v>
       </c>
       <c r="R41" t="n">
-        <v>6798096</v>
+        <v>6798396</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4810,7 +4810,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123913473</v>
+        <v>123913453</v>
       </c>
       <c r="B42" t="n">
         <v>78788</v>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>465720</v>
+        <v>465833</v>
       </c>
       <c r="R42" t="n">
-        <v>6798523</v>
+        <v>6798603</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5014,10 +5014,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123913266</v>
+        <v>123913249</v>
       </c>
       <c r="B44" t="n">
-        <v>78820</v>
+        <v>79406</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465839</v>
+        <v>465757</v>
       </c>
       <c r="R44" t="n">
-        <v>6798559</v>
+        <v>6798402</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5116,10 +5116,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123913309</v>
+        <v>123913564</v>
       </c>
       <c r="B45" t="n">
-        <v>78820</v>
+        <v>57491</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5132,34 +5132,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465845</v>
+        <v>465737</v>
       </c>
       <c r="R45" t="n">
-        <v>6798127</v>
+        <v>6798286</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5194,6 +5199,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spår efter födosök</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5211,17 +5221,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123913462</v>
+        <v>123913311</v>
       </c>
       <c r="B46" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5234,21 +5244,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5258,10 +5268,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465782</v>
+        <v>465842</v>
       </c>
       <c r="R46" t="n">
-        <v>6798650</v>
+        <v>6798116</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5320,10 +5330,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123913260</v>
+        <v>123913280</v>
       </c>
       <c r="B47" t="n">
-        <v>74879</v>
+        <v>78820</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5336,21 +5346,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5360,10 +5370,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465830</v>
+        <v>465753</v>
       </c>
       <c r="R47" t="n">
-        <v>6798623</v>
+        <v>6798400</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5422,10 +5432,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123913258</v>
+        <v>123913368</v>
       </c>
       <c r="B48" t="n">
-        <v>74879</v>
+        <v>78525</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5438,21 +5448,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5462,10 +5472,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>465915</v>
+        <v>465859</v>
       </c>
       <c r="R48" t="n">
-        <v>6798548</v>
+        <v>6798098</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5524,7 +5534,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123913434</v>
+        <v>123913446</v>
       </c>
       <c r="B49" t="n">
         <v>78788</v>
@@ -5564,10 +5574,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>465938</v>
+        <v>465875</v>
       </c>
       <c r="R49" t="n">
-        <v>6798529</v>
+        <v>6798559</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5626,10 +5636,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123913475</v>
+        <v>123913334</v>
       </c>
       <c r="B50" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5642,21 +5652,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5666,10 +5676,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>465719</v>
+        <v>465933</v>
       </c>
       <c r="R50" t="n">
-        <v>6798495</v>
+        <v>6798526</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5728,10 +5738,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123913532</v>
+        <v>123913406</v>
       </c>
       <c r="B51" t="n">
-        <v>78788</v>
+        <v>91150</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5740,25 +5750,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5768,10 +5778,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>465912</v>
+        <v>465872</v>
       </c>
       <c r="R51" t="n">
-        <v>6798108</v>
+        <v>6798093</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5830,7 +5840,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123913498</v>
+        <v>123913504</v>
       </c>
       <c r="B52" t="n">
         <v>78788</v>
@@ -5870,10 +5880,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>465746</v>
+        <v>465787</v>
       </c>
       <c r="R52" t="n">
-        <v>6798258</v>
+        <v>6798158</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5932,10 +5942,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123913277</v>
+        <v>123913256</v>
       </c>
       <c r="B53" t="n">
-        <v>78820</v>
+        <v>74879</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5948,21 +5958,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5972,10 +5982,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>465709</v>
+        <v>465939</v>
       </c>
       <c r="R53" t="n">
-        <v>6798426</v>
+        <v>6798534</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6034,7 +6044,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123913453</v>
+        <v>123913472</v>
       </c>
       <c r="B54" t="n">
         <v>78788</v>
@@ -6074,10 +6084,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>465833</v>
+        <v>465710</v>
       </c>
       <c r="R54" t="n">
-        <v>6798603</v>
+        <v>6798561</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6136,10 +6146,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123913317</v>
+        <v>123913423</v>
       </c>
       <c r="B55" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6152,21 +6162,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6176,10 +6186,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>465913</v>
+        <v>465920</v>
       </c>
       <c r="R55" t="n">
-        <v>6798106</v>
+        <v>6798445</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6238,7 +6248,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123913500</v>
+        <v>123913483</v>
       </c>
       <c r="B56" t="n">
         <v>78788</v>
@@ -6278,10 +6288,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>465780</v>
+        <v>465694</v>
       </c>
       <c r="R56" t="n">
-        <v>6798219</v>
+        <v>6798446</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6340,7 +6350,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123913443</v>
+        <v>123913500</v>
       </c>
       <c r="B57" t="n">
         <v>78788</v>
@@ -6380,10 +6390,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>465863</v>
+        <v>465780</v>
       </c>
       <c r="R57" t="n">
-        <v>6798532</v>
+        <v>6798219</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6442,10 +6452,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123913480</v>
+        <v>123913268</v>
       </c>
       <c r="B58" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6458,21 +6468,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6482,10 +6492,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>465696</v>
+        <v>465767</v>
       </c>
       <c r="R58" t="n">
-        <v>6798479</v>
+        <v>6798617</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6544,7 +6554,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123913438</v>
+        <v>123913475</v>
       </c>
       <c r="B59" t="n">
         <v>78788</v>
@@ -6584,10 +6594,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>465904</v>
+        <v>465719</v>
       </c>
       <c r="R59" t="n">
-        <v>6798521</v>
+        <v>6798495</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6646,7 +6656,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123913464</v>
+        <v>123913448</v>
       </c>
       <c r="B60" t="n">
         <v>78788</v>
@@ -6686,10 +6696,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>465767</v>
+        <v>465839</v>
       </c>
       <c r="R60" t="n">
-        <v>6798617</v>
+        <v>6798559</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6748,7 +6758,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123913522</v>
+        <v>123913460</v>
       </c>
       <c r="B61" t="n">
         <v>78788</v>
@@ -6788,10 +6798,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>465842</v>
+        <v>465809</v>
       </c>
       <c r="R61" t="n">
-        <v>6798113</v>
+        <v>6798627</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6850,10 +6860,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123913287</v>
+        <v>123913489</v>
       </c>
       <c r="B62" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6866,21 +6876,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6890,10 +6900,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>465786</v>
+        <v>465753</v>
       </c>
       <c r="R62" t="n">
-        <v>6798207</v>
+        <v>6798400</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6952,10 +6962,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123913483</v>
+        <v>123913247</v>
       </c>
       <c r="B63" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6968,21 +6978,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6992,10 +7002,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465694</v>
+        <v>465707</v>
       </c>
       <c r="R63" t="n">
-        <v>6798446</v>
+        <v>6798475</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7054,10 +7064,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123913280</v>
+        <v>123913494</v>
       </c>
       <c r="B64" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7070,21 +7080,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7094,10 +7104,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>465753</v>
+        <v>465741</v>
       </c>
       <c r="R64" t="n">
-        <v>6798400</v>
+        <v>6798286</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7156,10 +7166,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123913282</v>
+        <v>123913438</v>
       </c>
       <c r="B65" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7172,21 +7182,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7196,10 +7206,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465748</v>
+        <v>465904</v>
       </c>
       <c r="R65" t="n">
-        <v>6798396</v>
+        <v>6798521</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7258,7 +7268,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123913519</v>
+        <v>123913490</v>
       </c>
       <c r="B66" t="n">
         <v>78788</v>
@@ -7298,10 +7308,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465865</v>
+        <v>465741</v>
       </c>
       <c r="R66" t="n">
-        <v>6798133</v>
+        <v>6798376</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7360,10 +7370,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123913406</v>
+        <v>123913277</v>
       </c>
       <c r="B67" t="n">
-        <v>91150</v>
+        <v>78820</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7372,25 +7382,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1503</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7400,10 +7410,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465872</v>
+        <v>465709</v>
       </c>
       <c r="R67" t="n">
-        <v>6798093</v>
+        <v>6798426</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7462,10 +7472,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123913274</v>
+        <v>123913374</v>
       </c>
       <c r="B68" t="n">
-        <v>78820</v>
+        <v>80741</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7478,21 +7488,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7502,10 +7512,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465705</v>
+        <v>465857</v>
       </c>
       <c r="R68" t="n">
-        <v>6798509</v>
+        <v>6798531</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7564,10 +7574,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123913291</v>
+        <v>123913482</v>
       </c>
       <c r="B69" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7580,21 +7590,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7604,10 +7614,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465775</v>
+        <v>465693</v>
       </c>
       <c r="R69" t="n">
-        <v>6798148</v>
+        <v>6798461</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7666,7 +7676,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123913489</v>
+        <v>123913487</v>
       </c>
       <c r="B70" t="n">
         <v>78788</v>
@@ -7706,10 +7716,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>465753</v>
+        <v>465720</v>
       </c>
       <c r="R70" t="n">
-        <v>6798400</v>
+        <v>6798411</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7768,7 +7778,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123913271</v>
+        <v>123913287</v>
       </c>
       <c r="B71" t="n">
         <v>78820</v>
@@ -7808,10 +7818,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465720</v>
+        <v>465786</v>
       </c>
       <c r="R71" t="n">
-        <v>6798523</v>
+        <v>6798207</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7870,10 +7880,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123913525</v>
+        <v>123913271</v>
       </c>
       <c r="B72" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7886,21 +7896,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7910,10 +7920,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>465837</v>
+        <v>465720</v>
       </c>
       <c r="R72" t="n">
-        <v>6798100</v>
+        <v>6798523</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7972,10 +7982,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123913339</v>
+        <v>123913441</v>
       </c>
       <c r="B73" t="n">
-        <v>57644</v>
+        <v>78788</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7988,21 +7998,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8012,10 +8022,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>465825</v>
+        <v>465893</v>
       </c>
       <c r="R73" t="n">
-        <v>6798086</v>
+        <v>6798543</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8074,7 +8084,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123913504</v>
+        <v>123913496</v>
       </c>
       <c r="B74" t="n">
         <v>78788</v>
@@ -8114,10 +8124,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>465787</v>
+        <v>465749</v>
       </c>
       <c r="R74" t="n">
-        <v>6798158</v>
+        <v>6798268</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8176,10 +8186,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123913451</v>
+        <v>123913260</v>
       </c>
       <c r="B75" t="n">
-        <v>78788</v>
+        <v>74879</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8192,21 +8202,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8216,10 +8226,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>465838</v>
+        <v>465830</v>
       </c>
       <c r="R75" t="n">
-        <v>6798591</v>
+        <v>6798623</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8278,7 +8288,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123913441</v>
+        <v>123913458</v>
       </c>
       <c r="B76" t="n">
         <v>78788</v>
@@ -8318,10 +8328,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>465893</v>
+        <v>465826</v>
       </c>
       <c r="R76" t="n">
-        <v>6798543</v>
+        <v>6798611</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8380,10 +8390,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123913268</v>
+        <v>123913572</v>
       </c>
       <c r="B77" t="n">
-        <v>78820</v>
+        <v>78433</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8396,21 +8406,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8420,10 +8430,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>465767</v>
+        <v>465778</v>
       </c>
       <c r="R77" t="n">
-        <v>6798617</v>
+        <v>6798141</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8475,17 +8485,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123913564</v>
+        <v>123913323</v>
       </c>
       <c r="B78" t="n">
-        <v>57491</v>
+        <v>90955</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8494,43 +8504,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>465737</v>
+        <v>465849</v>
       </c>
       <c r="R78" t="n">
-        <v>6798286</v>
+        <v>6798130</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8565,11 +8570,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Spår efter födosök</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -8587,17 +8587,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123913330</v>
+        <v>123913313</v>
       </c>
       <c r="B79" t="n">
-        <v>79377</v>
+        <v>78820</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8610,21 +8610,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8634,10 +8634,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>465815</v>
+        <v>465883</v>
       </c>
       <c r="R79" t="n">
-        <v>6798097</v>
+        <v>6798119</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8696,10 +8696,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123913327</v>
+        <v>123913317</v>
       </c>
       <c r="B80" t="n">
-        <v>79377</v>
+        <v>78820</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8712,21 +8712,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>465779</v>
+        <v>465913</v>
       </c>
       <c r="R80" t="n">
-        <v>6798140</v>
+        <v>6798106</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8798,10 +8798,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123876771</v>
+        <v>123913306</v>
       </c>
       <c r="B81" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8814,21 +8814,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>465815</v>
+        <v>465841</v>
       </c>
       <c r="R81" t="n">
-        <v>6798172</v>
+        <v>6798109</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8876,11 +8876,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Garnlav bakom björnide, samt i en radie av ca 30 meter.  Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -8893,22 +8888,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123913311</v>
+        <v>123913532</v>
       </c>
       <c r="B82" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8921,21 +8916,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8945,10 +8940,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>465842</v>
+        <v>465912</v>
       </c>
       <c r="R82" t="n">
-        <v>6798116</v>
+        <v>6798108</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9007,7 +9002,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123913432</v>
+        <v>123913464</v>
       </c>
       <c r="B83" t="n">
         <v>78788</v>
@@ -9047,10 +9042,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>465943</v>
+        <v>465767</v>
       </c>
       <c r="R83" t="n">
-        <v>6798495</v>
+        <v>6798617</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9109,7 +9104,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123913436</v>
+        <v>123913450</v>
       </c>
       <c r="B84" t="n">
         <v>78788</v>
@@ -9149,10 +9144,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>465927</v>
+        <v>465835</v>
       </c>
       <c r="R84" t="n">
-        <v>6798517</v>
+        <v>6798579</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9211,10 +9206,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123913313</v>
+        <v>123913522</v>
       </c>
       <c r="B85" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9227,21 +9222,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9251,10 +9246,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>465883</v>
+        <v>465842</v>
       </c>
       <c r="R85" t="n">
-        <v>6798119</v>
+        <v>6798113</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9313,10 +9308,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123913285</v>
+        <v>123913439</v>
       </c>
       <c r="B86" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9329,21 +9324,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9353,10 +9348,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>465735</v>
+        <v>465919</v>
       </c>
       <c r="R86" t="n">
-        <v>6798291</v>
+        <v>6798535</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9415,10 +9410,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123913247</v>
+        <v>123913289</v>
       </c>
       <c r="B87" t="n">
-        <v>79406</v>
+        <v>78820</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9431,21 +9426,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9455,10 +9450,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>465707</v>
+        <v>465786</v>
       </c>
       <c r="R87" t="n">
-        <v>6798475</v>
+        <v>6798177</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9517,10 +9512,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123913496</v>
+        <v>123913315</v>
       </c>
       <c r="B88" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9533,21 +9528,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9557,10 +9552,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>465749</v>
+        <v>465899</v>
       </c>
       <c r="R88" t="n">
-        <v>6798268</v>
+        <v>6798123</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9619,10 +9614,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123913249</v>
+        <v>123913519</v>
       </c>
       <c r="B89" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9635,21 +9630,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9659,10 +9654,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>465757</v>
+        <v>465865</v>
       </c>
       <c r="R89" t="n">
-        <v>6798402</v>
+        <v>6798133</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9721,10 +9716,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123913276</v>
+        <v>123913473</v>
       </c>
       <c r="B90" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9737,21 +9732,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9761,10 +9756,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>465694</v>
+        <v>465720</v>
       </c>
       <c r="R90" t="n">
-        <v>6798446</v>
+        <v>6798523</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9823,10 +9818,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123913307</v>
+        <v>123913258</v>
       </c>
       <c r="B91" t="n">
-        <v>78820</v>
+        <v>74879</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9839,21 +9834,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9863,10 +9858,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>465884</v>
+        <v>465915</v>
       </c>
       <c r="R91" t="n">
-        <v>6798130</v>
+        <v>6798548</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9925,7 +9920,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123913450</v>
+        <v>123913515</v>
       </c>
       <c r="B92" t="n">
         <v>78788</v>
@@ -9965,10 +9960,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>465835</v>
+        <v>465825</v>
       </c>
       <c r="R92" t="n">
-        <v>6798579</v>
+        <v>6798086</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10027,10 +10022,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123913527</v>
+        <v>123913269</v>
       </c>
       <c r="B93" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10043,21 +10038,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10067,10 +10062,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>465878</v>
+        <v>465705</v>
       </c>
       <c r="R93" t="n">
-        <v>6798095</v>
+        <v>6798564</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10129,10 +10124,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123913244</v>
+        <v>123913327</v>
       </c>
       <c r="B94" t="n">
-        <v>79406</v>
+        <v>79377</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10145,21 +10140,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10169,10 +10164,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>465933</v>
+        <v>465779</v>
       </c>
       <c r="R94" t="n">
-        <v>6798458</v>
+        <v>6798140</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10231,10 +10226,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123913368</v>
+        <v>123913480</v>
       </c>
       <c r="B95" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10247,21 +10242,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10271,10 +10266,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>465859</v>
+        <v>465696</v>
       </c>
       <c r="R95" t="n">
-        <v>6798098</v>
+        <v>6798479</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10333,7 +10328,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123913530</v>
+        <v>123913517</v>
       </c>
       <c r="B96" t="n">
         <v>78788</v>
@@ -10373,10 +10368,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>465883</v>
+        <v>465837</v>
       </c>
       <c r="R96" t="n">
-        <v>6798119</v>
+        <v>6798096</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10435,10 +10430,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123913581</v>
+        <v>123913251</v>
       </c>
       <c r="B97" t="n">
-        <v>5176</v>
+        <v>79406</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10447,43 +10442,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>465737</v>
+        <v>465775</v>
       </c>
       <c r="R97" t="n">
-        <v>6798286</v>
+        <v>6798229</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10535,17 +10525,17 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123913472</v>
+        <v>123913285</v>
       </c>
       <c r="B98" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10558,21 +10548,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10582,10 +10572,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>465710</v>
+        <v>465735</v>
       </c>
       <c r="R98" t="n">
-        <v>6798561</v>
+        <v>6798291</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10644,10 +10634,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123913470</v>
+        <v>123913581</v>
       </c>
       <c r="B99" t="n">
-        <v>78788</v>
+        <v>5176</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10656,38 +10646,43 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>465726</v>
+        <v>465737</v>
       </c>
       <c r="R99" t="n">
-        <v>6798570</v>
+        <v>6798286</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10739,17 +10734,17 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123913572</v>
+        <v>123876771</v>
       </c>
       <c r="B100" t="n">
-        <v>78433</v>
+        <v>78788</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10762,21 +10757,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10786,10 +10781,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>465778</v>
+        <v>465815</v>
       </c>
       <c r="R100" t="n">
-        <v>6798141</v>
+        <v>6798172</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10824,6 +10819,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Garnlav bakom björnide, samt i en radie av ca 30 meter.  Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -10836,19 +10836,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123913492</v>
+        <v>123913451</v>
       </c>
       <c r="B101" t="n">
         <v>78788</v>
@@ -10888,10 +10888,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>465749</v>
+        <v>465838</v>
       </c>
       <c r="R101" t="n">
-        <v>6798363</v>
+        <v>6798591</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10950,10 +10950,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123913306</v>
+        <v>123913498</v>
       </c>
       <c r="B102" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10966,21 +10966,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10990,10 +10990,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>465841</v>
+        <v>465746</v>
       </c>
       <c r="R102" t="n">
-        <v>6798109</v>
+        <v>6798258</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11052,7 +11052,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123913460</v>
+        <v>123913530</v>
       </c>
       <c r="B103" t="n">
         <v>78788</v>
@@ -11092,10 +11092,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>465809</v>
+        <v>465883</v>
       </c>
       <c r="R103" t="n">
-        <v>6798627</v>
+        <v>6798119</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11154,10 +11154,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>123913494</v>
+        <v>123913274</v>
       </c>
       <c r="B104" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11170,21 +11170,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11194,10 +11194,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>465741</v>
+        <v>465705</v>
       </c>
       <c r="R104" t="n">
-        <v>6798286</v>
+        <v>6798509</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11256,10 +11256,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123913256</v>
+        <v>123913339</v>
       </c>
       <c r="B105" t="n">
-        <v>74879</v>
+        <v>57644</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11272,21 +11272,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11296,10 +11296,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>465939</v>
+        <v>465825</v>
       </c>
       <c r="R105" t="n">
-        <v>6798534</v>
+        <v>6798086</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11358,7 +11358,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123913487</v>
+        <v>123913485</v>
       </c>
       <c r="B106" t="n">
         <v>78788</v>
@@ -11398,10 +11398,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>465720</v>
+        <v>465709</v>
       </c>
       <c r="R106" t="n">
-        <v>6798411</v>
+        <v>6798426</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11460,7 +11460,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123913446</v>
+        <v>123913492</v>
       </c>
       <c r="B107" t="n">
         <v>78788</v>
@@ -11500,10 +11500,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>465875</v>
+        <v>465749</v>
       </c>
       <c r="R107" t="n">
-        <v>6798559</v>
+        <v>6798363</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11562,10 +11562,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123913482</v>
+        <v>123913244</v>
       </c>
       <c r="B108" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11578,21 +11578,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11602,10 +11602,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>465693</v>
+        <v>465933</v>
       </c>
       <c r="R108" t="n">
-        <v>6798461</v>
+        <v>6798458</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11664,7 +11664,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123913515</v>
+        <v>123913525</v>
       </c>
       <c r="B109" t="n">
         <v>78788</v>
@@ -11704,10 +11704,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>465825</v>
+        <v>465837</v>
       </c>
       <c r="R109" t="n">
-        <v>6798086</v>
+        <v>6798100</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11766,10 +11766,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123913423</v>
+        <v>123913291</v>
       </c>
       <c r="B110" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11782,21 +11782,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11806,10 +11806,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>465920</v>
+        <v>465775</v>
       </c>
       <c r="R110" t="n">
-        <v>6798445</v>
+        <v>6798148</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11868,10 +11868,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123913439</v>
+        <v>123913266</v>
       </c>
       <c r="B111" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11884,21 +11884,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11908,10 +11908,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>465919</v>
+        <v>465839</v>
       </c>
       <c r="R111" t="n">
-        <v>6798535</v>
+        <v>6798559</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11970,7 +11970,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123913289</v>
+        <v>123913276</v>
       </c>
       <c r="B112" t="n">
         <v>78820</v>
@@ -12010,10 +12010,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>465786</v>
+        <v>465694</v>
       </c>
       <c r="R112" t="n">
-        <v>6798177</v>
+        <v>6798446</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12072,10 +12072,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>123913251</v>
+        <v>123913307</v>
       </c>
       <c r="B113" t="n">
-        <v>79406</v>
+        <v>78820</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12088,21 +12088,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12112,10 +12112,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>465775</v>
+        <v>465884</v>
       </c>
       <c r="R113" t="n">
-        <v>6798229</v>
+        <v>6798130</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12174,10 +12174,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123913262</v>
+        <v>123913443</v>
       </c>
       <c r="B114" t="n">
-        <v>74879</v>
+        <v>78788</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12190,21 +12190,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12214,10 +12214,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>465764</v>
+        <v>465863</v>
       </c>
       <c r="R114" t="n">
-        <v>6798656</v>
+        <v>6798532</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12276,7 +12276,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123913485</v>
+        <v>123913434</v>
       </c>
       <c r="B115" t="n">
         <v>78788</v>
@@ -12316,10 +12316,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>465709</v>
+        <v>465938</v>
       </c>
       <c r="R115" t="n">
-        <v>6798426</v>
+        <v>6798529</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12378,10 +12378,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123913269</v>
+        <v>123913330</v>
       </c>
       <c r="B116" t="n">
-        <v>78820</v>
+        <v>79377</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12394,21 +12394,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12418,10 +12418,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>465705</v>
+        <v>465815</v>
       </c>
       <c r="R116" t="n">
-        <v>6798564</v>
+        <v>6798097</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12480,7 +12480,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123913315</v>
+        <v>123913309</v>
       </c>
       <c r="B117" t="n">
         <v>78820</v>
@@ -12520,10 +12520,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>465899</v>
+        <v>465845</v>
       </c>
       <c r="R117" t="n">
-        <v>6798123</v>
+        <v>6798127</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12684,7 +12684,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123913490</v>
+        <v>123913527</v>
       </c>
       <c r="B119" t="n">
         <v>78788</v>
@@ -12724,10 +12724,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>465741</v>
+        <v>465878</v>
       </c>
       <c r="R119" t="n">
-        <v>6798376</v>
+        <v>6798095</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12786,7 +12786,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>123913426</v>
+        <v>123913462</v>
       </c>
       <c r="B120" t="n">
         <v>78788</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>465923</v>
+        <v>465782</v>
       </c>
       <c r="R120" t="n">
-        <v>6798451</v>
+        <v>6798650</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12888,7 +12888,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123913448</v>
+        <v>123913426</v>
       </c>
       <c r="B121" t="n">
         <v>78788</v>
@@ -12928,10 +12928,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>465839</v>
+        <v>465923</v>
       </c>
       <c r="R121" t="n">
-        <v>6798559</v>
+        <v>6798451</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12990,10 +12990,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123913334</v>
+        <v>123913477</v>
       </c>
       <c r="B122" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13006,21 +13006,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13030,10 +13030,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>465933</v>
+        <v>465708</v>
       </c>
       <c r="R122" t="n">
-        <v>6798526</v>
+        <v>6798481</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13092,7 +13092,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123913458</v>
+        <v>123913502</v>
       </c>
       <c r="B123" t="n">
         <v>78788</v>
@@ -13132,10 +13132,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>465826</v>
+        <v>465783</v>
       </c>
       <c r="R123" t="n">
-        <v>6798611</v>
+        <v>6798169</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13194,10 +13194,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123913374</v>
+        <v>123913436</v>
       </c>
       <c r="B124" t="n">
-        <v>80741</v>
+        <v>78788</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13210,21 +13210,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13234,10 +13234,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>465857</v>
+        <v>465927</v>
       </c>
       <c r="R124" t="n">
-        <v>6798531</v>
+        <v>6798517</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13296,7 +13296,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>123913477</v>
+        <v>123913470</v>
       </c>
       <c r="B125" t="n">
         <v>78788</v>
@@ -13336,10 +13336,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>465708</v>
+        <v>465726</v>
       </c>
       <c r="R125" t="n">
-        <v>6798481</v>
+        <v>6798570</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>

--- a/artfynd/A 15853-2025 artfynd.xlsx
+++ b/artfynd/A 15853-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123877582</v>
+        <v>123877370</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465745</v>
+        <v>465830</v>
       </c>
       <c r="R2" t="n">
-        <v>6798476</v>
+        <v>6798388</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123876775</v>
+        <v>123878436</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465799</v>
+        <v>465800</v>
       </c>
       <c r="R3" t="n">
-        <v>6798205</v>
+        <v>6798391</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Garnlav synligt ca 30 meters radie. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,19 +872,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123878365</v>
+        <v>123878104</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -915,17 +920,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465783</v>
+        <v>465803</v>
       </c>
       <c r="R4" t="n">
-        <v>6798386</v>
+        <v>6798395</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123876786</v>
+        <v>123877433</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465862</v>
+        <v>465854</v>
       </c>
       <c r="R5" t="n">
-        <v>6798219</v>
+        <v>6798343</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123876845</v>
+        <v>123876291</v>
       </c>
       <c r="B6" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465832</v>
+        <v>465806</v>
       </c>
       <c r="R6" t="n">
-        <v>6798231</v>
+        <v>6798100</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123876656</v>
+        <v>123876845</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465833</v>
+        <v>465832</v>
       </c>
       <c r="R7" t="n">
-        <v>6798204</v>
+        <v>6798231</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1394,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123877370</v>
+        <v>123877884</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1430,17 +1435,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465830</v>
+        <v>465816</v>
       </c>
       <c r="R9" t="n">
-        <v>6798388</v>
+        <v>6798323</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1470,6 +1475,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1484,19 +1494,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123876878</v>
+        <v>123878888</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1532,17 +1542,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465833</v>
+        <v>465907</v>
       </c>
       <c r="R10" t="n">
-        <v>6798269</v>
+        <v>6798419</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1572,6 +1582,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Garnlav i synfältet, 30 meter i radie. Miljöbilder</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1586,22 +1601,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123878210</v>
+        <v>123876691</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465813</v>
+        <v>465832</v>
       </c>
       <c r="R11" t="n">
-        <v>6798394</v>
+        <v>6798208</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1700,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123877481</v>
+        <v>123878540</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,42 +1731,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465807</v>
+        <v>465797</v>
       </c>
       <c r="R12" t="n">
-        <v>6798288</v>
+        <v>6798473</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1795,19 +1805,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123877248</v>
+        <v>123876586</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1847,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465799</v>
+        <v>465848</v>
       </c>
       <c r="R13" t="n">
-        <v>6798259</v>
+        <v>6798129</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1883,11 +1893,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123876691</v>
+        <v>123878365</v>
       </c>
       <c r="B14" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465832</v>
+        <v>465783</v>
       </c>
       <c r="R14" t="n">
-        <v>6798208</v>
+        <v>6798386</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2016,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123877850</v>
+        <v>123876775</v>
       </c>
       <c r="B15" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,13 +2061,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465863</v>
+        <v>465799</v>
       </c>
       <c r="R15" t="n">
-        <v>6798375</v>
+        <v>6798205</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2106,19 +2111,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123876157</v>
+        <v>123877138</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2158,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465822</v>
+        <v>465846</v>
       </c>
       <c r="R16" t="n">
-        <v>6798106</v>
+        <v>6798341</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2220,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123876733</v>
+        <v>123876786</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2236,21 +2241,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465844</v>
+        <v>465862</v>
       </c>
       <c r="R17" t="n">
-        <v>6798212</v>
+        <v>6798219</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2322,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123877326</v>
+        <v>123877248</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,29 +2343,24 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2434,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123876339</v>
+        <v>123877582</v>
       </c>
       <c r="B19" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,21 +2450,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465823</v>
+        <v>465745</v>
       </c>
       <c r="R19" t="n">
-        <v>6798111</v>
+        <v>6798476</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123878923</v>
+        <v>123877481</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,37 +2552,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465911</v>
+        <v>465807</v>
       </c>
       <c r="R20" t="n">
-        <v>6798461</v>
+        <v>6798288</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2626,19 +2631,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123876586</v>
+        <v>123876143</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2674,17 +2679,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465848</v>
+        <v>465821</v>
       </c>
       <c r="R21" t="n">
-        <v>6798129</v>
+        <v>6798095</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2728,19 +2733,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123878540</v>
+        <v>123878923</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2780,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465797</v>
+        <v>465911</v>
       </c>
       <c r="R22" t="n">
-        <v>6798473</v>
+        <v>6798461</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2842,7 +2847,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123878104</v>
+        <v>123876157</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2878,17 +2883,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465803</v>
+        <v>465822</v>
       </c>
       <c r="R23" t="n">
-        <v>6798395</v>
+        <v>6798106</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2932,22 +2937,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123878561</v>
+        <v>123877326</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2960,37 +2965,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465804</v>
+        <v>465799</v>
       </c>
       <c r="R24" t="n">
-        <v>6798478</v>
+        <v>6798259</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3020,6 +3030,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3034,22 +3049,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123877138</v>
+        <v>123876339</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3062,21 +3077,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +3101,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465846</v>
+        <v>465823</v>
       </c>
       <c r="R25" t="n">
-        <v>6798341</v>
+        <v>6798111</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3148,10 +3163,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123876521</v>
+        <v>123877017</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3164,34 +3179,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465877</v>
+        <v>465805</v>
       </c>
       <c r="R26" t="n">
-        <v>6798138</v>
+        <v>6798194</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3226,6 +3241,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3238,22 +3258,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123877017</v>
+        <v>123877240</v>
       </c>
       <c r="B27" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,37 +3286,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465805</v>
+        <v>465859</v>
       </c>
       <c r="R27" t="n">
-        <v>6798194</v>
+        <v>6798332</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3326,11 +3346,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3345,22 +3360,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123876143</v>
+        <v>123877850</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3373,21 +3388,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3397,10 +3412,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465821</v>
+        <v>465863</v>
       </c>
       <c r="R28" t="n">
-        <v>6798095</v>
+        <v>6798375</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3459,7 +3474,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123878436</v>
+        <v>123878630</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3499,10 +3514,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465800</v>
+        <v>465884</v>
       </c>
       <c r="R29" t="n">
-        <v>6798391</v>
+        <v>6798405</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3539,7 +3554,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Garnlav synligt ca 30 meters radie. Miljöbilder.</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3566,10 +3581,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123876866</v>
+        <v>123876806</v>
       </c>
       <c r="B30" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3578,25 +3593,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3606,10 +3621,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465848</v>
+        <v>465847</v>
       </c>
       <c r="R30" t="n">
-        <v>6798245</v>
+        <v>6798227</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3642,11 +3657,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Nyare spillning.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3673,7 +3683,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123877884</v>
+        <v>123877304</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3709,14 +3719,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465816</v>
+        <v>465832</v>
       </c>
       <c r="R31" t="n">
-        <v>6798323</v>
+        <v>6798359</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3751,11 +3761,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3768,19 +3773,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123878888</v>
+        <v>123876656</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3816,14 +3821,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>465907</v>
+        <v>465833</v>
       </c>
       <c r="R32" t="n">
-        <v>6798419</v>
+        <v>6798204</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3858,11 +3863,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Garnlav i synfältet, 30 meter i radie. Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3875,19 +3875,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123876806</v>
+        <v>123876521</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -3927,13 +3927,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465847</v>
+        <v>465877</v>
       </c>
       <c r="R33" t="n">
-        <v>6798227</v>
+        <v>6798138</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3977,19 +3977,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123877240</v>
+        <v>123876733</v>
       </c>
       <c r="B34" t="n">
         <v>78810</v>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>465859</v>
+        <v>465844</v>
       </c>
       <c r="R34" t="n">
-        <v>6798332</v>
+        <v>6798212</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4091,7 +4091,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123877304</v>
+        <v>123876878</v>
       </c>
       <c r="B35" t="n">
         <v>78810</v>
@@ -4131,13 +4131,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465832</v>
+        <v>465833</v>
       </c>
       <c r="R35" t="n">
-        <v>6798359</v>
+        <v>6798269</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4181,22 +4181,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123877433</v>
+        <v>123876866</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4205,25 +4205,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465854</v>
+        <v>465848</v>
       </c>
       <c r="R36" t="n">
-        <v>6798343</v>
+        <v>6798245</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4269,6 +4269,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Nyare spillning.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4295,7 +4300,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123876291</v>
+        <v>123878210</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4335,10 +4340,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465806</v>
+        <v>465813</v>
       </c>
       <c r="R37" t="n">
-        <v>6798100</v>
+        <v>6798394</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4397,7 +4402,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123878630</v>
+        <v>123878561</v>
       </c>
       <c r="B38" t="n">
         <v>78810</v>
@@ -4433,17 +4438,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465884</v>
+        <v>465804</v>
       </c>
       <c r="R38" t="n">
-        <v>6798405</v>
+        <v>6798478</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4473,11 +4478,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4492,22 +4492,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123913426</v>
+        <v>123913271</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4520,21 +4520,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465923</v>
+        <v>465720</v>
       </c>
       <c r="R39" t="n">
-        <v>6798451</v>
+        <v>6798523</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4708,7 +4708,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123913489</v>
+        <v>123913492</v>
       </c>
       <c r="B41" t="n">
         <v>78810</v>
@@ -4748,10 +4748,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>465753</v>
+        <v>465749</v>
       </c>
       <c r="R41" t="n">
-        <v>6798400</v>
+        <v>6798363</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4810,7 +4810,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123913473</v>
+        <v>123913483</v>
       </c>
       <c r="B42" t="n">
         <v>78810</v>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>465720</v>
+        <v>465694</v>
       </c>
       <c r="R42" t="n">
-        <v>6798523</v>
+        <v>6798446</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4912,7 +4912,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123913448</v>
+        <v>123913500</v>
       </c>
       <c r="B43" t="n">
         <v>78810</v>
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465839</v>
+        <v>465780</v>
       </c>
       <c r="R43" t="n">
-        <v>6798559</v>
+        <v>6798219</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5014,10 +5014,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123913271</v>
+        <v>123913251</v>
       </c>
       <c r="B44" t="n">
-        <v>78842</v>
+        <v>79428</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465720</v>
+        <v>465775</v>
       </c>
       <c r="R44" t="n">
-        <v>6798523</v>
+        <v>6798229</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5116,10 +5116,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123913460</v>
+        <v>123913368</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5132,21 +5132,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5156,10 +5156,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465809</v>
+        <v>465859</v>
       </c>
       <c r="R45" t="n">
-        <v>6798627</v>
+        <v>6798098</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5218,10 +5218,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123913339</v>
+        <v>123913244</v>
       </c>
       <c r="B46" t="n">
-        <v>57666</v>
+        <v>79428</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5234,21 +5234,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5258,10 +5258,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465825</v>
+        <v>465933</v>
       </c>
       <c r="R46" t="n">
-        <v>6798086</v>
+        <v>6798458</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5320,7 +5320,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123913266</v>
+        <v>123913307</v>
       </c>
       <c r="B47" t="n">
         <v>78842</v>
@@ -5360,10 +5360,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465839</v>
+        <v>465884</v>
       </c>
       <c r="R47" t="n">
-        <v>6798559</v>
+        <v>6798130</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5422,7 +5422,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123913313</v>
+        <v>123913311</v>
       </c>
       <c r="B48" t="n">
         <v>78842</v>
@@ -5462,10 +5462,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>465883</v>
+        <v>465842</v>
       </c>
       <c r="R48" t="n">
-        <v>6798119</v>
+        <v>6798116</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5524,7 +5524,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123913443</v>
+        <v>123913487</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -5564,10 +5564,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>465863</v>
+        <v>465720</v>
       </c>
       <c r="R49" t="n">
-        <v>6798532</v>
+        <v>6798411</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5626,10 +5626,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123913279</v>
+        <v>123913489</v>
       </c>
       <c r="B50" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5642,21 +5642,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>465720</v>
+        <v>465753</v>
       </c>
       <c r="R50" t="n">
-        <v>6798411</v>
+        <v>6798400</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5728,7 +5728,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123913441</v>
+        <v>123913485</v>
       </c>
       <c r="B51" t="n">
         <v>78810</v>
@@ -5768,10 +5768,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>465893</v>
+        <v>465709</v>
       </c>
       <c r="R51" t="n">
-        <v>6798543</v>
+        <v>6798426</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5830,10 +5830,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123913334</v>
+        <v>123913522</v>
       </c>
       <c r="B52" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5846,21 +5846,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5870,10 +5870,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>465933</v>
+        <v>465842</v>
       </c>
       <c r="R52" t="n">
-        <v>6798526</v>
+        <v>6798113</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5932,10 +5932,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123913274</v>
+        <v>123913517</v>
       </c>
       <c r="B53" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5948,21 +5948,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5972,10 +5972,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>465705</v>
+        <v>465837</v>
       </c>
       <c r="R53" t="n">
-        <v>6798509</v>
+        <v>6798096</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6034,7 +6034,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123913490</v>
+        <v>123913446</v>
       </c>
       <c r="B54" t="n">
         <v>78810</v>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>465741</v>
+        <v>465875</v>
       </c>
       <c r="R54" t="n">
-        <v>6798376</v>
+        <v>6798559</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6136,7 +6136,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123913464</v>
+        <v>123913462</v>
       </c>
       <c r="B55" t="n">
         <v>78810</v>
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>465767</v>
+        <v>465782</v>
       </c>
       <c r="R55" t="n">
-        <v>6798617</v>
+        <v>6798650</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6238,7 +6238,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123913436</v>
+        <v>123913482</v>
       </c>
       <c r="B56" t="n">
         <v>78810</v>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>465927</v>
+        <v>465693</v>
       </c>
       <c r="R56" t="n">
-        <v>6798517</v>
+        <v>6798461</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6340,10 +6340,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123913434</v>
+        <v>123913572</v>
       </c>
       <c r="B57" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6356,21 +6356,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6380,10 +6380,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>465938</v>
+        <v>465778</v>
       </c>
       <c r="R57" t="n">
-        <v>6798529</v>
+        <v>6798141</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6435,14 +6435,14 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123913311</v>
+        <v>123913266</v>
       </c>
       <c r="B58" t="n">
         <v>78842</v>
@@ -6482,10 +6482,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>465842</v>
+        <v>465839</v>
       </c>
       <c r="R58" t="n">
-        <v>6798116</v>
+        <v>6798559</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6544,10 +6544,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123913251</v>
+        <v>123913436</v>
       </c>
       <c r="B59" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6560,21 +6560,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6584,10 +6584,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>465775</v>
+        <v>465927</v>
       </c>
       <c r="R59" t="n">
-        <v>6798229</v>
+        <v>6798517</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6646,7 +6646,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123913472</v>
+        <v>123913426</v>
       </c>
       <c r="B60" t="n">
         <v>78810</v>
@@ -6686,10 +6686,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>465710</v>
+        <v>465923</v>
       </c>
       <c r="R60" t="n">
-        <v>6798561</v>
+        <v>6798451</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6748,10 +6748,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123913262</v>
+        <v>123913458</v>
       </c>
       <c r="B61" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6764,21 +6764,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6788,10 +6788,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>465764</v>
+        <v>465826</v>
       </c>
       <c r="R61" t="n">
-        <v>6798656</v>
+        <v>6798611</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6850,10 +6850,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123913446</v>
+        <v>123913279</v>
       </c>
       <c r="B62" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6866,21 +6866,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6890,10 +6890,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>465875</v>
+        <v>465720</v>
       </c>
       <c r="R62" t="n">
-        <v>6798559</v>
+        <v>6798411</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6952,10 +6952,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123913462</v>
+        <v>123913274</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6968,21 +6968,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465782</v>
+        <v>465705</v>
       </c>
       <c r="R63" t="n">
-        <v>6798650</v>
+        <v>6798509</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7054,7 +7054,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123913477</v>
+        <v>123913502</v>
       </c>
       <c r="B64" t="n">
         <v>78810</v>
@@ -7094,10 +7094,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>465708</v>
+        <v>465783</v>
       </c>
       <c r="R64" t="n">
-        <v>6798481</v>
+        <v>6798169</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7156,10 +7156,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123913502</v>
+        <v>123913564</v>
       </c>
       <c r="B65" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7172,34 +7172,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465783</v>
+        <v>465737</v>
       </c>
       <c r="R65" t="n">
-        <v>6798169</v>
+        <v>6798286</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7234,6 +7239,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Spår efter födosök</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7251,17 +7261,17 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123913581</v>
+        <v>123913441</v>
       </c>
       <c r="B66" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7270,43 +7280,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465737</v>
+        <v>465893</v>
       </c>
       <c r="R66" t="n">
-        <v>6798286</v>
+        <v>6798543</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7358,17 +7363,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123913291</v>
+        <v>123913498</v>
       </c>
       <c r="B67" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7381,21 +7386,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7405,10 +7410,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465775</v>
+        <v>465746</v>
       </c>
       <c r="R67" t="n">
-        <v>6798148</v>
+        <v>6798258</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7467,10 +7472,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123913330</v>
+        <v>123913490</v>
       </c>
       <c r="B68" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7483,21 +7488,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7507,10 +7512,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465815</v>
+        <v>465741</v>
       </c>
       <c r="R68" t="n">
-        <v>6798097</v>
+        <v>6798376</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7569,10 +7574,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123913244</v>
+        <v>123913530</v>
       </c>
       <c r="B69" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7585,21 +7590,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7609,10 +7614,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465933</v>
+        <v>465883</v>
       </c>
       <c r="R69" t="n">
-        <v>6798458</v>
+        <v>6798119</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7671,7 +7676,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123913517</v>
+        <v>123913519</v>
       </c>
       <c r="B70" t="n">
         <v>78810</v>
@@ -7711,10 +7716,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>465837</v>
+        <v>465865</v>
       </c>
       <c r="R70" t="n">
-        <v>6798096</v>
+        <v>6798133</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7773,7 +7778,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123913532</v>
+        <v>123913443</v>
       </c>
       <c r="B71" t="n">
         <v>78810</v>
@@ -7813,10 +7818,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465912</v>
+        <v>465863</v>
       </c>
       <c r="R71" t="n">
-        <v>6798108</v>
+        <v>6798532</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7875,10 +7880,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123913515</v>
+        <v>123913256</v>
       </c>
       <c r="B72" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7891,21 +7896,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7915,10 +7920,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>465825</v>
+        <v>465939</v>
       </c>
       <c r="R72" t="n">
-        <v>6798086</v>
+        <v>6798534</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7977,10 +7982,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123913406</v>
+        <v>123913313</v>
       </c>
       <c r="B73" t="n">
-        <v>91172</v>
+        <v>78842</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7989,25 +7994,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1503</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8017,10 +8022,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>465872</v>
+        <v>465883</v>
       </c>
       <c r="R73" t="n">
-        <v>6798093</v>
+        <v>6798119</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8079,10 +8084,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123913368</v>
+        <v>123913289</v>
       </c>
       <c r="B74" t="n">
-        <v>78547</v>
+        <v>78842</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8095,21 +8100,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8119,10 +8124,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>465859</v>
+        <v>465786</v>
       </c>
       <c r="R74" t="n">
-        <v>6798098</v>
+        <v>6798177</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8181,10 +8186,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123913480</v>
+        <v>123913374</v>
       </c>
       <c r="B75" t="n">
-        <v>78810</v>
+        <v>80763</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8197,21 +8202,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8221,10 +8226,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>465696</v>
+        <v>465857</v>
       </c>
       <c r="R75" t="n">
-        <v>6798479</v>
+        <v>6798531</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8283,10 +8288,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123913487</v>
+        <v>123913406</v>
       </c>
       <c r="B76" t="n">
-        <v>78810</v>
+        <v>91172</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8295,25 +8300,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8323,10 +8328,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>465720</v>
+        <v>465872</v>
       </c>
       <c r="R76" t="n">
-        <v>6798411</v>
+        <v>6798093</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8385,7 +8390,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123913525</v>
+        <v>123913439</v>
       </c>
       <c r="B77" t="n">
         <v>78810</v>
@@ -8425,10 +8430,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>465837</v>
+        <v>465919</v>
       </c>
       <c r="R77" t="n">
-        <v>6798100</v>
+        <v>6798535</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8487,7 +8492,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123913530</v>
+        <v>123913434</v>
       </c>
       <c r="B78" t="n">
         <v>78810</v>
@@ -8527,10 +8532,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>465883</v>
+        <v>465938</v>
       </c>
       <c r="R78" t="n">
-        <v>6798119</v>
+        <v>6798529</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8589,7 +8594,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123913277</v>
+        <v>123913287</v>
       </c>
       <c r="B79" t="n">
         <v>78842</v>
@@ -8629,10 +8634,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>465709</v>
+        <v>465786</v>
       </c>
       <c r="R79" t="n">
-        <v>6798426</v>
+        <v>6798207</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8691,10 +8696,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123913492</v>
+        <v>123913306</v>
       </c>
       <c r="B80" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8707,21 +8712,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8731,10 +8736,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>465749</v>
+        <v>465841</v>
       </c>
       <c r="R80" t="n">
-        <v>6798363</v>
+        <v>6798109</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8793,10 +8798,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123913323</v>
+        <v>123876771</v>
       </c>
       <c r="B81" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8805,25 +8810,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8833,10 +8838,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>465849</v>
+        <v>465815</v>
       </c>
       <c r="R81" t="n">
-        <v>6798130</v>
+        <v>6798172</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8871,6 +8876,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Garnlav bakom björnide, samt i en radie av ca 30 meter.  Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -8883,19 +8893,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123913458</v>
+        <v>123913464</v>
       </c>
       <c r="B82" t="n">
         <v>78810</v>
@@ -8935,10 +8945,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>465826</v>
+        <v>465767</v>
       </c>
       <c r="R82" t="n">
-        <v>6798611</v>
+        <v>6798617</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8997,7 +9007,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123913438</v>
+        <v>123913472</v>
       </c>
       <c r="B83" t="n">
         <v>78810</v>
@@ -9037,10 +9047,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>465904</v>
+        <v>465710</v>
       </c>
       <c r="R83" t="n">
-        <v>6798521</v>
+        <v>6798561</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9099,10 +9109,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123913258</v>
+        <v>123913327</v>
       </c>
       <c r="B84" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9115,21 +9125,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9139,10 +9149,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>465915</v>
+        <v>465779</v>
       </c>
       <c r="R84" t="n">
-        <v>6798548</v>
+        <v>6798140</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9201,7 +9211,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123913269</v>
+        <v>123913268</v>
       </c>
       <c r="B85" t="n">
         <v>78842</v>
@@ -9241,10 +9251,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>465705</v>
+        <v>465767</v>
       </c>
       <c r="R85" t="n">
-        <v>6798564</v>
+        <v>6798617</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9303,7 +9313,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123913430</v>
+        <v>123913496</v>
       </c>
       <c r="B86" t="n">
         <v>78810</v>
@@ -9343,10 +9353,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>465947</v>
+        <v>465749</v>
       </c>
       <c r="R86" t="n">
-        <v>6798479</v>
+        <v>6798268</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9405,10 +9415,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123913315</v>
+        <v>123913477</v>
       </c>
       <c r="B87" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9421,21 +9431,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9445,10 +9455,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>465899</v>
+        <v>465708</v>
       </c>
       <c r="R87" t="n">
-        <v>6798123</v>
+        <v>6798481</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9507,7 +9517,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123913475</v>
+        <v>123913532</v>
       </c>
       <c r="B88" t="n">
         <v>78810</v>
@@ -9547,10 +9557,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>465719</v>
+        <v>465912</v>
       </c>
       <c r="R88" t="n">
-        <v>6798495</v>
+        <v>6798108</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9609,7 +9619,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123913527</v>
+        <v>123913473</v>
       </c>
       <c r="B89" t="n">
         <v>78810</v>
@@ -9649,10 +9659,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>465878</v>
+        <v>465720</v>
       </c>
       <c r="R89" t="n">
-        <v>6798095</v>
+        <v>6798523</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9711,10 +9721,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123876771</v>
+        <v>123913323</v>
       </c>
       <c r="B90" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9723,25 +9733,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9751,10 +9761,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>465815</v>
+        <v>465849</v>
       </c>
       <c r="R90" t="n">
-        <v>6798172</v>
+        <v>6798130</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9789,11 +9799,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Garnlav bakom björnide, samt i en radie av ca 30 meter.  Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -9806,22 +9811,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123913327</v>
+        <v>123913269</v>
       </c>
       <c r="B91" t="n">
-        <v>79399</v>
+        <v>78842</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9834,21 +9839,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9858,10 +9863,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>465779</v>
+        <v>465705</v>
       </c>
       <c r="R91" t="n">
-        <v>6798140</v>
+        <v>6798564</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9920,10 +9925,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123913572</v>
+        <v>123913280</v>
       </c>
       <c r="B92" t="n">
-        <v>78455</v>
+        <v>78842</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9936,21 +9941,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9960,10 +9965,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>465778</v>
+        <v>465753</v>
       </c>
       <c r="R92" t="n">
-        <v>6798141</v>
+        <v>6798400</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10015,17 +10020,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123913374</v>
+        <v>123913315</v>
       </c>
       <c r="B93" t="n">
-        <v>80763</v>
+        <v>78842</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10038,21 +10043,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1049</v>
+        <v>185</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10062,10 +10067,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>465857</v>
+        <v>465899</v>
       </c>
       <c r="R93" t="n">
-        <v>6798531</v>
+        <v>6798123</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10124,10 +10129,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123913256</v>
+        <v>123913460</v>
       </c>
       <c r="B94" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10140,21 +10145,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10164,10 +10169,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>465939</v>
+        <v>465809</v>
       </c>
       <c r="R94" t="n">
-        <v>6798534</v>
+        <v>6798627</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10226,10 +10231,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123913247</v>
+        <v>123913527</v>
       </c>
       <c r="B95" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10242,21 +10247,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10266,10 +10271,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>465707</v>
+        <v>465878</v>
       </c>
       <c r="R95" t="n">
-        <v>6798475</v>
+        <v>6798095</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10328,10 +10333,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123913289</v>
+        <v>123913330</v>
       </c>
       <c r="B96" t="n">
-        <v>78842</v>
+        <v>79399</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10344,21 +10349,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10368,10 +10373,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>465786</v>
+        <v>465815</v>
       </c>
       <c r="R96" t="n">
-        <v>6798177</v>
+        <v>6798097</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10430,10 +10435,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123913519</v>
+        <v>123913276</v>
       </c>
       <c r="B97" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10446,21 +10451,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10470,10 +10475,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>465865</v>
+        <v>465694</v>
       </c>
       <c r="R97" t="n">
-        <v>6798133</v>
+        <v>6798446</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10532,7 +10537,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123913483</v>
+        <v>123913448</v>
       </c>
       <c r="B98" t="n">
         <v>78810</v>
@@ -10572,10 +10577,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>465694</v>
+        <v>465839</v>
       </c>
       <c r="R98" t="n">
-        <v>6798446</v>
+        <v>6798559</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10634,10 +10639,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123913470</v>
+        <v>123913309</v>
       </c>
       <c r="B99" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10650,21 +10655,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10674,10 +10679,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>465726</v>
+        <v>465845</v>
       </c>
       <c r="R99" t="n">
-        <v>6798570</v>
+        <v>6798127</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10736,7 +10741,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123913307</v>
+        <v>123913277</v>
       </c>
       <c r="B100" t="n">
         <v>78842</v>
@@ -10776,10 +10781,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>465884</v>
+        <v>465709</v>
       </c>
       <c r="R100" t="n">
-        <v>6798130</v>
+        <v>6798426</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10838,10 +10843,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123913317</v>
+        <v>123913432</v>
       </c>
       <c r="B101" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10854,21 +10859,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10878,10 +10883,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>465913</v>
+        <v>465943</v>
       </c>
       <c r="R101" t="n">
-        <v>6798106</v>
+        <v>6798495</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10940,10 +10945,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123913453</v>
+        <v>123913260</v>
       </c>
       <c r="B102" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10956,21 +10961,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10980,10 +10985,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>465833</v>
+        <v>465830</v>
       </c>
       <c r="R102" t="n">
-        <v>6798603</v>
+        <v>6798623</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11042,10 +11047,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123913287</v>
+        <v>123913258</v>
       </c>
       <c r="B103" t="n">
-        <v>78842</v>
+        <v>74901</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11058,21 +11063,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11082,10 +11087,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>465786</v>
+        <v>465915</v>
       </c>
       <c r="R103" t="n">
-        <v>6798207</v>
+        <v>6798548</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11144,7 +11149,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>123913439</v>
+        <v>123913515</v>
       </c>
       <c r="B104" t="n">
         <v>78810</v>
@@ -11184,10 +11189,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>465919</v>
+        <v>465825</v>
       </c>
       <c r="R104" t="n">
-        <v>6798535</v>
+        <v>6798086</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11246,7 +11251,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123913494</v>
+        <v>123913430</v>
       </c>
       <c r="B105" t="n">
         <v>78810</v>
@@ -11286,10 +11291,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>465741</v>
+        <v>465947</v>
       </c>
       <c r="R105" t="n">
-        <v>6798286</v>
+        <v>6798479</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11348,7 +11353,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123913451</v>
+        <v>123913480</v>
       </c>
       <c r="B106" t="n">
         <v>78810</v>
@@ -11388,10 +11393,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>465838</v>
+        <v>465696</v>
       </c>
       <c r="R106" t="n">
-        <v>6798591</v>
+        <v>6798479</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11450,7 +11455,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123913485</v>
+        <v>123913423</v>
       </c>
       <c r="B107" t="n">
         <v>78810</v>
@@ -11490,10 +11495,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>465709</v>
+        <v>465920</v>
       </c>
       <c r="R107" t="n">
-        <v>6798426</v>
+        <v>6798445</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11552,10 +11557,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123913309</v>
+        <v>123913247</v>
       </c>
       <c r="B108" t="n">
-        <v>78842</v>
+        <v>79428</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11568,21 +11573,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11592,10 +11597,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>465845</v>
+        <v>465707</v>
       </c>
       <c r="R108" t="n">
-        <v>6798127</v>
+        <v>6798475</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11654,7 +11659,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123913482</v>
+        <v>123913494</v>
       </c>
       <c r="B109" t="n">
         <v>78810</v>
@@ -11694,10 +11699,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>465693</v>
+        <v>465741</v>
       </c>
       <c r="R109" t="n">
-        <v>6798461</v>
+        <v>6798286</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11756,10 +11761,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123913260</v>
+        <v>123913450</v>
       </c>
       <c r="B110" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11772,21 +11777,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11796,10 +11801,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>465830</v>
+        <v>465835</v>
       </c>
       <c r="R110" t="n">
-        <v>6798623</v>
+        <v>6798579</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11858,7 +11863,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123913496</v>
+        <v>123913475</v>
       </c>
       <c r="B111" t="n">
         <v>78810</v>
@@ -11898,10 +11903,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>465749</v>
+        <v>465719</v>
       </c>
       <c r="R111" t="n">
-        <v>6798268</v>
+        <v>6798495</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11960,10 +11965,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123913423</v>
+        <v>123913249</v>
       </c>
       <c r="B112" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11976,21 +11981,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12000,10 +12005,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>465920</v>
+        <v>465757</v>
       </c>
       <c r="R112" t="n">
-        <v>6798445</v>
+        <v>6798402</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12062,10 +12067,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>123913498</v>
+        <v>123913262</v>
       </c>
       <c r="B113" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12078,21 +12083,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12102,10 +12107,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>465746</v>
+        <v>465764</v>
       </c>
       <c r="R113" t="n">
-        <v>6798258</v>
+        <v>6798656</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12164,10 +12169,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123913306</v>
+        <v>123913453</v>
       </c>
       <c r="B114" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12180,21 +12185,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12204,10 +12209,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>465841</v>
+        <v>465833</v>
       </c>
       <c r="R114" t="n">
-        <v>6798109</v>
+        <v>6798603</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12266,7 +12271,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123913450</v>
+        <v>123913438</v>
       </c>
       <c r="B115" t="n">
         <v>78810</v>
@@ -12306,10 +12311,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>465835</v>
+        <v>465904</v>
       </c>
       <c r="R115" t="n">
-        <v>6798579</v>
+        <v>6798521</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12368,10 +12373,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123913249</v>
+        <v>123913525</v>
       </c>
       <c r="B116" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12384,21 +12389,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12408,10 +12413,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>465757</v>
+        <v>465837</v>
       </c>
       <c r="R116" t="n">
-        <v>6798402</v>
+        <v>6798100</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12470,10 +12475,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123913282</v>
+        <v>123913581</v>
       </c>
       <c r="B117" t="n">
-        <v>78842</v>
+        <v>5176</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12482,38 +12487,43 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>465748</v>
+        <v>465737</v>
       </c>
       <c r="R117" t="n">
-        <v>6798396</v>
+        <v>6798286</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12565,17 +12575,17 @@
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123913522</v>
+        <v>123913339</v>
       </c>
       <c r="B118" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12588,21 +12598,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12612,10 +12622,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>465842</v>
+        <v>465825</v>
       </c>
       <c r="R118" t="n">
-        <v>6798113</v>
+        <v>6798086</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12674,7 +12684,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123913276</v>
+        <v>123913282</v>
       </c>
       <c r="B119" t="n">
         <v>78842</v>
@@ -12714,10 +12724,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>465694</v>
+        <v>465748</v>
       </c>
       <c r="R119" t="n">
-        <v>6798446</v>
+        <v>6798396</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12776,10 +12786,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>123913432</v>
+        <v>123913285</v>
       </c>
       <c r="B120" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12792,21 +12802,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12816,10 +12826,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>465943</v>
+        <v>465735</v>
       </c>
       <c r="R120" t="n">
-        <v>6798495</v>
+        <v>6798291</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12878,10 +12888,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123913268</v>
+        <v>123913334</v>
       </c>
       <c r="B121" t="n">
-        <v>78842</v>
+        <v>91012</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12894,21 +12904,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12918,10 +12928,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>465767</v>
+        <v>465933</v>
       </c>
       <c r="R121" t="n">
-        <v>6798617</v>
+        <v>6798526</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12980,10 +12990,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123913285</v>
+        <v>123913451</v>
       </c>
       <c r="B122" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -12996,21 +13006,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13020,10 +13030,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>465735</v>
+        <v>465838</v>
       </c>
       <c r="R122" t="n">
-        <v>6798291</v>
+        <v>6798591</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13082,7 +13092,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123913500</v>
+        <v>123913470</v>
       </c>
       <c r="B123" t="n">
         <v>78810</v>
@@ -13122,10 +13132,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>465780</v>
+        <v>465726</v>
       </c>
       <c r="R123" t="n">
-        <v>6798219</v>
+        <v>6798570</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13184,7 +13194,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123913280</v>
+        <v>123913317</v>
       </c>
       <c r="B124" t="n">
         <v>78842</v>
@@ -13224,10 +13234,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>465753</v>
+        <v>465913</v>
       </c>
       <c r="R124" t="n">
-        <v>6798400</v>
+        <v>6798106</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13286,10 +13296,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>123913564</v>
+        <v>123913291</v>
       </c>
       <c r="B125" t="n">
-        <v>57513</v>
+        <v>78842</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13302,39 +13312,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>465737</v>
+        <v>465775</v>
       </c>
       <c r="R125" t="n">
-        <v>6798286</v>
+        <v>6798148</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13369,11 +13374,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Spår efter födosök</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>

--- a/artfynd/A 15853-2025 artfynd.xlsx
+++ b/artfynd/A 15853-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123877370</v>
+        <v>123877582</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465830</v>
+        <v>465745</v>
       </c>
       <c r="R2" t="n">
-        <v>6798388</v>
+        <v>6798476</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123878436</v>
+        <v>123877433</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465800</v>
+        <v>465854</v>
       </c>
       <c r="R3" t="n">
-        <v>6798391</v>
+        <v>6798343</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Garnlav synligt ca 30 meters radie. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,19 +867,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123878104</v>
+        <v>123878436</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -924,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465803</v>
+        <v>465800</v>
       </c>
       <c r="R4" t="n">
-        <v>6798395</v>
+        <v>6798391</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Garnlav synligt ca 30 meters radie. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,19 +974,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123877433</v>
+        <v>123878540</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465854</v>
+        <v>465797</v>
       </c>
       <c r="R5" t="n">
-        <v>6798343</v>
+        <v>6798473</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123876291</v>
+        <v>123876157</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465806</v>
+        <v>465822</v>
       </c>
       <c r="R6" t="n">
-        <v>6798100</v>
+        <v>6798106</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123876845</v>
+        <v>123876291</v>
       </c>
       <c r="B7" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465832</v>
+        <v>465806</v>
       </c>
       <c r="R7" t="n">
-        <v>6798231</v>
+        <v>6798100</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123877175</v>
+        <v>123876845</v>
       </c>
       <c r="B8" t="n">
-        <v>79399</v>
+        <v>78842</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,37 +1308,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465790</v>
+        <v>465832</v>
       </c>
       <c r="R8" t="n">
-        <v>6798239</v>
+        <v>6798231</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1368,11 +1368,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,19 +1382,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123877884</v>
+        <v>123878104</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1439,13 +1434,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465816</v>
+        <v>465803</v>
       </c>
       <c r="R9" t="n">
-        <v>6798323</v>
+        <v>6798395</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1475,11 +1470,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,19 +1484,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123878888</v>
+        <v>123876733</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1542,17 +1532,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465907</v>
+        <v>465844</v>
       </c>
       <c r="R10" t="n">
-        <v>6798419</v>
+        <v>6798212</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1582,11 +1572,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Garnlav i synfältet, 30 meter i radie. Miljöbilder</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,22 +1586,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123876691</v>
+        <v>123877481</v>
       </c>
       <c r="B11" t="n">
-        <v>78842</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,37 +1614,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465832</v>
+        <v>465807</v>
       </c>
       <c r="R11" t="n">
-        <v>6798208</v>
+        <v>6798288</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1703,22 +1693,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123878540</v>
+        <v>123877850</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465797</v>
+        <v>465863</v>
       </c>
       <c r="R12" t="n">
-        <v>6798473</v>
+        <v>6798375</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1817,7 +1807,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123876586</v>
+        <v>123877884</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1857,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465848</v>
+        <v>465816</v>
       </c>
       <c r="R13" t="n">
-        <v>6798129</v>
+        <v>6798323</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1893,6 +1883,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1919,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123878365</v>
+        <v>123877240</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1959,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465783</v>
+        <v>465859</v>
       </c>
       <c r="R14" t="n">
-        <v>6798386</v>
+        <v>6798332</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2021,7 +2016,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123876775</v>
+        <v>123877138</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2061,13 +2056,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465799</v>
+        <v>465846</v>
       </c>
       <c r="R15" t="n">
-        <v>6798205</v>
+        <v>6798341</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2111,19 +2106,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123877138</v>
+        <v>123877248</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2159,17 +2154,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465846</v>
+        <v>465799</v>
       </c>
       <c r="R16" t="n">
-        <v>6798341</v>
+        <v>6798259</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2199,6 +2194,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2213,12 +2213,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2327,7 +2327,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123877248</v>
+        <v>123878561</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2363,17 +2363,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465799</v>
+        <v>465804</v>
       </c>
       <c r="R18" t="n">
-        <v>6798259</v>
+        <v>6798478</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2403,11 +2403,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2422,19 +2417,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123877582</v>
+        <v>123878365</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2474,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465745</v>
+        <v>465783</v>
       </c>
       <c r="R19" t="n">
-        <v>6798476</v>
+        <v>6798386</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2536,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123877481</v>
+        <v>123877326</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,16 +2547,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2572,7 +2567,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2581,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465807</v>
+        <v>465799</v>
       </c>
       <c r="R20" t="n">
-        <v>6798288</v>
+        <v>6798259</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2617,6 +2612,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2643,7 +2643,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123876143</v>
+        <v>123876775</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2683,13 +2683,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465821</v>
+        <v>465799</v>
       </c>
       <c r="R21" t="n">
-        <v>6798095</v>
+        <v>6798205</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2733,19 +2733,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123878923</v>
+        <v>123878888</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2781,17 +2781,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465911</v>
+        <v>465907</v>
       </c>
       <c r="R22" t="n">
-        <v>6798461</v>
+        <v>6798419</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2821,6 +2821,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Garnlav i synfältet, 30 meter i radie. Miljöbilder</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2835,19 +2840,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123876157</v>
+        <v>123877304</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2887,13 +2892,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465822</v>
+        <v>465832</v>
       </c>
       <c r="R23" t="n">
-        <v>6798106</v>
+        <v>6798359</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2949,10 +2954,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123877326</v>
+        <v>123878923</v>
       </c>
       <c r="B24" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2965,42 +2970,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465799</v>
+        <v>465911</v>
       </c>
       <c r="R24" t="n">
-        <v>6798259</v>
+        <v>6798461</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3030,11 +3030,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3049,22 +3044,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123876339</v>
+        <v>123876806</v>
       </c>
       <c r="B25" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3077,21 +3072,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3101,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465823</v>
+        <v>465847</v>
       </c>
       <c r="R25" t="n">
-        <v>6798111</v>
+        <v>6798227</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3163,10 +3158,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123877017</v>
+        <v>123876586</v>
       </c>
       <c r="B26" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3179,21 +3174,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3203,10 +3198,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465805</v>
+        <v>465848</v>
       </c>
       <c r="R26" t="n">
-        <v>6798194</v>
+        <v>6798129</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3239,11 +3234,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3270,10 +3260,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123877240</v>
+        <v>123876691</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3286,21 +3276,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3310,10 +3300,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465859</v>
+        <v>465832</v>
       </c>
       <c r="R27" t="n">
-        <v>6798332</v>
+        <v>6798208</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3372,10 +3362,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123877850</v>
+        <v>123878630</v>
       </c>
       <c r="B28" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3388,37 +3378,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465863</v>
+        <v>465884</v>
       </c>
       <c r="R28" t="n">
-        <v>6798375</v>
+        <v>6798405</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3448,6 +3438,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3462,19 +3457,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123878630</v>
+        <v>123876521</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3510,14 +3505,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465884</v>
+        <v>465877</v>
       </c>
       <c r="R29" t="n">
-        <v>6798405</v>
+        <v>6798138</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3552,11 +3547,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3569,22 +3559,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123876806</v>
+        <v>123876866</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3593,25 +3583,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3621,10 +3611,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465847</v>
+        <v>465848</v>
       </c>
       <c r="R30" t="n">
-        <v>6798227</v>
+        <v>6798245</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3657,6 +3647,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Nyare spillning.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3683,10 +3678,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123877304</v>
+        <v>123877175</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3699,34 +3694,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465832</v>
+        <v>465790</v>
       </c>
       <c r="R31" t="n">
-        <v>6798359</v>
+        <v>6798239</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3761,6 +3756,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3773,12 +3773,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3887,7 +3887,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123876521</v>
+        <v>123878210</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -3927,13 +3927,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465877</v>
+        <v>465813</v>
       </c>
       <c r="R33" t="n">
-        <v>6798138</v>
+        <v>6798394</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3977,22 +3977,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123876733</v>
+        <v>123877017</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4005,37 +4005,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>465844</v>
+        <v>465805</v>
       </c>
       <c r="R34" t="n">
-        <v>6798212</v>
+        <v>6798194</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4065,6 +4065,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4079,19 +4084,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123876878</v>
+        <v>123876143</v>
       </c>
       <c r="B35" t="n">
         <v>78810</v>
@@ -4131,13 +4136,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465833</v>
+        <v>465821</v>
       </c>
       <c r="R35" t="n">
-        <v>6798269</v>
+        <v>6798095</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4181,22 +4186,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123876866</v>
+        <v>123877370</v>
       </c>
       <c r="B36" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4205,25 +4210,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4233,10 +4238,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465848</v>
+        <v>465830</v>
       </c>
       <c r="R36" t="n">
-        <v>6798245</v>
+        <v>6798388</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4269,11 +4274,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Nyare spillning.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4300,7 +4300,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123878210</v>
+        <v>123876878</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4340,13 +4340,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465813</v>
+        <v>465833</v>
       </c>
       <c r="R37" t="n">
-        <v>6798394</v>
+        <v>6798269</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4390,22 +4390,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123878561</v>
+        <v>123876339</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4418,21 +4418,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4442,10 +4442,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465804</v>
+        <v>465823</v>
       </c>
       <c r="R38" t="n">
-        <v>6798478</v>
+        <v>6798111</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4504,10 +4504,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123913271</v>
+        <v>123913374</v>
       </c>
       <c r="B39" t="n">
-        <v>78842</v>
+        <v>80763</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4520,21 +4520,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465720</v>
+        <v>465857</v>
       </c>
       <c r="R39" t="n">
-        <v>6798523</v>
+        <v>6798531</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4606,7 +4606,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123913504</v>
+        <v>123913439</v>
       </c>
       <c r="B40" t="n">
         <v>78810</v>
@@ -4646,10 +4646,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465787</v>
+        <v>465919</v>
       </c>
       <c r="R40" t="n">
-        <v>6798158</v>
+        <v>6798535</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4701,17 +4701,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123913492</v>
+        <v>123913279</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4724,21 +4724,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4748,10 +4748,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>465749</v>
+        <v>465720</v>
       </c>
       <c r="R41" t="n">
-        <v>6798363</v>
+        <v>6798411</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4810,10 +4810,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123913483</v>
+        <v>123913368</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4826,21 +4826,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>465694</v>
+        <v>465859</v>
       </c>
       <c r="R42" t="n">
-        <v>6798446</v>
+        <v>6798098</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4912,7 +4912,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123913500</v>
+        <v>123913450</v>
       </c>
       <c r="B43" t="n">
         <v>78810</v>
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465780</v>
+        <v>465835</v>
       </c>
       <c r="R43" t="n">
-        <v>6798219</v>
+        <v>6798579</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5007,17 +5007,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123913251</v>
+        <v>123913460</v>
       </c>
       <c r="B44" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465775</v>
+        <v>465809</v>
       </c>
       <c r="R44" t="n">
-        <v>6798229</v>
+        <v>6798627</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5116,10 +5116,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123913368</v>
+        <v>123913334</v>
       </c>
       <c r="B45" t="n">
-        <v>78547</v>
+        <v>91012</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5132,21 +5132,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5156,10 +5156,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465859</v>
+        <v>465933</v>
       </c>
       <c r="R45" t="n">
-        <v>6798098</v>
+        <v>6798526</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5218,10 +5218,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123913244</v>
+        <v>123913277</v>
       </c>
       <c r="B46" t="n">
-        <v>79428</v>
+        <v>78842</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5234,21 +5234,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5258,10 +5258,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465933</v>
+        <v>465709</v>
       </c>
       <c r="R46" t="n">
-        <v>6798458</v>
+        <v>6798426</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5320,10 +5320,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123913307</v>
+        <v>123913441</v>
       </c>
       <c r="B47" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5336,21 +5336,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5360,10 +5360,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465884</v>
+        <v>465893</v>
       </c>
       <c r="R47" t="n">
-        <v>6798130</v>
+        <v>6798543</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5415,17 +5415,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123913311</v>
+        <v>123913256</v>
       </c>
       <c r="B48" t="n">
-        <v>78842</v>
+        <v>74901</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5438,21 +5438,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5462,10 +5462,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>465842</v>
+        <v>465939</v>
       </c>
       <c r="R48" t="n">
-        <v>6798116</v>
+        <v>6798534</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5524,7 +5524,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123913487</v>
+        <v>123913470</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -5564,10 +5564,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>465720</v>
+        <v>465726</v>
       </c>
       <c r="R49" t="n">
-        <v>6798411</v>
+        <v>6798570</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5619,14 +5619,14 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123913489</v>
+        <v>123913434</v>
       </c>
       <c r="B50" t="n">
         <v>78810</v>
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>465753</v>
+        <v>465938</v>
       </c>
       <c r="R50" t="n">
-        <v>6798400</v>
+        <v>6798529</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5728,10 +5728,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123913485</v>
+        <v>123913282</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5744,21 +5744,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5768,10 +5768,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>465709</v>
+        <v>465748</v>
       </c>
       <c r="R51" t="n">
-        <v>6798426</v>
+        <v>6798396</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5830,10 +5830,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123913522</v>
+        <v>123913280</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5846,21 +5846,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5870,10 +5870,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>465842</v>
+        <v>465753</v>
       </c>
       <c r="R52" t="n">
-        <v>6798113</v>
+        <v>6798400</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5932,7 +5932,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123913517</v>
+        <v>123913464</v>
       </c>
       <c r="B53" t="n">
         <v>78810</v>
@@ -5972,10 +5972,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>465837</v>
+        <v>465767</v>
       </c>
       <c r="R53" t="n">
-        <v>6798096</v>
+        <v>6798617</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6027,14 +6027,14 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123913446</v>
+        <v>123913453</v>
       </c>
       <c r="B54" t="n">
         <v>78810</v>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>465875</v>
+        <v>465833</v>
       </c>
       <c r="R54" t="n">
-        <v>6798559</v>
+        <v>6798603</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6129,14 +6129,14 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123913462</v>
+        <v>123913438</v>
       </c>
       <c r="B55" t="n">
         <v>78810</v>
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>465782</v>
+        <v>465904</v>
       </c>
       <c r="R55" t="n">
-        <v>6798650</v>
+        <v>6798521</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6238,7 +6238,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123913482</v>
+        <v>123913519</v>
       </c>
       <c r="B56" t="n">
         <v>78810</v>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>465693</v>
+        <v>465865</v>
       </c>
       <c r="R56" t="n">
-        <v>6798461</v>
+        <v>6798133</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6333,17 +6333,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123913572</v>
+        <v>123913309</v>
       </c>
       <c r="B57" t="n">
-        <v>78455</v>
+        <v>78842</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6356,21 +6356,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6380,10 +6380,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>465778</v>
+        <v>465845</v>
       </c>
       <c r="R57" t="n">
-        <v>6798141</v>
+        <v>6798127</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6435,17 +6435,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123913266</v>
+        <v>123913432</v>
       </c>
       <c r="B58" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6458,21 +6458,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6482,10 +6482,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>465839</v>
+        <v>465943</v>
       </c>
       <c r="R58" t="n">
-        <v>6798559</v>
+        <v>6798495</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6544,10 +6544,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123913436</v>
+        <v>123913268</v>
       </c>
       <c r="B59" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6560,21 +6560,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6584,10 +6584,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>465927</v>
+        <v>465767</v>
       </c>
       <c r="R59" t="n">
-        <v>6798517</v>
+        <v>6798617</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6646,7 +6646,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123913426</v>
+        <v>123913498</v>
       </c>
       <c r="B60" t="n">
         <v>78810</v>
@@ -6686,10 +6686,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>465923</v>
+        <v>465746</v>
       </c>
       <c r="R60" t="n">
-        <v>6798451</v>
+        <v>6798258</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6748,10 +6748,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123913458</v>
+        <v>123913247</v>
       </c>
       <c r="B61" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6764,21 +6764,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6788,10 +6788,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>465826</v>
+        <v>465707</v>
       </c>
       <c r="R61" t="n">
-        <v>6798611</v>
+        <v>6798475</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6843,17 +6843,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123913279</v>
+        <v>123913451</v>
       </c>
       <c r="B62" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6866,21 +6866,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6890,10 +6890,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>465720</v>
+        <v>465838</v>
       </c>
       <c r="R62" t="n">
-        <v>6798411</v>
+        <v>6798591</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6952,7 +6952,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123913274</v>
+        <v>123913315</v>
       </c>
       <c r="B63" t="n">
         <v>78842</v>
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465705</v>
+        <v>465899</v>
       </c>
       <c r="R63" t="n">
-        <v>6798509</v>
+        <v>6798123</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7047,14 +7047,14 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123913502</v>
+        <v>123913487</v>
       </c>
       <c r="B64" t="n">
         <v>78810</v>
@@ -7094,10 +7094,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>465783</v>
+        <v>465720</v>
       </c>
       <c r="R64" t="n">
-        <v>6798169</v>
+        <v>6798411</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7149,17 +7149,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123913564</v>
+        <v>123913260</v>
       </c>
       <c r="B65" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7172,39 +7172,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465737</v>
+        <v>465830</v>
       </c>
       <c r="R65" t="n">
-        <v>6798286</v>
+        <v>6798623</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7239,11 +7234,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Spår efter födosök</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7261,17 +7251,17 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123913441</v>
+        <v>123913311</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7284,21 +7274,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7308,10 +7298,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465893</v>
+        <v>465842</v>
       </c>
       <c r="R66" t="n">
-        <v>6798543</v>
+        <v>6798116</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7370,7 +7360,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123913498</v>
+        <v>123913423</v>
       </c>
       <c r="B67" t="n">
         <v>78810</v>
@@ -7410,10 +7400,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465746</v>
+        <v>465920</v>
       </c>
       <c r="R67" t="n">
-        <v>6798258</v>
+        <v>6798445</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7472,10 +7462,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123913490</v>
+        <v>123913271</v>
       </c>
       <c r="B68" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7488,21 +7478,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7512,10 +7502,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465741</v>
+        <v>465720</v>
       </c>
       <c r="R68" t="n">
-        <v>6798376</v>
+        <v>6798523</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7574,7 +7564,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123913530</v>
+        <v>123913462</v>
       </c>
       <c r="B69" t="n">
         <v>78810</v>
@@ -7614,10 +7604,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465883</v>
+        <v>465782</v>
       </c>
       <c r="R69" t="n">
-        <v>6798119</v>
+        <v>6798650</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7669,14 +7659,14 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123913519</v>
+        <v>123913496</v>
       </c>
       <c r="B70" t="n">
         <v>78810</v>
@@ -7716,10 +7706,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>465865</v>
+        <v>465749</v>
       </c>
       <c r="R70" t="n">
-        <v>6798133</v>
+        <v>6798268</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7771,17 +7761,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123913443</v>
+        <v>123913317</v>
       </c>
       <c r="B71" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7794,21 +7784,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7818,10 +7808,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465863</v>
+        <v>465913</v>
       </c>
       <c r="R71" t="n">
-        <v>6798532</v>
+        <v>6798106</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7880,10 +7870,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123913256</v>
+        <v>123913477</v>
       </c>
       <c r="B72" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7896,21 +7886,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7920,10 +7910,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>465939</v>
+        <v>465708</v>
       </c>
       <c r="R72" t="n">
-        <v>6798534</v>
+        <v>6798481</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7982,10 +7972,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123913313</v>
+        <v>123913472</v>
       </c>
       <c r="B73" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7998,21 +7988,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8022,10 +8012,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>465883</v>
+        <v>465710</v>
       </c>
       <c r="R73" t="n">
-        <v>6798119</v>
+        <v>6798561</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8084,10 +8074,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123913289</v>
+        <v>123913436</v>
       </c>
       <c r="B74" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8100,21 +8090,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8124,10 +8114,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>465786</v>
+        <v>465927</v>
       </c>
       <c r="R74" t="n">
-        <v>6798177</v>
+        <v>6798517</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8179,17 +8169,17 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123913374</v>
+        <v>123913515</v>
       </c>
       <c r="B75" t="n">
-        <v>80763</v>
+        <v>78810</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8202,21 +8192,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8226,10 +8216,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>465857</v>
+        <v>465825</v>
       </c>
       <c r="R75" t="n">
-        <v>6798531</v>
+        <v>6798086</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8288,10 +8278,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123913406</v>
+        <v>123913504</v>
       </c>
       <c r="B76" t="n">
-        <v>91172</v>
+        <v>78810</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8300,25 +8290,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8328,10 +8318,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>465872</v>
+        <v>465787</v>
       </c>
       <c r="R76" t="n">
-        <v>6798093</v>
+        <v>6798158</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8383,14 +8373,14 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123913439</v>
+        <v>123913494</v>
       </c>
       <c r="B77" t="n">
         <v>78810</v>
@@ -8430,10 +8420,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>465919</v>
+        <v>465741</v>
       </c>
       <c r="R77" t="n">
-        <v>6798535</v>
+        <v>6798286</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8492,10 +8482,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123913434</v>
+        <v>123913330</v>
       </c>
       <c r="B78" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8508,21 +8498,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8532,10 +8522,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>465938</v>
+        <v>465815</v>
       </c>
       <c r="R78" t="n">
-        <v>6798529</v>
+        <v>6798097</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8587,17 +8577,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123913287</v>
+        <v>123913492</v>
       </c>
       <c r="B79" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8610,21 +8600,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8634,10 +8624,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>465786</v>
+        <v>465749</v>
       </c>
       <c r="R79" t="n">
-        <v>6798207</v>
+        <v>6798363</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8696,10 +8686,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123913306</v>
+        <v>123913532</v>
       </c>
       <c r="B80" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8712,21 +8702,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8736,10 +8726,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>465841</v>
+        <v>465912</v>
       </c>
       <c r="R80" t="n">
-        <v>6798109</v>
+        <v>6798108</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8798,7 +8788,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123876771</v>
+        <v>123913443</v>
       </c>
       <c r="B81" t="n">
         <v>78810</v>
@@ -8838,10 +8828,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>465815</v>
+        <v>465863</v>
       </c>
       <c r="R81" t="n">
-        <v>6798172</v>
+        <v>6798532</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8876,11 +8866,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Garnlav bakom björnide, samt i en radie av ca 30 meter.  Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -8893,19 +8878,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123913464</v>
+        <v>123913483</v>
       </c>
       <c r="B82" t="n">
         <v>78810</v>
@@ -8945,10 +8930,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>465767</v>
+        <v>465694</v>
       </c>
       <c r="R82" t="n">
-        <v>6798617</v>
+        <v>6798446</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9007,7 +8992,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123913472</v>
+        <v>123913448</v>
       </c>
       <c r="B83" t="n">
         <v>78810</v>
@@ -9047,10 +9032,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>465710</v>
+        <v>465839</v>
       </c>
       <c r="R83" t="n">
-        <v>6798561</v>
+        <v>6798559</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9109,10 +9094,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123913327</v>
+        <v>123913430</v>
       </c>
       <c r="B84" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9125,21 +9110,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9149,10 +9134,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>465779</v>
+        <v>465947</v>
       </c>
       <c r="R84" t="n">
-        <v>6798140</v>
+        <v>6798479</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9204,17 +9189,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123913268</v>
+        <v>123913327</v>
       </c>
       <c r="B85" t="n">
-        <v>78842</v>
+        <v>79399</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9227,21 +9212,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9251,10 +9236,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>465767</v>
+        <v>465779</v>
       </c>
       <c r="R85" t="n">
-        <v>6798617</v>
+        <v>6798140</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9306,17 +9291,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123913496</v>
+        <v>123913287</v>
       </c>
       <c r="B86" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9329,21 +9314,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9353,10 +9338,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>465749</v>
+        <v>465786</v>
       </c>
       <c r="R86" t="n">
-        <v>6798268</v>
+        <v>6798207</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9408,14 +9393,14 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123913477</v>
+        <v>123913458</v>
       </c>
       <c r="B87" t="n">
         <v>78810</v>
@@ -9455,10 +9440,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>465708</v>
+        <v>465826</v>
       </c>
       <c r="R87" t="n">
-        <v>6798481</v>
+        <v>6798611</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9517,10 +9502,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123913532</v>
+        <v>123913249</v>
       </c>
       <c r="B88" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9533,21 +9518,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9557,10 +9542,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>465912</v>
+        <v>465757</v>
       </c>
       <c r="R88" t="n">
-        <v>6798108</v>
+        <v>6798402</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9619,10 +9604,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123913473</v>
+        <v>123913339</v>
       </c>
       <c r="B89" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9635,21 +9620,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9659,10 +9644,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>465720</v>
+        <v>465825</v>
       </c>
       <c r="R89" t="n">
-        <v>6798523</v>
+        <v>6798086</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9721,10 +9706,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123913323</v>
+        <v>123913480</v>
       </c>
       <c r="B90" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9733,25 +9718,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9761,10 +9746,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>465849</v>
+        <v>465696</v>
       </c>
       <c r="R90" t="n">
-        <v>6798130</v>
+        <v>6798479</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9823,10 +9808,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123913269</v>
+        <v>123913500</v>
       </c>
       <c r="B91" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9839,21 +9824,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9863,10 +9848,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>465705</v>
+        <v>465780</v>
       </c>
       <c r="R91" t="n">
-        <v>6798564</v>
+        <v>6798219</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9925,7 +9910,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123913280</v>
+        <v>123913291</v>
       </c>
       <c r="B92" t="n">
         <v>78842</v>
@@ -9965,10 +9950,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>465753</v>
+        <v>465775</v>
       </c>
       <c r="R92" t="n">
-        <v>6798400</v>
+        <v>6798148</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10027,10 +10012,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123913315</v>
+        <v>123913485</v>
       </c>
       <c r="B93" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10043,21 +10028,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10067,10 +10052,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>465899</v>
+        <v>465709</v>
       </c>
       <c r="R93" t="n">
-        <v>6798123</v>
+        <v>6798426</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10129,10 +10114,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123913460</v>
+        <v>123913289</v>
       </c>
       <c r="B94" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10145,21 +10130,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10169,10 +10154,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>465809</v>
+        <v>465786</v>
       </c>
       <c r="R94" t="n">
-        <v>6798627</v>
+        <v>6798177</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10231,7 +10216,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123913527</v>
+        <v>123913490</v>
       </c>
       <c r="B95" t="n">
         <v>78810</v>
@@ -10271,10 +10256,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>465878</v>
+        <v>465741</v>
       </c>
       <c r="R95" t="n">
-        <v>6798095</v>
+        <v>6798376</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10326,17 +10311,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123913330</v>
+        <v>123876771</v>
       </c>
       <c r="B96" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10349,21 +10334,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10376,7 +10361,7 @@
         <v>465815</v>
       </c>
       <c r="R96" t="n">
-        <v>6798097</v>
+        <v>6798172</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10411,6 +10396,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Garnlav bakom björnide, samt i en radie av ca 30 meter.  Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -10423,22 +10413,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123913276</v>
+        <v>123913489</v>
       </c>
       <c r="B97" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10451,21 +10441,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10475,10 +10465,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>465694</v>
+        <v>465753</v>
       </c>
       <c r="R97" t="n">
-        <v>6798446</v>
+        <v>6798400</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10537,7 +10527,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123913448</v>
+        <v>123913446</v>
       </c>
       <c r="B98" t="n">
         <v>78810</v>
@@ -10577,7 +10567,7 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>465839</v>
+        <v>465875</v>
       </c>
       <c r="R98" t="n">
         <v>6798559</v>
@@ -10639,10 +10629,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123913309</v>
+        <v>123913572</v>
       </c>
       <c r="B99" t="n">
-        <v>78842</v>
+        <v>78455</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10655,21 +10645,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10679,10 +10669,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>465845</v>
+        <v>465778</v>
       </c>
       <c r="R99" t="n">
-        <v>6798127</v>
+        <v>6798141</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10734,17 +10724,17 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123913277</v>
+        <v>123913525</v>
       </c>
       <c r="B100" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10757,21 +10747,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10781,10 +10771,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>465709</v>
+        <v>465837</v>
       </c>
       <c r="R100" t="n">
-        <v>6798426</v>
+        <v>6798100</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10843,10 +10833,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123913432</v>
+        <v>123913307</v>
       </c>
       <c r="B101" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10859,21 +10849,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10883,10 +10873,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>465943</v>
+        <v>465884</v>
       </c>
       <c r="R101" t="n">
-        <v>6798495</v>
+        <v>6798130</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10938,17 +10928,17 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123913260</v>
+        <v>123913306</v>
       </c>
       <c r="B102" t="n">
-        <v>74901</v>
+        <v>78842</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10961,21 +10951,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10985,10 +10975,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>465830</v>
+        <v>465841</v>
       </c>
       <c r="R102" t="n">
-        <v>6798623</v>
+        <v>6798109</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11047,10 +11037,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123913258</v>
+        <v>123913517</v>
       </c>
       <c r="B103" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11063,21 +11053,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11087,10 +11077,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>465915</v>
+        <v>465837</v>
       </c>
       <c r="R103" t="n">
-        <v>6798548</v>
+        <v>6798096</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11149,7 +11139,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>123913515</v>
+        <v>123913426</v>
       </c>
       <c r="B104" t="n">
         <v>78810</v>
@@ -11189,10 +11179,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>465825</v>
+        <v>465923</v>
       </c>
       <c r="R104" t="n">
-        <v>6798086</v>
+        <v>6798451</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11251,7 +11241,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123913430</v>
+        <v>123913522</v>
       </c>
       <c r="B105" t="n">
         <v>78810</v>
@@ -11291,10 +11281,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>465947</v>
+        <v>465842</v>
       </c>
       <c r="R105" t="n">
-        <v>6798479</v>
+        <v>6798113</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11346,14 +11336,14 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123913480</v>
+        <v>123913475</v>
       </c>
       <c r="B106" t="n">
         <v>78810</v>
@@ -11393,10 +11383,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>465696</v>
+        <v>465719</v>
       </c>
       <c r="R106" t="n">
-        <v>6798479</v>
+        <v>6798495</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11455,7 +11445,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123913423</v>
+        <v>123913482</v>
       </c>
       <c r="B107" t="n">
         <v>78810</v>
@@ -11495,10 +11485,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>465920</v>
+        <v>465693</v>
       </c>
       <c r="R107" t="n">
-        <v>6798445</v>
+        <v>6798461</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11550,17 +11540,17 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123913247</v>
+        <v>123913527</v>
       </c>
       <c r="B108" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11573,21 +11563,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11597,10 +11587,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>465707</v>
+        <v>465878</v>
       </c>
       <c r="R108" t="n">
-        <v>6798475</v>
+        <v>6798095</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11652,17 +11642,17 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123913494</v>
+        <v>123913581</v>
       </c>
       <c r="B109" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11671,35 +11661,40 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>465741</v>
+        <v>465737</v>
       </c>
       <c r="R109" t="n">
         <v>6798286</v>
@@ -11754,17 +11749,17 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123913450</v>
+        <v>123913266</v>
       </c>
       <c r="B110" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11777,21 +11772,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11801,10 +11796,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>465835</v>
+        <v>465839</v>
       </c>
       <c r="R110" t="n">
-        <v>6798579</v>
+        <v>6798559</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11863,7 +11858,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123913475</v>
+        <v>123913502</v>
       </c>
       <c r="B111" t="n">
         <v>78810</v>
@@ -11903,10 +11898,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>465719</v>
+        <v>465783</v>
       </c>
       <c r="R111" t="n">
-        <v>6798495</v>
+        <v>6798169</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11958,17 +11953,17 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123913249</v>
+        <v>123913258</v>
       </c>
       <c r="B112" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11981,21 +11976,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12005,10 +12000,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>465757</v>
+        <v>465915</v>
       </c>
       <c r="R112" t="n">
-        <v>6798402</v>
+        <v>6798548</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12060,17 +12055,17 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>123913262</v>
+        <v>123913530</v>
       </c>
       <c r="B113" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12083,21 +12078,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12107,10 +12102,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>465764</v>
+        <v>465883</v>
       </c>
       <c r="R113" t="n">
-        <v>6798656</v>
+        <v>6798119</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12162,17 +12157,17 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123913453</v>
+        <v>123913313</v>
       </c>
       <c r="B114" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12185,21 +12180,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12209,10 +12204,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>465833</v>
+        <v>465883</v>
       </c>
       <c r="R114" t="n">
-        <v>6798603</v>
+        <v>6798119</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12264,17 +12259,17 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123913438</v>
+        <v>123913274</v>
       </c>
       <c r="B115" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12287,21 +12282,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12311,10 +12306,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>465904</v>
+        <v>465705</v>
       </c>
       <c r="R115" t="n">
-        <v>6798521</v>
+        <v>6798509</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12373,10 +12368,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123913525</v>
+        <v>123913244</v>
       </c>
       <c r="B116" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12389,21 +12384,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12413,10 +12408,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>465837</v>
+        <v>465933</v>
       </c>
       <c r="R116" t="n">
-        <v>6798100</v>
+        <v>6798458</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12468,17 +12463,17 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123913581</v>
+        <v>123913251</v>
       </c>
       <c r="B117" t="n">
-        <v>5176</v>
+        <v>79428</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12487,43 +12482,38 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>465737</v>
+        <v>465775</v>
       </c>
       <c r="R117" t="n">
-        <v>6798286</v>
+        <v>6798229</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12575,17 +12565,17 @@
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123913339</v>
+        <v>123913262</v>
       </c>
       <c r="B118" t="n">
-        <v>57666</v>
+        <v>74901</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12598,21 +12588,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12622,10 +12612,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>465825</v>
+        <v>465764</v>
       </c>
       <c r="R118" t="n">
-        <v>6798086</v>
+        <v>6798656</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12684,7 +12674,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123913282</v>
+        <v>123913276</v>
       </c>
       <c r="B119" t="n">
         <v>78842</v>
@@ -12724,10 +12714,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>465748</v>
+        <v>465694</v>
       </c>
       <c r="R119" t="n">
-        <v>6798396</v>
+        <v>6798446</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12786,10 +12776,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>123913285</v>
+        <v>123913323</v>
       </c>
       <c r="B120" t="n">
-        <v>78842</v>
+        <v>90977</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12798,25 +12788,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12826,10 +12816,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>465735</v>
+        <v>465849</v>
       </c>
       <c r="R120" t="n">
-        <v>6798291</v>
+        <v>6798130</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12888,10 +12878,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123913334</v>
+        <v>123913473</v>
       </c>
       <c r="B121" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12904,21 +12894,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12928,10 +12918,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>465933</v>
+        <v>465720</v>
       </c>
       <c r="R121" t="n">
-        <v>6798526</v>
+        <v>6798523</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12983,17 +12973,17 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123913451</v>
+        <v>123913285</v>
       </c>
       <c r="B122" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13006,21 +12996,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13030,10 +13020,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>465838</v>
+        <v>465735</v>
       </c>
       <c r="R122" t="n">
-        <v>6798591</v>
+        <v>6798291</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13092,10 +13082,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123913470</v>
+        <v>123913406</v>
       </c>
       <c r="B123" t="n">
-        <v>78810</v>
+        <v>91172</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13104,25 +13094,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13132,10 +13122,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>465726</v>
+        <v>465872</v>
       </c>
       <c r="R123" t="n">
-        <v>6798570</v>
+        <v>6798093</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13194,7 +13184,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123913317</v>
+        <v>123913269</v>
       </c>
       <c r="B124" t="n">
         <v>78842</v>
@@ -13234,10 +13224,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>465913</v>
+        <v>465705</v>
       </c>
       <c r="R124" t="n">
-        <v>6798106</v>
+        <v>6798564</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13296,10 +13286,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>123913291</v>
+        <v>123913564</v>
       </c>
       <c r="B125" t="n">
-        <v>78842</v>
+        <v>57513</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13312,34 +13302,39 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>465775</v>
+        <v>465737</v>
       </c>
       <c r="R125" t="n">
-        <v>6798148</v>
+        <v>6798286</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13374,6 +13369,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Spår efter födosök</t>
+        </is>
+      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>

--- a/artfynd/A 15853-2025 artfynd.xlsx
+++ b/artfynd/A 15853-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123877582</v>
+        <v>123876786</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465745</v>
+        <v>465862</v>
       </c>
       <c r="R2" t="n">
-        <v>6798476</v>
+        <v>6798219</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123877433</v>
+        <v>123876291</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465854</v>
+        <v>465806</v>
       </c>
       <c r="R3" t="n">
-        <v>6798343</v>
+        <v>6798100</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123878436</v>
+        <v>123876691</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465800</v>
+        <v>465832</v>
       </c>
       <c r="R4" t="n">
-        <v>6798391</v>
+        <v>6798208</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -955,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Garnlav synligt ca 30 meters radie. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,19 +969,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123878540</v>
+        <v>123877240</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465797</v>
+        <v>465859</v>
       </c>
       <c r="R5" t="n">
-        <v>6798473</v>
+        <v>6798332</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123876157</v>
+        <v>123876339</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465822</v>
+        <v>465823</v>
       </c>
       <c r="R6" t="n">
-        <v>6798106</v>
+        <v>6798111</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1190,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123876291</v>
+        <v>123876521</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1230,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465806</v>
+        <v>465877</v>
       </c>
       <c r="R7" t="n">
-        <v>6798100</v>
+        <v>6798138</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123876845</v>
+        <v>123877370</v>
       </c>
       <c r="B8" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465832</v>
+        <v>465830</v>
       </c>
       <c r="R8" t="n">
-        <v>6798231</v>
+        <v>6798388</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123878104</v>
+        <v>123877017</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,13 +1429,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465803</v>
+        <v>465805</v>
       </c>
       <c r="R9" t="n">
-        <v>6798395</v>
+        <v>6798194</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1470,6 +1465,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1484,19 +1484,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123876733</v>
+        <v>123877138</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465844</v>
+        <v>465846</v>
       </c>
       <c r="R10" t="n">
-        <v>6798212</v>
+        <v>6798341</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123877481</v>
+        <v>123878923</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,42 +1614,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465807</v>
+        <v>465911</v>
       </c>
       <c r="R11" t="n">
-        <v>6798288</v>
+        <v>6798461</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1693,22 +1688,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123877850</v>
+        <v>123878540</v>
       </c>
       <c r="B12" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465863</v>
+        <v>465797</v>
       </c>
       <c r="R12" t="n">
-        <v>6798375</v>
+        <v>6798473</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1807,7 +1802,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123877884</v>
+        <v>123876656</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1843,14 +1838,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465816</v>
+        <v>465833</v>
       </c>
       <c r="R13" t="n">
-        <v>6798323</v>
+        <v>6798204</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1885,11 +1880,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1902,19 +1892,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123877240</v>
+        <v>123876157</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1954,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465859</v>
+        <v>465822</v>
       </c>
       <c r="R14" t="n">
-        <v>6798332</v>
+        <v>6798106</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2016,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123877138</v>
+        <v>123876866</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465846</v>
+        <v>465848</v>
       </c>
       <c r="R15" t="n">
-        <v>6798341</v>
+        <v>6798245</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2092,6 +2082,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Nyare spillning.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2118,7 +2113,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123877248</v>
+        <v>123877582</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2154,17 +2149,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465799</v>
+        <v>465745</v>
       </c>
       <c r="R16" t="n">
-        <v>6798259</v>
+        <v>6798476</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2194,11 +2189,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2213,22 +2203,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123876786</v>
+        <v>123877248</v>
       </c>
       <c r="B17" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,37 +2231,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465862</v>
+        <v>465799</v>
       </c>
       <c r="R17" t="n">
-        <v>6798219</v>
+        <v>6798259</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2301,6 +2291,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2315,22 +2310,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123878561</v>
+        <v>123877481</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,37 +2338,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465804</v>
+        <v>465807</v>
       </c>
       <c r="R18" t="n">
-        <v>6798478</v>
+        <v>6798288</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2417,19 +2417,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123878365</v>
+        <v>123878888</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2465,17 +2465,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465783</v>
+        <v>465907</v>
       </c>
       <c r="R19" t="n">
-        <v>6798386</v>
+        <v>6798419</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2505,6 +2505,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Garnlav i synfältet, 30 meter i radie. Miljöbilder</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2519,22 +2524,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123877326</v>
+        <v>123877884</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,39 +2552,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465799</v>
+        <v>465816</v>
       </c>
       <c r="R20" t="n">
-        <v>6798259</v>
+        <v>6798323</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2643,7 +2643,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123876775</v>
+        <v>123876878</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465799</v>
+        <v>465833</v>
       </c>
       <c r="R21" t="n">
-        <v>6798205</v>
+        <v>6798269</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2745,7 +2745,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123878888</v>
+        <v>123878561</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2781,17 +2781,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465907</v>
+        <v>465804</v>
       </c>
       <c r="R22" t="n">
-        <v>6798419</v>
+        <v>6798478</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2821,11 +2821,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Garnlav i synfältet, 30 meter i radie. Miljöbilder</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2840,22 +2835,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123877304</v>
+        <v>123877850</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2868,21 +2863,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2892,13 +2887,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465832</v>
+        <v>465863</v>
       </c>
       <c r="R23" t="n">
-        <v>6798359</v>
+        <v>6798375</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2954,7 +2949,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123878923</v>
+        <v>123878365</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -2994,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465911</v>
+        <v>465783</v>
       </c>
       <c r="R24" t="n">
-        <v>6798461</v>
+        <v>6798386</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3158,10 +3153,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123876586</v>
+        <v>123876845</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3174,37 +3169,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465848</v>
+        <v>465832</v>
       </c>
       <c r="R26" t="n">
-        <v>6798129</v>
+        <v>6798231</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3248,22 +3243,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123876691</v>
+        <v>123876733</v>
       </c>
       <c r="B27" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3276,21 +3271,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3300,10 +3295,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465832</v>
+        <v>465844</v>
       </c>
       <c r="R27" t="n">
-        <v>6798208</v>
+        <v>6798212</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3362,7 +3357,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123878630</v>
+        <v>123878210</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3398,17 +3393,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465884</v>
+        <v>465813</v>
       </c>
       <c r="R28" t="n">
-        <v>6798405</v>
+        <v>6798394</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3438,11 +3433,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3457,19 +3447,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123876521</v>
+        <v>123876586</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3505,14 +3495,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465877</v>
+        <v>465848</v>
       </c>
       <c r="R29" t="n">
-        <v>6798138</v>
+        <v>6798129</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3559,22 +3549,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123876866</v>
+        <v>123877433</v>
       </c>
       <c r="B30" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3583,25 +3573,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3611,10 +3601,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465848</v>
+        <v>465854</v>
       </c>
       <c r="R30" t="n">
-        <v>6798245</v>
+        <v>6798343</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3647,11 +3637,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Nyare spillning.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3678,10 +3663,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123877175</v>
+        <v>123876775</v>
       </c>
       <c r="B31" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3694,37 +3679,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465790</v>
+        <v>465799</v>
       </c>
       <c r="R31" t="n">
-        <v>6798239</v>
+        <v>6798205</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3754,11 +3739,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3773,19 +3753,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123876656</v>
+        <v>123876143</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3825,13 +3805,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>465833</v>
+        <v>465821</v>
       </c>
       <c r="R32" t="n">
-        <v>6798204</v>
+        <v>6798095</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3887,7 +3867,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123878210</v>
+        <v>123878104</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -3923,17 +3903,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465813</v>
+        <v>465803</v>
       </c>
       <c r="R33" t="n">
-        <v>6798394</v>
+        <v>6798395</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3977,22 +3957,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123877017</v>
+        <v>123877326</v>
       </c>
       <c r="B34" t="n">
-        <v>79399</v>
+        <v>57529</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4005,34 +3985,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>465805</v>
+        <v>465799</v>
       </c>
       <c r="R34" t="n">
-        <v>6798194</v>
+        <v>6798259</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4069,7 +4054,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4096,7 +4081,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123876143</v>
+        <v>123877304</v>
       </c>
       <c r="B35" t="n">
         <v>78810</v>
@@ -4136,13 +4121,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465821</v>
+        <v>465832</v>
       </c>
       <c r="R35" t="n">
-        <v>6798095</v>
+        <v>6798359</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4198,7 +4183,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123877370</v>
+        <v>123878630</v>
       </c>
       <c r="B36" t="n">
         <v>78810</v>
@@ -4234,17 +4219,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465830</v>
+        <v>465884</v>
       </c>
       <c r="R36" t="n">
-        <v>6798388</v>
+        <v>6798405</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4274,6 +4259,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4288,22 +4278,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123876878</v>
+        <v>123877175</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4316,37 +4306,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465833</v>
+        <v>465790</v>
       </c>
       <c r="R37" t="n">
-        <v>6798269</v>
+        <v>6798239</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4376,6 +4366,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4390,22 +4385,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123876339</v>
+        <v>123878436</v>
       </c>
       <c r="B38" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4418,37 +4413,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465823</v>
+        <v>465800</v>
       </c>
       <c r="R38" t="n">
-        <v>6798111</v>
+        <v>6798391</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4478,6 +4473,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Garnlav synligt ca 30 meters radie. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4492,22 +4492,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123913374</v>
+        <v>123913492</v>
       </c>
       <c r="B39" t="n">
-        <v>80763</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4520,21 +4520,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465857</v>
+        <v>465749</v>
       </c>
       <c r="R39" t="n">
-        <v>6798531</v>
+        <v>6798363</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4606,7 +4606,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123913439</v>
+        <v>123913482</v>
       </c>
       <c r="B40" t="n">
         <v>78810</v>
@@ -4646,10 +4646,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465919</v>
+        <v>465693</v>
       </c>
       <c r="R40" t="n">
-        <v>6798535</v>
+        <v>6798461</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4701,17 +4701,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123913279</v>
+        <v>123913470</v>
       </c>
       <c r="B41" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4724,21 +4724,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4748,10 +4748,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>465720</v>
+        <v>465726</v>
       </c>
       <c r="R41" t="n">
-        <v>6798411</v>
+        <v>6798570</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4810,10 +4810,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123913368</v>
+        <v>123913262</v>
       </c>
       <c r="B42" t="n">
-        <v>78547</v>
+        <v>74901</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4826,21 +4826,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>465859</v>
+        <v>465764</v>
       </c>
       <c r="R42" t="n">
-        <v>6798098</v>
+        <v>6798656</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4912,10 +4912,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123913450</v>
+        <v>123913258</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4928,21 +4928,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465835</v>
+        <v>465915</v>
       </c>
       <c r="R43" t="n">
-        <v>6798579</v>
+        <v>6798548</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5007,17 +5007,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123913460</v>
+        <v>123913269</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465809</v>
+        <v>465705</v>
       </c>
       <c r="R44" t="n">
-        <v>6798627</v>
+        <v>6798564</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5116,10 +5116,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123913334</v>
+        <v>123913268</v>
       </c>
       <c r="B45" t="n">
-        <v>91012</v>
+        <v>78842</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5132,21 +5132,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5156,10 +5156,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465933</v>
+        <v>465767</v>
       </c>
       <c r="R45" t="n">
-        <v>6798526</v>
+        <v>6798617</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5218,10 +5218,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123913277</v>
+        <v>123913564</v>
       </c>
       <c r="B46" t="n">
-        <v>78842</v>
+        <v>57513</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5234,34 +5234,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465709</v>
+        <v>465737</v>
       </c>
       <c r="R46" t="n">
-        <v>6798426</v>
+        <v>6798286</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5296,6 +5301,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Spår efter födosök</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5313,14 +5323,14 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123913441</v>
+        <v>123913517</v>
       </c>
       <c r="B47" t="n">
         <v>78810</v>
@@ -5360,10 +5370,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465893</v>
+        <v>465837</v>
       </c>
       <c r="R47" t="n">
-        <v>6798543</v>
+        <v>6798096</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5415,17 +5425,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123913256</v>
+        <v>123913323</v>
       </c>
       <c r="B48" t="n">
-        <v>74901</v>
+        <v>90977</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5434,25 +5444,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5462,10 +5472,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>465939</v>
+        <v>465849</v>
       </c>
       <c r="R48" t="n">
-        <v>6798534</v>
+        <v>6798130</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5524,7 +5534,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123913470</v>
+        <v>123913487</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -5564,10 +5574,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>465726</v>
+        <v>465720</v>
       </c>
       <c r="R49" t="n">
-        <v>6798570</v>
+        <v>6798411</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5619,14 +5629,14 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123913434</v>
+        <v>123913530</v>
       </c>
       <c r="B50" t="n">
         <v>78810</v>
@@ -5666,10 +5676,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>465938</v>
+        <v>465883</v>
       </c>
       <c r="R50" t="n">
-        <v>6798529</v>
+        <v>6798119</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5728,10 +5738,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123913282</v>
+        <v>123876771</v>
       </c>
       <c r="B51" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5744,21 +5754,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5768,10 +5778,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>465748</v>
+        <v>465815</v>
       </c>
       <c r="R51" t="n">
-        <v>6798396</v>
+        <v>6798172</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5806,6 +5816,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Garnlav bakom björnide, samt i en radie av ca 30 meter.  Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5818,22 +5833,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123913280</v>
+        <v>123913472</v>
       </c>
       <c r="B52" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5846,21 +5861,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5870,10 +5885,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>465753</v>
+        <v>465710</v>
       </c>
       <c r="R52" t="n">
-        <v>6798400</v>
+        <v>6798561</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5932,7 +5947,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123913464</v>
+        <v>123913502</v>
       </c>
       <c r="B53" t="n">
         <v>78810</v>
@@ -5972,10 +5987,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>465767</v>
+        <v>465783</v>
       </c>
       <c r="R53" t="n">
-        <v>6798617</v>
+        <v>6798169</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6027,14 +6042,14 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123913453</v>
+        <v>123913443</v>
       </c>
       <c r="B54" t="n">
         <v>78810</v>
@@ -6074,10 +6089,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>465833</v>
+        <v>465863</v>
       </c>
       <c r="R54" t="n">
-        <v>6798603</v>
+        <v>6798532</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6129,17 +6144,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123913438</v>
+        <v>123913256</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6152,21 +6167,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6176,10 +6191,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>465904</v>
+        <v>465939</v>
       </c>
       <c r="R55" t="n">
-        <v>6798521</v>
+        <v>6798534</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6238,10 +6253,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123913519</v>
+        <v>123913247</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6254,21 +6269,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6278,10 +6293,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>465865</v>
+        <v>465707</v>
       </c>
       <c r="R56" t="n">
-        <v>6798133</v>
+        <v>6798475</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6333,17 +6348,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123913309</v>
+        <v>123913423</v>
       </c>
       <c r="B57" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6356,21 +6371,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6380,10 +6395,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>465845</v>
+        <v>465920</v>
       </c>
       <c r="R57" t="n">
-        <v>6798127</v>
+        <v>6798445</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6442,7 +6457,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123913432</v>
+        <v>123913460</v>
       </c>
       <c r="B58" t="n">
         <v>78810</v>
@@ -6482,10 +6497,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>465943</v>
+        <v>465809</v>
       </c>
       <c r="R58" t="n">
-        <v>6798495</v>
+        <v>6798627</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6544,7 +6559,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123913268</v>
+        <v>123913266</v>
       </c>
       <c r="B59" t="n">
         <v>78842</v>
@@ -6584,10 +6599,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>465767</v>
+        <v>465839</v>
       </c>
       <c r="R59" t="n">
-        <v>6798617</v>
+        <v>6798559</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6646,10 +6661,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123913498</v>
+        <v>123913277</v>
       </c>
       <c r="B60" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6662,21 +6677,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6686,10 +6701,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>465746</v>
+        <v>465709</v>
       </c>
       <c r="R60" t="n">
-        <v>6798258</v>
+        <v>6798426</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6748,10 +6763,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123913247</v>
+        <v>123913279</v>
       </c>
       <c r="B61" t="n">
-        <v>79428</v>
+        <v>78842</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6764,21 +6779,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6788,10 +6803,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>465707</v>
+        <v>465720</v>
       </c>
       <c r="R61" t="n">
-        <v>6798475</v>
+        <v>6798411</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6843,14 +6858,14 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123913451</v>
+        <v>123913500</v>
       </c>
       <c r="B62" t="n">
         <v>78810</v>
@@ -6890,10 +6905,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>465838</v>
+        <v>465780</v>
       </c>
       <c r="R62" t="n">
-        <v>6798591</v>
+        <v>6798219</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6952,10 +6967,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123913315</v>
+        <v>123913490</v>
       </c>
       <c r="B63" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6968,21 +6983,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6992,10 +7007,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465899</v>
+        <v>465741</v>
       </c>
       <c r="R63" t="n">
-        <v>6798123</v>
+        <v>6798376</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7047,17 +7062,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123913487</v>
+        <v>123913368</v>
       </c>
       <c r="B64" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7070,21 +7085,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7094,10 +7109,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>465720</v>
+        <v>465859</v>
       </c>
       <c r="R64" t="n">
-        <v>6798411</v>
+        <v>6798098</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7149,17 +7164,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123913260</v>
+        <v>123913330</v>
       </c>
       <c r="B65" t="n">
-        <v>74901</v>
+        <v>79399</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7172,21 +7187,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7196,10 +7211,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465830</v>
+        <v>465815</v>
       </c>
       <c r="R65" t="n">
-        <v>6798623</v>
+        <v>6798097</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7258,10 +7273,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123913311</v>
+        <v>123913494</v>
       </c>
       <c r="B66" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7274,21 +7289,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7298,10 +7313,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465842</v>
+        <v>465741</v>
       </c>
       <c r="R66" t="n">
-        <v>6798116</v>
+        <v>6798286</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7360,7 +7375,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123913423</v>
+        <v>123913451</v>
       </c>
       <c r="B67" t="n">
         <v>78810</v>
@@ -7400,10 +7415,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465920</v>
+        <v>465838</v>
       </c>
       <c r="R67" t="n">
-        <v>6798445</v>
+        <v>6798591</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7462,10 +7477,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123913271</v>
+        <v>123913462</v>
       </c>
       <c r="B68" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7478,21 +7493,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7502,10 +7517,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465720</v>
+        <v>465782</v>
       </c>
       <c r="R68" t="n">
-        <v>6798523</v>
+        <v>6798650</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7564,7 +7579,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123913462</v>
+        <v>123913448</v>
       </c>
       <c r="B69" t="n">
         <v>78810</v>
@@ -7604,10 +7619,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465782</v>
+        <v>465839</v>
       </c>
       <c r="R69" t="n">
-        <v>6798650</v>
+        <v>6798559</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7659,14 +7674,14 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123913496</v>
+        <v>123913438</v>
       </c>
       <c r="B70" t="n">
         <v>78810</v>
@@ -7706,10 +7721,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>465749</v>
+        <v>465904</v>
       </c>
       <c r="R70" t="n">
-        <v>6798268</v>
+        <v>6798521</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7761,17 +7776,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123913317</v>
+        <v>123913439</v>
       </c>
       <c r="B71" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7784,21 +7799,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7808,10 +7823,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465913</v>
+        <v>465919</v>
       </c>
       <c r="R71" t="n">
-        <v>6798106</v>
+        <v>6798535</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7870,10 +7885,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123913477</v>
+        <v>123913280</v>
       </c>
       <c r="B72" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7886,21 +7901,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7910,10 +7925,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>465708</v>
+        <v>465753</v>
       </c>
       <c r="R72" t="n">
-        <v>6798481</v>
+        <v>6798400</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7972,7 +7987,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123913472</v>
+        <v>123913485</v>
       </c>
       <c r="B73" t="n">
         <v>78810</v>
@@ -8012,10 +8027,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>465710</v>
+        <v>465709</v>
       </c>
       <c r="R73" t="n">
-        <v>6798561</v>
+        <v>6798426</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8074,10 +8089,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123913436</v>
+        <v>123913311</v>
       </c>
       <c r="B74" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8090,21 +8105,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8114,10 +8129,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>465927</v>
+        <v>465842</v>
       </c>
       <c r="R74" t="n">
-        <v>6798517</v>
+        <v>6798116</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8169,17 +8184,17 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123913515</v>
+        <v>123913334</v>
       </c>
       <c r="B75" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8192,21 +8207,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8216,10 +8231,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>465825</v>
+        <v>465933</v>
       </c>
       <c r="R75" t="n">
-        <v>6798086</v>
+        <v>6798526</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8278,10 +8293,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123913504</v>
+        <v>123913251</v>
       </c>
       <c r="B76" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8294,21 +8309,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8318,10 +8333,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>465787</v>
+        <v>465775</v>
       </c>
       <c r="R76" t="n">
-        <v>6798158</v>
+        <v>6798229</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8373,14 +8388,14 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123913494</v>
+        <v>123913532</v>
       </c>
       <c r="B77" t="n">
         <v>78810</v>
@@ -8420,10 +8435,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>465741</v>
+        <v>465912</v>
       </c>
       <c r="R77" t="n">
-        <v>6798286</v>
+        <v>6798108</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8482,10 +8497,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123913330</v>
+        <v>123913453</v>
       </c>
       <c r="B78" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8498,21 +8513,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8522,10 +8537,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>465815</v>
+        <v>465833</v>
       </c>
       <c r="R78" t="n">
-        <v>6798097</v>
+        <v>6798603</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8577,14 +8592,14 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123913492</v>
+        <v>123913473</v>
       </c>
       <c r="B79" t="n">
         <v>78810</v>
@@ -8624,10 +8639,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>465749</v>
+        <v>465720</v>
       </c>
       <c r="R79" t="n">
-        <v>6798363</v>
+        <v>6798523</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8686,10 +8701,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123913532</v>
+        <v>123913291</v>
       </c>
       <c r="B80" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8702,21 +8717,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8726,10 +8741,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>465912</v>
+        <v>465775</v>
       </c>
       <c r="R80" t="n">
-        <v>6798108</v>
+        <v>6798148</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8788,10 +8803,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123913443</v>
+        <v>123913289</v>
       </c>
       <c r="B81" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8804,21 +8819,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8828,10 +8843,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>465863</v>
+        <v>465786</v>
       </c>
       <c r="R81" t="n">
-        <v>6798532</v>
+        <v>6798177</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8890,10 +8905,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123913483</v>
+        <v>123913309</v>
       </c>
       <c r="B82" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8906,21 +8921,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8930,10 +8945,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>465694</v>
+        <v>465845</v>
       </c>
       <c r="R82" t="n">
-        <v>6798446</v>
+        <v>6798127</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8992,7 +9007,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123913448</v>
+        <v>123913450</v>
       </c>
       <c r="B83" t="n">
         <v>78810</v>
@@ -9032,10 +9047,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>465839</v>
+        <v>465835</v>
       </c>
       <c r="R83" t="n">
-        <v>6798559</v>
+        <v>6798579</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9094,7 +9109,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123913430</v>
+        <v>123913527</v>
       </c>
       <c r="B84" t="n">
         <v>78810</v>
@@ -9134,10 +9149,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>465947</v>
+        <v>465878</v>
       </c>
       <c r="R84" t="n">
-        <v>6798479</v>
+        <v>6798095</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9189,17 +9204,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123913327</v>
+        <v>123913525</v>
       </c>
       <c r="B85" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9212,21 +9227,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9236,10 +9251,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>465779</v>
+        <v>465837</v>
       </c>
       <c r="R85" t="n">
-        <v>6798140</v>
+        <v>6798100</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9291,17 +9306,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123913287</v>
+        <v>123913406</v>
       </c>
       <c r="B86" t="n">
-        <v>78842</v>
+        <v>91172</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9310,25 +9325,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>185</v>
+        <v>1503</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9338,10 +9353,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>465786</v>
+        <v>465872</v>
       </c>
       <c r="R86" t="n">
-        <v>6798207</v>
+        <v>6798093</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9393,14 +9408,14 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123913458</v>
+        <v>123913446</v>
       </c>
       <c r="B87" t="n">
         <v>78810</v>
@@ -9440,10 +9455,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>465826</v>
+        <v>465875</v>
       </c>
       <c r="R87" t="n">
-        <v>6798611</v>
+        <v>6798559</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9502,10 +9517,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123913249</v>
+        <v>123913432</v>
       </c>
       <c r="B88" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9518,21 +9533,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9542,10 +9557,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>465757</v>
+        <v>465943</v>
       </c>
       <c r="R88" t="n">
-        <v>6798402</v>
+        <v>6798495</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9604,10 +9619,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123913339</v>
+        <v>123913436</v>
       </c>
       <c r="B89" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9620,21 +9635,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9644,10 +9659,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>465825</v>
+        <v>465927</v>
       </c>
       <c r="R89" t="n">
-        <v>6798086</v>
+        <v>6798517</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9706,7 +9721,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123913480</v>
+        <v>123913426</v>
       </c>
       <c r="B90" t="n">
         <v>78810</v>
@@ -9746,10 +9761,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>465696</v>
+        <v>465923</v>
       </c>
       <c r="R90" t="n">
-        <v>6798479</v>
+        <v>6798451</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9808,7 +9823,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123913500</v>
+        <v>123913477</v>
       </c>
       <c r="B91" t="n">
         <v>78810</v>
@@ -9848,10 +9863,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>465780</v>
+        <v>465708</v>
       </c>
       <c r="R91" t="n">
-        <v>6798219</v>
+        <v>6798481</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9910,10 +9925,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123913291</v>
+        <v>123913572</v>
       </c>
       <c r="B92" t="n">
-        <v>78842</v>
+        <v>78455</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9926,21 +9941,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9950,10 +9965,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>465775</v>
+        <v>465778</v>
       </c>
       <c r="R92" t="n">
-        <v>6798148</v>
+        <v>6798141</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10005,17 +10020,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123913485</v>
+        <v>123913313</v>
       </c>
       <c r="B93" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10028,21 +10043,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10052,10 +10067,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>465709</v>
+        <v>465883</v>
       </c>
       <c r="R93" t="n">
-        <v>6798426</v>
+        <v>6798119</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10114,10 +10129,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123913289</v>
+        <v>123913374</v>
       </c>
       <c r="B94" t="n">
-        <v>78842</v>
+        <v>80763</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10130,21 +10145,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10154,10 +10169,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>465786</v>
+        <v>465857</v>
       </c>
       <c r="R94" t="n">
-        <v>6798177</v>
+        <v>6798531</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10216,10 +10231,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123913490</v>
+        <v>123913244</v>
       </c>
       <c r="B95" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10232,21 +10247,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10256,10 +10271,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>465741</v>
+        <v>465933</v>
       </c>
       <c r="R95" t="n">
-        <v>6798376</v>
+        <v>6798458</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10311,17 +10326,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123876771</v>
+        <v>123913274</v>
       </c>
       <c r="B96" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10334,21 +10349,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10358,10 +10373,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>465815</v>
+        <v>465705</v>
       </c>
       <c r="R96" t="n">
-        <v>6798172</v>
+        <v>6798509</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10396,11 +10411,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Garnlav bakom björnide, samt i en radie av ca 30 meter.  Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -10413,19 +10423,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123913489</v>
+        <v>123913504</v>
       </c>
       <c r="B97" t="n">
         <v>78810</v>
@@ -10465,10 +10475,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>465753</v>
+        <v>465787</v>
       </c>
       <c r="R97" t="n">
-        <v>6798400</v>
+        <v>6798158</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10527,7 +10537,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123913446</v>
+        <v>123913522</v>
       </c>
       <c r="B98" t="n">
         <v>78810</v>
@@ -10567,10 +10577,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>465875</v>
+        <v>465842</v>
       </c>
       <c r="R98" t="n">
-        <v>6798559</v>
+        <v>6798113</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10629,10 +10639,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123913572</v>
+        <v>123913515</v>
       </c>
       <c r="B99" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10645,21 +10655,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10669,10 +10679,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>465778</v>
+        <v>465825</v>
       </c>
       <c r="R99" t="n">
-        <v>6798141</v>
+        <v>6798086</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10724,17 +10734,17 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123913525</v>
+        <v>123913249</v>
       </c>
       <c r="B100" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10747,21 +10757,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10771,10 +10781,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>465837</v>
+        <v>465757</v>
       </c>
       <c r="R100" t="n">
-        <v>6798100</v>
+        <v>6798402</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10833,7 +10843,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123913307</v>
+        <v>123913315</v>
       </c>
       <c r="B101" t="n">
         <v>78842</v>
@@ -10873,10 +10883,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>465884</v>
+        <v>465899</v>
       </c>
       <c r="R101" t="n">
-        <v>6798130</v>
+        <v>6798123</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10928,14 +10938,14 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123913306</v>
+        <v>123913282</v>
       </c>
       <c r="B102" t="n">
         <v>78842</v>
@@ -10975,10 +10985,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>465841</v>
+        <v>465748</v>
       </c>
       <c r="R102" t="n">
-        <v>6798109</v>
+        <v>6798396</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11037,10 +11047,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123913517</v>
+        <v>123913317</v>
       </c>
       <c r="B103" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11053,21 +11063,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11077,10 +11087,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>465837</v>
+        <v>465913</v>
       </c>
       <c r="R103" t="n">
-        <v>6798096</v>
+        <v>6798106</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11139,7 +11149,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>123913426</v>
+        <v>123913483</v>
       </c>
       <c r="B104" t="n">
         <v>78810</v>
@@ -11179,10 +11189,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>465923</v>
+        <v>465694</v>
       </c>
       <c r="R104" t="n">
-        <v>6798451</v>
+        <v>6798446</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11241,10 +11251,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123913522</v>
+        <v>123913581</v>
       </c>
       <c r="B105" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11253,38 +11263,43 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>465842</v>
+        <v>465737</v>
       </c>
       <c r="R105" t="n">
-        <v>6798113</v>
+        <v>6798286</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11343,10 +11358,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123913475</v>
+        <v>123913327</v>
       </c>
       <c r="B106" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11359,21 +11374,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11383,10 +11398,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>465719</v>
+        <v>465779</v>
       </c>
       <c r="R106" t="n">
-        <v>6798495</v>
+        <v>6798140</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11445,10 +11460,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123913482</v>
+        <v>123913339</v>
       </c>
       <c r="B107" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11461,21 +11476,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11485,10 +11500,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>465693</v>
+        <v>465825</v>
       </c>
       <c r="R107" t="n">
-        <v>6798461</v>
+        <v>6798086</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11540,14 +11555,14 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123913527</v>
+        <v>123913489</v>
       </c>
       <c r="B108" t="n">
         <v>78810</v>
@@ -11587,10 +11602,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>465878</v>
+        <v>465753</v>
       </c>
       <c r="R108" t="n">
-        <v>6798095</v>
+        <v>6798400</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11642,17 +11657,17 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123913581</v>
+        <v>123913519</v>
       </c>
       <c r="B109" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11661,43 +11676,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>465737</v>
+        <v>465865</v>
       </c>
       <c r="R109" t="n">
-        <v>6798286</v>
+        <v>6798133</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11749,17 +11759,17 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123913266</v>
+        <v>123913458</v>
       </c>
       <c r="B110" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11772,21 +11782,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11796,10 +11806,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>465839</v>
+        <v>465826</v>
       </c>
       <c r="R110" t="n">
-        <v>6798559</v>
+        <v>6798611</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11858,7 +11868,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123913502</v>
+        <v>123913498</v>
       </c>
       <c r="B111" t="n">
         <v>78810</v>
@@ -11898,10 +11908,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>465783</v>
+        <v>465746</v>
       </c>
       <c r="R111" t="n">
-        <v>6798169</v>
+        <v>6798258</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11953,17 +11963,17 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123913258</v>
+        <v>123913430</v>
       </c>
       <c r="B112" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11976,21 +11986,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12000,10 +12010,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>465915</v>
+        <v>465947</v>
       </c>
       <c r="R112" t="n">
-        <v>6798548</v>
+        <v>6798479</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12055,14 +12065,14 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>123913530</v>
+        <v>123913434</v>
       </c>
       <c r="B113" t="n">
         <v>78810</v>
@@ -12102,10 +12112,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>465883</v>
+        <v>465938</v>
       </c>
       <c r="R113" t="n">
-        <v>6798119</v>
+        <v>6798529</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12157,17 +12167,17 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123913313</v>
+        <v>123913441</v>
       </c>
       <c r="B114" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12180,21 +12190,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12204,10 +12214,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>465883</v>
+        <v>465893</v>
       </c>
       <c r="R114" t="n">
-        <v>6798119</v>
+        <v>6798543</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12259,17 +12269,17 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123913274</v>
+        <v>123913475</v>
       </c>
       <c r="B115" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12282,21 +12292,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12306,10 +12316,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>465705</v>
+        <v>465719</v>
       </c>
       <c r="R115" t="n">
-        <v>6798509</v>
+        <v>6798495</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12368,10 +12378,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123913244</v>
+        <v>123913260</v>
       </c>
       <c r="B116" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12384,21 +12394,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12408,10 +12418,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>465933</v>
+        <v>465830</v>
       </c>
       <c r="R116" t="n">
-        <v>6798458</v>
+        <v>6798623</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12463,17 +12473,17 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123913251</v>
+        <v>123913480</v>
       </c>
       <c r="B117" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12486,21 +12496,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12510,10 +12520,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>465775</v>
+        <v>465696</v>
       </c>
       <c r="R117" t="n">
-        <v>6798229</v>
+        <v>6798479</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12572,10 +12582,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123913262</v>
+        <v>123913496</v>
       </c>
       <c r="B118" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12588,21 +12598,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12612,10 +12622,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>465764</v>
+        <v>465749</v>
       </c>
       <c r="R118" t="n">
-        <v>6798656</v>
+        <v>6798268</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12674,7 +12684,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123913276</v>
+        <v>123913287</v>
       </c>
       <c r="B119" t="n">
         <v>78842</v>
@@ -12714,10 +12724,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>465694</v>
+        <v>465786</v>
       </c>
       <c r="R119" t="n">
-        <v>6798446</v>
+        <v>6798207</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12776,10 +12786,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>123913323</v>
+        <v>123913276</v>
       </c>
       <c r="B120" t="n">
-        <v>90977</v>
+        <v>78842</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12788,25 +12798,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12816,10 +12826,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>465849</v>
+        <v>465694</v>
       </c>
       <c r="R120" t="n">
-        <v>6798130</v>
+        <v>6798446</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12878,10 +12888,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123913473</v>
+        <v>123913307</v>
       </c>
       <c r="B121" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12894,21 +12904,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12918,10 +12928,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>465720</v>
+        <v>465884</v>
       </c>
       <c r="R121" t="n">
-        <v>6798523</v>
+        <v>6798130</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12973,14 +12983,14 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123913285</v>
+        <v>123913271</v>
       </c>
       <c r="B122" t="n">
         <v>78842</v>
@@ -13020,10 +13030,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>465735</v>
+        <v>465720</v>
       </c>
       <c r="R122" t="n">
-        <v>6798291</v>
+        <v>6798523</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13082,10 +13092,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123913406</v>
+        <v>123913464</v>
       </c>
       <c r="B123" t="n">
-        <v>91172</v>
+        <v>78810</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13094,25 +13104,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13122,10 +13132,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>465872</v>
+        <v>465767</v>
       </c>
       <c r="R123" t="n">
-        <v>6798093</v>
+        <v>6798617</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13184,7 +13194,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123913269</v>
+        <v>123913285</v>
       </c>
       <c r="B124" t="n">
         <v>78842</v>
@@ -13224,10 +13234,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>465705</v>
+        <v>465735</v>
       </c>
       <c r="R124" t="n">
-        <v>6798564</v>
+        <v>6798291</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13286,10 +13296,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>123913564</v>
+        <v>123913306</v>
       </c>
       <c r="B125" t="n">
-        <v>57513</v>
+        <v>78842</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13302,39 +13312,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>465737</v>
+        <v>465841</v>
       </c>
       <c r="R125" t="n">
-        <v>6798286</v>
+        <v>6798109</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13369,11 +13374,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Spår efter födosök</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>

--- a/artfynd/A 15853-2025 artfynd.xlsx
+++ b/artfynd/A 15853-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123876786</v>
+        <v>123877138</v>
       </c>
       <c r="B2" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465862</v>
+        <v>465846</v>
       </c>
       <c r="R2" t="n">
-        <v>6798219</v>
+        <v>6798341</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123876291</v>
+        <v>123878630</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465806</v>
+        <v>465884</v>
       </c>
       <c r="R3" t="n">
-        <v>6798100</v>
+        <v>6798405</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123876691</v>
+        <v>123876866</v>
       </c>
       <c r="B4" t="n">
-        <v>78842</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465832</v>
+        <v>465848</v>
       </c>
       <c r="R4" t="n">
-        <v>6798208</v>
+        <v>6798245</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -955,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Nyare spillning.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123877240</v>
+        <v>123876656</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1021,13 +1031,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465859</v>
+        <v>465833</v>
       </c>
       <c r="R5" t="n">
-        <v>6798332</v>
+        <v>6798204</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123876339</v>
+        <v>123878104</v>
       </c>
       <c r="B6" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,37 +1109,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465823</v>
+        <v>465803</v>
       </c>
       <c r="R6" t="n">
-        <v>6798111</v>
+        <v>6798395</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,19 +1183,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123876521</v>
+        <v>123876143</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1225,13 +1235,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465877</v>
+        <v>465821</v>
       </c>
       <c r="R7" t="n">
-        <v>6798138</v>
+        <v>6798095</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,19 +1285,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123877370</v>
+        <v>123878540</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1327,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465830</v>
+        <v>465797</v>
       </c>
       <c r="R8" t="n">
-        <v>6798388</v>
+        <v>6798473</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1389,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123877017</v>
+        <v>123877248</v>
       </c>
       <c r="B9" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465805</v>
+        <v>465799</v>
       </c>
       <c r="R9" t="n">
-        <v>6798194</v>
+        <v>6798259</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123877138</v>
+        <v>123876845</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465846</v>
+        <v>465832</v>
       </c>
       <c r="R10" t="n">
-        <v>6798341</v>
+        <v>6798231</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1700,7 +1710,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123878540</v>
+        <v>123878210</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1740,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465797</v>
+        <v>465813</v>
       </c>
       <c r="R12" t="n">
-        <v>6798473</v>
+        <v>6798394</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1802,7 +1812,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123876656</v>
+        <v>123877582</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1842,13 +1852,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465833</v>
+        <v>465745</v>
       </c>
       <c r="R13" t="n">
-        <v>6798204</v>
+        <v>6798476</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1904,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123876157</v>
+        <v>123877370</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1944,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465822</v>
+        <v>465830</v>
       </c>
       <c r="R14" t="n">
-        <v>6798106</v>
+        <v>6798388</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2006,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123876866</v>
+        <v>123876733</v>
       </c>
       <c r="B15" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,25 +2028,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465848</v>
+        <v>465844</v>
       </c>
       <c r="R15" t="n">
-        <v>6798245</v>
+        <v>6798212</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2082,11 +2092,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Nyare spillning.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2113,7 +2118,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123877582</v>
+        <v>123876586</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2149,17 +2154,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465745</v>
+        <v>465848</v>
       </c>
       <c r="R16" t="n">
-        <v>6798476</v>
+        <v>6798129</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2203,19 +2208,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123877248</v>
+        <v>123877433</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2251,17 +2256,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465799</v>
+        <v>465854</v>
       </c>
       <c r="R17" t="n">
-        <v>6798259</v>
+        <v>6798343</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2291,11 +2296,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,22 +2310,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123877481</v>
+        <v>123878365</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,42 +2338,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465807</v>
+        <v>465783</v>
       </c>
       <c r="R18" t="n">
-        <v>6798288</v>
+        <v>6798386</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2417,19 +2412,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123878888</v>
+        <v>123876775</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2465,17 +2460,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465907</v>
+        <v>465799</v>
       </c>
       <c r="R19" t="n">
-        <v>6798419</v>
+        <v>6798205</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2505,11 +2500,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Garnlav i synfältet, 30 meter i radie. Miljöbilder</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2524,22 +2514,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123877884</v>
+        <v>123877175</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,21 +2542,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465816</v>
+        <v>465790</v>
       </c>
       <c r="R20" t="n">
-        <v>6798323</v>
+        <v>6798239</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2616,7 +2606,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2643,7 +2633,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123876878</v>
+        <v>123876291</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2683,13 +2673,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465833</v>
+        <v>465806</v>
       </c>
       <c r="R21" t="n">
-        <v>6798269</v>
+        <v>6798100</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2733,22 +2723,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123878561</v>
+        <v>123876691</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2761,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465804</v>
+        <v>465832</v>
       </c>
       <c r="R22" t="n">
-        <v>6798478</v>
+        <v>6798208</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2847,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123877850</v>
+        <v>123877240</v>
       </c>
       <c r="B23" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2863,21 +2853,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2887,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465863</v>
+        <v>465859</v>
       </c>
       <c r="R23" t="n">
-        <v>6798375</v>
+        <v>6798332</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2949,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123878365</v>
+        <v>123877017</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2965,37 +2955,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465783</v>
+        <v>465805</v>
       </c>
       <c r="R24" t="n">
-        <v>6798386</v>
+        <v>6798194</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3025,6 +3015,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3039,22 +3034,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123876806</v>
+        <v>123877326</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3067,37 +3062,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465847</v>
+        <v>465799</v>
       </c>
       <c r="R25" t="n">
-        <v>6798227</v>
+        <v>6798259</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3127,6 +3127,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3141,22 +3146,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123876845</v>
+        <v>123876339</v>
       </c>
       <c r="B26" t="n">
-        <v>78842</v>
+        <v>78547</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3169,21 +3174,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3193,10 +3198,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465832</v>
+        <v>465823</v>
       </c>
       <c r="R26" t="n">
-        <v>6798231</v>
+        <v>6798111</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3255,7 +3260,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123876733</v>
+        <v>123878561</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3295,10 +3300,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465844</v>
+        <v>465804</v>
       </c>
       <c r="R27" t="n">
-        <v>6798212</v>
+        <v>6798478</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3357,7 +3362,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123878210</v>
+        <v>123876521</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3397,13 +3402,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465813</v>
+        <v>465877</v>
       </c>
       <c r="R28" t="n">
-        <v>6798394</v>
+        <v>6798138</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3447,19 +3452,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123876586</v>
+        <v>123877304</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3495,14 +3500,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465848</v>
+        <v>465832</v>
       </c>
       <c r="R29" t="n">
-        <v>6798129</v>
+        <v>6798359</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3549,19 +3554,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123877433</v>
+        <v>123878436</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3597,17 +3602,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465854</v>
+        <v>465800</v>
       </c>
       <c r="R30" t="n">
-        <v>6798343</v>
+        <v>6798391</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3637,6 +3642,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Garnlav synligt ca 30 meters radie. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3651,22 +3661,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123876775</v>
+        <v>123876786</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3679,21 +3689,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3703,13 +3713,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465799</v>
+        <v>465862</v>
       </c>
       <c r="R31" t="n">
-        <v>6798205</v>
+        <v>6798219</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3753,19 +3763,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123876143</v>
+        <v>123876878</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3805,13 +3815,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>465821</v>
+        <v>465833</v>
       </c>
       <c r="R32" t="n">
-        <v>6798095</v>
+        <v>6798269</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3855,22 +3865,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123878104</v>
+        <v>123877850</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3883,37 +3893,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465803</v>
+        <v>465863</v>
       </c>
       <c r="R33" t="n">
-        <v>6798395</v>
+        <v>6798375</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3957,22 +3967,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123877326</v>
+        <v>123877884</v>
       </c>
       <c r="B34" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3985,39 +3995,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>465799</v>
+        <v>465816</v>
       </c>
       <c r="R34" t="n">
-        <v>6798259</v>
+        <v>6798323</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4054,7 +4059,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4081,7 +4086,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123877304</v>
+        <v>123876806</v>
       </c>
       <c r="B35" t="n">
         <v>78810</v>
@@ -4121,13 +4126,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>465832</v>
+        <v>465847</v>
       </c>
       <c r="R35" t="n">
-        <v>6798359</v>
+        <v>6798227</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4183,7 +4188,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123878630</v>
+        <v>123876157</v>
       </c>
       <c r="B36" t="n">
         <v>78810</v>
@@ -4219,17 +4224,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Pipokangasheden, Dlr</t>
+          <t>Pipokangasheden, Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465884</v>
+        <v>465822</v>
       </c>
       <c r="R36" t="n">
-        <v>6798405</v>
+        <v>6798106</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4259,11 +4264,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4278,22 +4278,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123877175</v>
+        <v>123878888</v>
       </c>
       <c r="B37" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4306,21 +4306,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>465790</v>
+        <v>465907</v>
       </c>
       <c r="R37" t="n">
-        <v>6798239</v>
+        <v>6798419</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Miljöbilder.</t>
+          <t>Garnlav i synfältet, 30 meter i radie. Miljöbilder</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4397,10 +4397,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123878436</v>
+        <v>123877481</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4413,34 +4413,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>465800</v>
+        <v>465807</v>
       </c>
       <c r="R38" t="n">
-        <v>6798391</v>
+        <v>6798288</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4473,11 +4478,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Garnlav synligt ca 30 meters radie. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4504,7 +4504,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123913492</v>
+        <v>123913502</v>
       </c>
       <c r="B39" t="n">
         <v>78810</v>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465749</v>
+        <v>465783</v>
       </c>
       <c r="R39" t="n">
-        <v>6798363</v>
+        <v>6798169</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4606,7 +4606,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123913482</v>
+        <v>123913532</v>
       </c>
       <c r="B40" t="n">
         <v>78810</v>
@@ -4646,10 +4646,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465693</v>
+        <v>465912</v>
       </c>
       <c r="R40" t="n">
-        <v>6798461</v>
+        <v>6798108</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4708,10 +4708,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123913470</v>
+        <v>123913289</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4724,21 +4724,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4748,10 +4748,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>465726</v>
+        <v>465786</v>
       </c>
       <c r="R41" t="n">
-        <v>6798570</v>
+        <v>6798177</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4810,10 +4810,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123913262</v>
+        <v>123913309</v>
       </c>
       <c r="B42" t="n">
-        <v>74901</v>
+        <v>78842</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4826,21 +4826,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>465764</v>
+        <v>465845</v>
       </c>
       <c r="R42" t="n">
-        <v>6798656</v>
+        <v>6798127</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4912,7 +4912,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123913258</v>
+        <v>123913262</v>
       </c>
       <c r="B43" t="n">
         <v>74901</v>
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>465915</v>
+        <v>465764</v>
       </c>
       <c r="R43" t="n">
-        <v>6798548</v>
+        <v>6798656</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5014,10 +5014,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123913269</v>
+        <v>123913517</v>
       </c>
       <c r="B44" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>465705</v>
+        <v>465837</v>
       </c>
       <c r="R44" t="n">
-        <v>6798564</v>
+        <v>6798096</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5116,10 +5116,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123913268</v>
+        <v>123913443</v>
       </c>
       <c r="B45" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5132,21 +5132,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5156,10 +5156,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>465767</v>
+        <v>465863</v>
       </c>
       <c r="R45" t="n">
-        <v>6798617</v>
+        <v>6798532</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5218,10 +5218,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123913564</v>
+        <v>123913515</v>
       </c>
       <c r="B46" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5234,39 +5234,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>465737</v>
+        <v>465825</v>
       </c>
       <c r="R46" t="n">
-        <v>6798286</v>
+        <v>6798086</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5301,11 +5296,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Spår efter födosök</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5323,14 +5313,14 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123913517</v>
+        <v>123913439</v>
       </c>
       <c r="B47" t="n">
         <v>78810</v>
@@ -5370,10 +5360,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>465837</v>
+        <v>465919</v>
       </c>
       <c r="R47" t="n">
-        <v>6798096</v>
+        <v>6798535</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5432,10 +5422,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123913323</v>
+        <v>123913434</v>
       </c>
       <c r="B48" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5444,25 +5434,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5472,10 +5462,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>465849</v>
+        <v>465938</v>
       </c>
       <c r="R48" t="n">
-        <v>6798130</v>
+        <v>6798529</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,7 +5524,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123913487</v>
+        <v>123913490</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -5574,10 +5564,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>465720</v>
+        <v>465741</v>
       </c>
       <c r="R49" t="n">
-        <v>6798411</v>
+        <v>6798376</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5636,10 +5626,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123913530</v>
+        <v>123913313</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5652,21 +5642,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5738,10 +5728,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123876771</v>
+        <v>123913280</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5754,21 +5744,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5778,10 +5768,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>465815</v>
+        <v>465753</v>
       </c>
       <c r="R51" t="n">
-        <v>6798172</v>
+        <v>6798400</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5816,11 +5806,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Garnlav bakom björnide, samt i en radie av ca 30 meter.  Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5833,19 +5818,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123913472</v>
+        <v>123913525</v>
       </c>
       <c r="B52" t="n">
         <v>78810</v>
@@ -5885,10 +5870,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>465710</v>
+        <v>465837</v>
       </c>
       <c r="R52" t="n">
-        <v>6798561</v>
+        <v>6798100</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5947,7 +5932,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123913502</v>
+        <v>123913473</v>
       </c>
       <c r="B53" t="n">
         <v>78810</v>
@@ -5987,10 +5972,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>465783</v>
+        <v>465720</v>
       </c>
       <c r="R53" t="n">
-        <v>6798169</v>
+        <v>6798523</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6049,10 +6034,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123913443</v>
+        <v>123913249</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6065,21 +6050,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6089,10 +6074,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>465863</v>
+        <v>465757</v>
       </c>
       <c r="R54" t="n">
-        <v>6798532</v>
+        <v>6798402</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6151,10 +6136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123913256</v>
+        <v>123913494</v>
       </c>
       <c r="B55" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6167,21 +6152,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6191,10 +6176,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>465939</v>
+        <v>465741</v>
       </c>
       <c r="R55" t="n">
-        <v>6798534</v>
+        <v>6798286</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6253,10 +6238,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123913247</v>
+        <v>123913581</v>
       </c>
       <c r="B56" t="n">
-        <v>79428</v>
+        <v>5176</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6265,38 +6250,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>465707</v>
+        <v>465737</v>
       </c>
       <c r="R56" t="n">
-        <v>6798475</v>
+        <v>6798286</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6348,17 +6338,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123913423</v>
+        <v>123913274</v>
       </c>
       <c r="B57" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6371,21 +6361,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6395,10 +6385,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>465920</v>
+        <v>465705</v>
       </c>
       <c r="R57" t="n">
-        <v>6798445</v>
+        <v>6798509</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6457,10 +6447,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123913460</v>
+        <v>123913260</v>
       </c>
       <c r="B58" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6473,21 +6463,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6497,10 +6487,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>465809</v>
+        <v>465830</v>
       </c>
       <c r="R58" t="n">
-        <v>6798627</v>
+        <v>6798623</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6559,10 +6549,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123913266</v>
+        <v>123913451</v>
       </c>
       <c r="B59" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6575,21 +6565,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6599,10 +6589,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>465839</v>
+        <v>465838</v>
       </c>
       <c r="R59" t="n">
-        <v>6798559</v>
+        <v>6798591</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6661,10 +6651,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123913277</v>
+        <v>123913496</v>
       </c>
       <c r="B60" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6677,21 +6667,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6701,10 +6691,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>465709</v>
+        <v>465749</v>
       </c>
       <c r="R60" t="n">
-        <v>6798426</v>
+        <v>6798268</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6763,10 +6753,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123913279</v>
+        <v>123913323</v>
       </c>
       <c r="B61" t="n">
-        <v>78842</v>
+        <v>90977</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6775,25 +6765,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6803,10 +6793,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>465720</v>
+        <v>465849</v>
       </c>
       <c r="R61" t="n">
-        <v>6798411</v>
+        <v>6798130</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6865,7 +6855,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123913500</v>
+        <v>123913458</v>
       </c>
       <c r="B62" t="n">
         <v>78810</v>
@@ -6905,10 +6895,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>465780</v>
+        <v>465826</v>
       </c>
       <c r="R62" t="n">
-        <v>6798219</v>
+        <v>6798611</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6967,10 +6957,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123913490</v>
+        <v>123913368</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6983,21 +6973,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7007,10 +6997,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>465741</v>
+        <v>465859</v>
       </c>
       <c r="R63" t="n">
-        <v>6798376</v>
+        <v>6798098</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7069,10 +7059,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123913368</v>
+        <v>123913572</v>
       </c>
       <c r="B64" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7085,21 +7075,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7109,10 +7099,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>465859</v>
+        <v>465778</v>
       </c>
       <c r="R64" t="n">
-        <v>6798098</v>
+        <v>6798141</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7164,17 +7154,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123913330</v>
+        <v>123913277</v>
       </c>
       <c r="B65" t="n">
-        <v>79399</v>
+        <v>78842</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7187,21 +7177,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7211,10 +7201,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465815</v>
+        <v>465709</v>
       </c>
       <c r="R65" t="n">
-        <v>6798097</v>
+        <v>6798426</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7273,10 +7263,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123913494</v>
+        <v>123913374</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>80763</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7289,21 +7279,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7313,10 +7303,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465741</v>
+        <v>465857</v>
       </c>
       <c r="R66" t="n">
-        <v>6798286</v>
+        <v>6798531</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7375,7 +7365,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123913451</v>
+        <v>123913504</v>
       </c>
       <c r="B67" t="n">
         <v>78810</v>
@@ -7415,10 +7405,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465838</v>
+        <v>465787</v>
       </c>
       <c r="R67" t="n">
-        <v>6798591</v>
+        <v>6798158</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7477,10 +7467,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123913462</v>
+        <v>123913266</v>
       </c>
       <c r="B68" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7493,21 +7483,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7517,10 +7507,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465782</v>
+        <v>465839</v>
       </c>
       <c r="R68" t="n">
-        <v>6798650</v>
+        <v>6798559</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7579,7 +7569,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123913448</v>
+        <v>123913436</v>
       </c>
       <c r="B69" t="n">
         <v>78810</v>
@@ -7619,10 +7609,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465839</v>
+        <v>465927</v>
       </c>
       <c r="R69" t="n">
-        <v>6798559</v>
+        <v>6798517</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7681,10 +7671,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123913438</v>
+        <v>123913339</v>
       </c>
       <c r="B70" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7697,21 +7687,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7721,10 +7711,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>465904</v>
+        <v>465825</v>
       </c>
       <c r="R70" t="n">
-        <v>6798521</v>
+        <v>6798086</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7783,7 +7773,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123913439</v>
+        <v>123913530</v>
       </c>
       <c r="B71" t="n">
         <v>78810</v>
@@ -7823,10 +7813,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>465919</v>
+        <v>465883</v>
       </c>
       <c r="R71" t="n">
-        <v>6798535</v>
+        <v>6798119</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7885,10 +7875,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123913280</v>
+        <v>123913334</v>
       </c>
       <c r="B72" t="n">
-        <v>78842</v>
+        <v>91012</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7901,21 +7891,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7925,10 +7915,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>465753</v>
+        <v>465933</v>
       </c>
       <c r="R72" t="n">
-        <v>6798400</v>
+        <v>6798526</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7987,10 +7977,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123913485</v>
+        <v>123913287</v>
       </c>
       <c r="B73" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8003,21 +7993,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8027,10 +8017,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>465709</v>
+        <v>465786</v>
       </c>
       <c r="R73" t="n">
-        <v>6798426</v>
+        <v>6798207</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8089,7 +8079,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123913311</v>
+        <v>123913268</v>
       </c>
       <c r="B74" t="n">
         <v>78842</v>
@@ -8129,10 +8119,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>465842</v>
+        <v>465767</v>
       </c>
       <c r="R74" t="n">
-        <v>6798116</v>
+        <v>6798617</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8191,10 +8181,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123913334</v>
+        <v>123913279</v>
       </c>
       <c r="B75" t="n">
-        <v>91012</v>
+        <v>78842</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8207,21 +8197,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8231,10 +8221,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>465933</v>
+        <v>465720</v>
       </c>
       <c r="R75" t="n">
-        <v>6798526</v>
+        <v>6798411</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8293,10 +8283,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123913251</v>
+        <v>123913472</v>
       </c>
       <c r="B76" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8309,21 +8299,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8333,10 +8323,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>465775</v>
+        <v>465710</v>
       </c>
       <c r="R76" t="n">
-        <v>6798229</v>
+        <v>6798561</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8395,7 +8385,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123913532</v>
+        <v>123913423</v>
       </c>
       <c r="B77" t="n">
         <v>78810</v>
@@ -8435,10 +8425,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>465912</v>
+        <v>465920</v>
       </c>
       <c r="R77" t="n">
-        <v>6798108</v>
+        <v>6798445</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8497,10 +8487,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123913453</v>
+        <v>123913307</v>
       </c>
       <c r="B78" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8513,21 +8503,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8537,10 +8527,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>465833</v>
+        <v>465884</v>
       </c>
       <c r="R78" t="n">
-        <v>6798603</v>
+        <v>6798130</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8599,10 +8589,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123913473</v>
+        <v>123913306</v>
       </c>
       <c r="B79" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8615,21 +8605,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8639,10 +8629,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>465720</v>
+        <v>465841</v>
       </c>
       <c r="R79" t="n">
-        <v>6798523</v>
+        <v>6798109</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8701,10 +8691,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123913291</v>
+        <v>123913487</v>
       </c>
       <c r="B80" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8717,21 +8707,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8741,10 +8731,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>465775</v>
+        <v>465720</v>
       </c>
       <c r="R80" t="n">
-        <v>6798148</v>
+        <v>6798411</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8803,10 +8793,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123913289</v>
+        <v>123913251</v>
       </c>
       <c r="B81" t="n">
-        <v>78842</v>
+        <v>79428</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8819,21 +8809,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8843,10 +8833,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>465786</v>
+        <v>465775</v>
       </c>
       <c r="R81" t="n">
-        <v>6798177</v>
+        <v>6798229</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8905,10 +8895,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123913309</v>
+        <v>123913483</v>
       </c>
       <c r="B82" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8921,21 +8911,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8945,10 +8935,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>465845</v>
+        <v>465694</v>
       </c>
       <c r="R82" t="n">
-        <v>6798127</v>
+        <v>6798446</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9007,7 +8997,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123913450</v>
+        <v>123913470</v>
       </c>
       <c r="B83" t="n">
         <v>78810</v>
@@ -9047,10 +9037,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>465835</v>
+        <v>465726</v>
       </c>
       <c r="R83" t="n">
-        <v>6798579</v>
+        <v>6798570</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9109,7 +9099,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123913527</v>
+        <v>123913453</v>
       </c>
       <c r="B84" t="n">
         <v>78810</v>
@@ -9149,10 +9139,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>465878</v>
+        <v>465833</v>
       </c>
       <c r="R84" t="n">
-        <v>6798095</v>
+        <v>6798603</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9211,7 +9201,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123913525</v>
+        <v>123913477</v>
       </c>
       <c r="B85" t="n">
         <v>78810</v>
@@ -9251,10 +9241,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>465837</v>
+        <v>465708</v>
       </c>
       <c r="R85" t="n">
-        <v>6798100</v>
+        <v>6798481</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9313,10 +9303,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123913406</v>
+        <v>123913460</v>
       </c>
       <c r="B86" t="n">
-        <v>91172</v>
+        <v>78810</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9325,25 +9315,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9353,10 +9343,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>465872</v>
+        <v>465809</v>
       </c>
       <c r="R86" t="n">
-        <v>6798093</v>
+        <v>6798627</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9415,10 +9405,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123913446</v>
+        <v>123913330</v>
       </c>
       <c r="B87" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9431,21 +9421,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9455,10 +9445,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>465875</v>
+        <v>465815</v>
       </c>
       <c r="R87" t="n">
-        <v>6798559</v>
+        <v>6798097</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9517,10 +9507,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123913432</v>
+        <v>123913317</v>
       </c>
       <c r="B88" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9533,21 +9523,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9557,10 +9547,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>465943</v>
+        <v>465913</v>
       </c>
       <c r="R88" t="n">
-        <v>6798495</v>
+        <v>6798106</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9619,7 +9609,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123913436</v>
+        <v>123913441</v>
       </c>
       <c r="B89" t="n">
         <v>78810</v>
@@ -9659,10 +9649,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>465927</v>
+        <v>465893</v>
       </c>
       <c r="R89" t="n">
-        <v>6798517</v>
+        <v>6798543</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9721,7 +9711,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123913426</v>
+        <v>123913432</v>
       </c>
       <c r="B90" t="n">
         <v>78810</v>
@@ -9761,10 +9751,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>465923</v>
+        <v>465943</v>
       </c>
       <c r="R90" t="n">
-        <v>6798451</v>
+        <v>6798495</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9823,10 +9813,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123913477</v>
+        <v>123913271</v>
       </c>
       <c r="B91" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9839,21 +9829,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9863,10 +9853,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>465708</v>
+        <v>465720</v>
       </c>
       <c r="R91" t="n">
-        <v>6798481</v>
+        <v>6798523</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9925,10 +9915,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123913572</v>
+        <v>123913485</v>
       </c>
       <c r="B92" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9941,21 +9931,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9965,10 +9955,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>465778</v>
+        <v>465709</v>
       </c>
       <c r="R92" t="n">
-        <v>6798141</v>
+        <v>6798426</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10020,17 +10010,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123913313</v>
+        <v>123913256</v>
       </c>
       <c r="B93" t="n">
-        <v>78842</v>
+        <v>74901</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10043,21 +10033,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10067,10 +10057,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>465883</v>
+        <v>465939</v>
       </c>
       <c r="R93" t="n">
-        <v>6798119</v>
+        <v>6798534</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10129,10 +10119,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123913374</v>
+        <v>123913489</v>
       </c>
       <c r="B94" t="n">
-        <v>80763</v>
+        <v>78810</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10145,21 +10135,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10169,10 +10159,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>465857</v>
+        <v>465753</v>
       </c>
       <c r="R94" t="n">
-        <v>6798531</v>
+        <v>6798400</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10231,10 +10221,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123913244</v>
+        <v>123913527</v>
       </c>
       <c r="B95" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10247,21 +10237,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10271,10 +10261,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>465933</v>
+        <v>465878</v>
       </c>
       <c r="R95" t="n">
-        <v>6798458</v>
+        <v>6798095</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10333,10 +10323,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123913274</v>
+        <v>123913482</v>
       </c>
       <c r="B96" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10349,21 +10339,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10373,10 +10363,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>465705</v>
+        <v>465693</v>
       </c>
       <c r="R96" t="n">
-        <v>6798509</v>
+        <v>6798461</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10435,10 +10425,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123913504</v>
+        <v>123913327</v>
       </c>
       <c r="B97" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10451,21 +10441,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10475,10 +10465,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>465787</v>
+        <v>465779</v>
       </c>
       <c r="R97" t="n">
-        <v>6798158</v>
+        <v>6798140</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10537,10 +10527,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123913522</v>
+        <v>123913285</v>
       </c>
       <c r="B98" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10553,21 +10543,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10577,10 +10567,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>465842</v>
+        <v>465735</v>
       </c>
       <c r="R98" t="n">
-        <v>6798113</v>
+        <v>6798291</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10639,7 +10629,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123913515</v>
+        <v>123913522</v>
       </c>
       <c r="B99" t="n">
         <v>78810</v>
@@ -10679,10 +10669,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>465825</v>
+        <v>465842</v>
       </c>
       <c r="R99" t="n">
-        <v>6798086</v>
+        <v>6798113</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10741,7 +10731,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123913249</v>
+        <v>123913244</v>
       </c>
       <c r="B100" t="n">
         <v>79428</v>
@@ -10781,10 +10771,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>465757</v>
+        <v>465933</v>
       </c>
       <c r="R100" t="n">
-        <v>6798402</v>
+        <v>6798458</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10843,10 +10833,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>123913315</v>
+        <v>123913498</v>
       </c>
       <c r="B101" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10859,21 +10849,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10883,10 +10873,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>465899</v>
+        <v>465746</v>
       </c>
       <c r="R101" t="n">
-        <v>6798123</v>
+        <v>6798258</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10945,10 +10935,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123913282</v>
+        <v>123913438</v>
       </c>
       <c r="B102" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10961,21 +10951,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10985,10 +10975,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>465748</v>
+        <v>465904</v>
       </c>
       <c r="R102" t="n">
-        <v>6798396</v>
+        <v>6798521</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11047,10 +11037,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>123913317</v>
+        <v>123913564</v>
       </c>
       <c r="B103" t="n">
-        <v>78842</v>
+        <v>57513</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11063,34 +11053,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>465913</v>
+        <v>465737</v>
       </c>
       <c r="R103" t="n">
-        <v>6798106</v>
+        <v>6798286</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11125,6 +11120,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Spår efter födosök</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -11142,17 +11142,17 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>123913483</v>
+        <v>123913406</v>
       </c>
       <c r="B104" t="n">
-        <v>78810</v>
+        <v>91172</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11161,25 +11161,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11189,10 +11189,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>465694</v>
+        <v>465872</v>
       </c>
       <c r="R104" t="n">
-        <v>6798446</v>
+        <v>6798093</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11251,10 +11251,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>123913581</v>
+        <v>123913258</v>
       </c>
       <c r="B105" t="n">
-        <v>5176</v>
+        <v>74901</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11263,43 +11263,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100526</v>
+        <v>6440</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>465737</v>
+        <v>465915</v>
       </c>
       <c r="R105" t="n">
-        <v>6798286</v>
+        <v>6798548</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11351,17 +11346,17 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123913327</v>
+        <v>123913430</v>
       </c>
       <c r="B106" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11374,21 +11369,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11398,10 +11393,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>465779</v>
+        <v>465947</v>
       </c>
       <c r="R106" t="n">
-        <v>6798140</v>
+        <v>6798479</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11460,10 +11455,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123913339</v>
+        <v>123913475</v>
       </c>
       <c r="B107" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11476,21 +11471,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11500,10 +11495,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>465825</v>
+        <v>465719</v>
       </c>
       <c r="R107" t="n">
-        <v>6798086</v>
+        <v>6798495</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11562,10 +11557,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123913489</v>
+        <v>123913315</v>
       </c>
       <c r="B108" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11578,21 +11573,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11602,10 +11597,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>465753</v>
+        <v>465899</v>
       </c>
       <c r="R108" t="n">
-        <v>6798400</v>
+        <v>6798123</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11657,14 +11652,14 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad, lennart karlsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123913519</v>
+        <v>123913500</v>
       </c>
       <c r="B109" t="n">
         <v>78810</v>
@@ -11704,10 +11699,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>465865</v>
+        <v>465780</v>
       </c>
       <c r="R109" t="n">
-        <v>6798133</v>
+        <v>6798219</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11766,7 +11761,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123913458</v>
+        <v>123876771</v>
       </c>
       <c r="B110" t="n">
         <v>78810</v>
@@ -11806,10 +11801,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>465826</v>
+        <v>465815</v>
       </c>
       <c r="R110" t="n">
-        <v>6798611</v>
+        <v>6798172</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11844,6 +11839,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Garnlav bakom björnide, samt i en radie av ca 30 meter.  Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -11856,19 +11856,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123913498</v>
+        <v>123913450</v>
       </c>
       <c r="B111" t="n">
         <v>78810</v>
@@ -11908,10 +11908,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>465746</v>
+        <v>465835</v>
       </c>
       <c r="R111" t="n">
-        <v>6798258</v>
+        <v>6798579</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11970,7 +11970,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>123913430</v>
+        <v>123913480</v>
       </c>
       <c r="B112" t="n">
         <v>78810</v>
@@ -12010,7 +12010,7 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>465947</v>
+        <v>465696</v>
       </c>
       <c r="R112" t="n">
         <v>6798479</v>
@@ -12072,10 +12072,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>123913434</v>
+        <v>123913269</v>
       </c>
       <c r="B113" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12088,21 +12088,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12112,10 +12112,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>465938</v>
+        <v>465705</v>
       </c>
       <c r="R113" t="n">
-        <v>6798529</v>
+        <v>6798564</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12174,7 +12174,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123913441</v>
+        <v>123913426</v>
       </c>
       <c r="B114" t="n">
         <v>78810</v>
@@ -12214,10 +12214,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>465893</v>
+        <v>465923</v>
       </c>
       <c r="R114" t="n">
-        <v>6798543</v>
+        <v>6798451</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12276,7 +12276,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123913475</v>
+        <v>123913519</v>
       </c>
       <c r="B115" t="n">
         <v>78810</v>
@@ -12316,10 +12316,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>465719</v>
+        <v>465865</v>
       </c>
       <c r="R115" t="n">
-        <v>6798495</v>
+        <v>6798133</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12378,10 +12378,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123913260</v>
+        <v>123913492</v>
       </c>
       <c r="B116" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12394,21 +12394,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12418,10 +12418,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>465830</v>
+        <v>465749</v>
       </c>
       <c r="R116" t="n">
-        <v>6798623</v>
+        <v>6798363</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12480,10 +12480,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123913480</v>
+        <v>123913247</v>
       </c>
       <c r="B117" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12496,21 +12496,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12520,10 +12520,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>465696</v>
+        <v>465707</v>
       </c>
       <c r="R117" t="n">
-        <v>6798479</v>
+        <v>6798475</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12582,7 +12582,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123913496</v>
+        <v>123913446</v>
       </c>
       <c r="B118" t="n">
         <v>78810</v>
@@ -12622,10 +12622,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>465749</v>
+        <v>465875</v>
       </c>
       <c r="R118" t="n">
-        <v>6798268</v>
+        <v>6798559</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12684,10 +12684,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123913287</v>
+        <v>123913448</v>
       </c>
       <c r="B119" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12700,21 +12700,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12724,10 +12724,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>465786</v>
+        <v>465839</v>
       </c>
       <c r="R119" t="n">
-        <v>6798207</v>
+        <v>6798559</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12786,7 +12786,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>123913276</v>
+        <v>123913311</v>
       </c>
       <c r="B120" t="n">
         <v>78842</v>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>465694</v>
+        <v>465842</v>
       </c>
       <c r="R120" t="n">
-        <v>6798446</v>
+        <v>6798116</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12888,7 +12888,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123913307</v>
+        <v>123913291</v>
       </c>
       <c r="B121" t="n">
         <v>78842</v>
@@ -12928,10 +12928,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>465884</v>
+        <v>465775</v>
       </c>
       <c r="R121" t="n">
-        <v>6798130</v>
+        <v>6798148</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12990,7 +12990,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123913271</v>
+        <v>123913282</v>
       </c>
       <c r="B122" t="n">
         <v>78842</v>
@@ -13030,10 +13030,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>465720</v>
+        <v>465748</v>
       </c>
       <c r="R122" t="n">
-        <v>6798523</v>
+        <v>6798396</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13092,10 +13092,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123913464</v>
+        <v>123913276</v>
       </c>
       <c r="B123" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13108,21 +13108,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13132,10 +13132,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>465767</v>
+        <v>465694</v>
       </c>
       <c r="R123" t="n">
-        <v>6798617</v>
+        <v>6798446</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13194,10 +13194,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123913285</v>
+        <v>123913464</v>
       </c>
       <c r="B124" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13210,21 +13210,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13234,10 +13234,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>465735</v>
+        <v>465767</v>
       </c>
       <c r="R124" t="n">
-        <v>6798291</v>
+        <v>6798617</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13296,10 +13296,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>123913306</v>
+        <v>123913462</v>
       </c>
       <c r="B125" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13312,21 +13312,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13336,10 +13336,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>465841</v>
+        <v>465782</v>
       </c>
       <c r="R125" t="n">
-        <v>6798109</v>
+        <v>6798650</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>

--- a/artfynd/A 15853-2025 artfynd.xlsx
+++ b/artfynd/A 15853-2025 artfynd.xlsx
@@ -4504,10 +4504,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123913502</v>
+        <v>123913289</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4520,21 +4520,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>465783</v>
+        <v>465786</v>
       </c>
       <c r="R39" t="n">
-        <v>6798169</v>
+        <v>6798177</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4606,10 +4606,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123913532</v>
+        <v>123913309</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4622,21 +4622,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4646,10 +4646,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>465912</v>
+        <v>465845</v>
       </c>
       <c r="R40" t="n">
-        <v>6798108</v>
+        <v>6798127</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4708,10 +4708,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123913289</v>
+        <v>123913502</v>
       </c>
       <c r="B41" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4724,21 +4724,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4748,10 +4748,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>465786</v>
+        <v>465783</v>
       </c>
       <c r="R41" t="n">
-        <v>6798177</v>
+        <v>6798169</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4810,10 +4810,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123913309</v>
+        <v>123913532</v>
       </c>
       <c r="B42" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4826,21 +4826,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>465845</v>
+        <v>465912</v>
       </c>
       <c r="R42" t="n">
-        <v>6798127</v>
+        <v>6798108</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5728,10 +5728,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123913280</v>
+        <v>123913525</v>
       </c>
       <c r="B51" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5744,21 +5744,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5768,10 +5768,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>465753</v>
+        <v>465837</v>
       </c>
       <c r="R51" t="n">
-        <v>6798400</v>
+        <v>6798100</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5830,7 +5830,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123913525</v>
+        <v>123913473</v>
       </c>
       <c r="B52" t="n">
         <v>78810</v>
@@ -5870,10 +5870,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>465837</v>
+        <v>465720</v>
       </c>
       <c r="R52" t="n">
-        <v>6798100</v>
+        <v>6798523</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5932,10 +5932,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123913473</v>
+        <v>123913280</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5948,21 +5948,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5972,10 +5972,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>465720</v>
+        <v>465753</v>
       </c>
       <c r="R53" t="n">
-        <v>6798523</v>
+        <v>6798400</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6136,10 +6136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123913494</v>
+        <v>123913581</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6148,35 +6148,40 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>465741</v>
+        <v>465737</v>
       </c>
       <c r="R55" t="n">
         <v>6798286</v>
@@ -6231,17 +6236,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123913581</v>
+        <v>123913494</v>
       </c>
       <c r="B56" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6250,40 +6255,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Pipokangasheden, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>465737</v>
+        <v>465741</v>
       </c>
       <c r="R56" t="n">
         <v>6798286</v>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7059,10 +7059,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123913572</v>
+        <v>123913504</v>
       </c>
       <c r="B64" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7075,21 +7075,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7099,10 +7099,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>465778</v>
+        <v>465787</v>
       </c>
       <c r="R64" t="n">
-        <v>6798141</v>
+        <v>6798158</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7154,17 +7154,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123913277</v>
+        <v>123913572</v>
       </c>
       <c r="B65" t="n">
-        <v>78842</v>
+        <v>78455</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7177,21 +7177,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7201,10 +7201,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465709</v>
+        <v>465778</v>
       </c>
       <c r="R65" t="n">
-        <v>6798426</v>
+        <v>6798141</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7256,17 +7256,17 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123913374</v>
+        <v>123913277</v>
       </c>
       <c r="B66" t="n">
-        <v>80763</v>
+        <v>78842</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7279,21 +7279,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1049</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7303,10 +7303,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>465857</v>
+        <v>465709</v>
       </c>
       <c r="R66" t="n">
-        <v>6798531</v>
+        <v>6798426</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7365,10 +7365,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123913504</v>
+        <v>123913374</v>
       </c>
       <c r="B67" t="n">
-        <v>78810</v>
+        <v>80763</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7381,21 +7381,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7405,10 +7405,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>465787</v>
+        <v>465857</v>
       </c>
       <c r="R67" t="n">
-        <v>6798158</v>
+        <v>6798531</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7467,10 +7467,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123913266</v>
+        <v>123913436</v>
       </c>
       <c r="B68" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7483,21 +7483,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7507,10 +7507,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465839</v>
+        <v>465927</v>
       </c>
       <c r="R68" t="n">
-        <v>6798559</v>
+        <v>6798517</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7569,10 +7569,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123913436</v>
+        <v>123913266</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7585,21 +7585,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7609,10 +7609,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>465927</v>
+        <v>465839</v>
       </c>
       <c r="R69" t="n">
-        <v>6798517</v>
+        <v>6798559</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -10323,10 +10323,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123913482</v>
+        <v>123913285</v>
       </c>
       <c r="B96" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10339,21 +10339,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10363,10 +10363,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>465693</v>
+        <v>465735</v>
       </c>
       <c r="R96" t="n">
-        <v>6798461</v>
+        <v>6798291</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10425,10 +10425,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>123913327</v>
+        <v>123913522</v>
       </c>
       <c r="B97" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10441,21 +10441,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10465,10 +10465,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>465779</v>
+        <v>465842</v>
       </c>
       <c r="R97" t="n">
-        <v>6798140</v>
+        <v>6798113</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10527,10 +10527,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>123913285</v>
+        <v>123913244</v>
       </c>
       <c r="B98" t="n">
-        <v>78842</v>
+        <v>79428</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10543,21 +10543,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10567,10 +10567,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>465735</v>
+        <v>465933</v>
       </c>
       <c r="R98" t="n">
-        <v>6798291</v>
+        <v>6798458</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10629,7 +10629,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>123913522</v>
+        <v>123913482</v>
       </c>
       <c r="B99" t="n">
         <v>78810</v>
@@ -10669,10 +10669,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>465842</v>
+        <v>465693</v>
       </c>
       <c r="R99" t="n">
-        <v>6798113</v>
+        <v>6798461</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10731,10 +10731,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>123913244</v>
+        <v>123913327</v>
       </c>
       <c r="B100" t="n">
-        <v>79428</v>
+        <v>79399</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10747,21 +10747,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10771,10 +10771,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>465933</v>
+        <v>465779</v>
       </c>
       <c r="R100" t="n">
-        <v>6798458</v>
+        <v>6798140</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12480,10 +12480,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123913247</v>
+        <v>123913311</v>
       </c>
       <c r="B117" t="n">
-        <v>79428</v>
+        <v>78842</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12496,21 +12496,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12520,10 +12520,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>465707</v>
+        <v>465842</v>
       </c>
       <c r="R117" t="n">
-        <v>6798475</v>
+        <v>6798116</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12582,10 +12582,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123913446</v>
+        <v>123913247</v>
       </c>
       <c r="B118" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12598,21 +12598,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12622,10 +12622,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>465875</v>
+        <v>465707</v>
       </c>
       <c r="R118" t="n">
-        <v>6798559</v>
+        <v>6798475</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12684,7 +12684,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123913448</v>
+        <v>123913446</v>
       </c>
       <c r="B119" t="n">
         <v>78810</v>
@@ -12724,7 +12724,7 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>465839</v>
+        <v>465875</v>
       </c>
       <c r="R119" t="n">
         <v>6798559</v>
@@ -12786,10 +12786,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>123913311</v>
+        <v>123913448</v>
       </c>
       <c r="B120" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12802,21 +12802,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12826,10 +12826,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>465842</v>
+        <v>465839</v>
       </c>
       <c r="R120" t="n">
-        <v>6798116</v>
+        <v>6798559</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
